--- a/research/traditional_assets/database/data/germany/germany_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_food_wholesalers.xlsx
@@ -647,10 +647,10 @@
         <v>-0.06286116983791402</v>
       </c>
       <c r="X2">
-        <v>0.1115698607025245</v>
+        <v>0.111527576529726</v>
       </c>
       <c r="Y2">
-        <v>-0.1744310305404385</v>
+        <v>-0.17438874636764</v>
       </c>
       <c r="Z2">
         <v>7.48041673871693</v>
@@ -659,10 +659,10 @@
         <v>0.03663755836071243</v>
       </c>
       <c r="AB2">
-        <v>0.05987077389074671</v>
+        <v>0.05985984902778248</v>
       </c>
       <c r="AC2">
-        <v>-0.02323321553003428</v>
+        <v>-0.02322229066707005</v>
       </c>
       <c r="AD2">
         <v>4482.5</v>
@@ -781,10 +781,10 @@
         <v>-0.06286116983791402</v>
       </c>
       <c r="X3">
-        <v>0.1115698607025245</v>
+        <v>0.111527576529726</v>
       </c>
       <c r="Y3">
-        <v>-0.1744310305404385</v>
+        <v>-0.17438874636764</v>
       </c>
       <c r="Z3">
         <v>7.48041673871693</v>
@@ -793,10 +793,10 @@
         <v>0.03663755836071243</v>
       </c>
       <c r="AB3">
-        <v>0.05987077389074671</v>
+        <v>0.05985984902778248</v>
       </c>
       <c r="AC3">
-        <v>-0.02323321553003428</v>
+        <v>-0.02322229066707005</v>
       </c>
       <c r="AD3">
         <v>4482.5</v>
@@ -1133,49 +1133,49 @@
         <v>0.741469816272966</v>
       </c>
       <c r="F2">
-        <v>4.56018916843922</v>
+        <v>4.55251821647582</v>
       </c>
       <c r="G2">
         <v>6.16405390539054</v>
       </c>
       <c r="H2">
-        <v>3.40770214521452</v>
+        <v>3.57393151815182</v>
       </c>
       <c r="I2">
         <v>0.741632335666187</v>
       </c>
       <c r="J2">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="K2">
         <v>1561.6</v>
       </c>
       <c r="L2">
-        <v>2675.54096080156</v>
+        <v>2826.67928289698</v>
       </c>
       <c r="M2">
         <v>5158.5</v>
       </c>
       <c r="N2">
-        <v>4268.02196080156</v>
+        <v>4540.04228289698</v>
       </c>
       <c r="O2">
         <v>4482.5</v>
       </c>
       <c r="P2">
-        <v>2478.081</v>
+        <v>2598.963</v>
       </c>
       <c r="Q2">
-        <v>0.0598707738907467</v>
+        <v>0.0598598490277825</v>
       </c>
       <c r="R2">
-        <v>0.062806493355012</v>
+        <v>0.0617751224086698</v>
       </c>
       <c r="S2">
         <v>0.04186</v>
       </c>
       <c r="T2">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.111569860702524</v>
+        <v>0.111527576529726</v>
       </c>
       <c r="X2">
-        <v>0.07828676839832539</v>
+        <v>0.07917512703275401</v>
       </c>
       <c r="Y2">
         <v>1.51795788752254</v>
       </c>
       <c r="Z2">
-        <v>0.7497894294379009</v>
+        <v>0.770788153181386</v>
       </c>
       <c r="AA2">
         <v>4482.5</v>
@@ -1230,7 +1230,7 @@
         <v>1561.6</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06765540861460888</v>
+        <v>0.06764135753004567</v>
       </c>
       <c r="C2">
-        <v>4206.704098090362</v>
+        <v>4206.260408129141</v>
       </c>
       <c r="D2">
-        <v>3321.104098090362</v>
+        <v>3320.660408129141</v>
       </c>
       <c r="E2">
         <v>-4482.5</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06765540861460888</v>
+        <v>0.06764135753004567</v>
       </c>
       <c r="T2">
         <v>0.5044193424952811</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06749374238876504</v>
+        <v>0.06746993345745553</v>
       </c>
       <c r="C3">
-        <v>4171.012648239478</v>
+        <v>4172.088115043628</v>
       </c>
       <c r="D3">
-        <v>3345.853648239477</v>
+        <v>3346.929115043628</v>
       </c>
       <c r="E3">
         <v>-4422.059</v>
@@ -1533,37 +1533,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M3">
-        <v>3.124799700000001</v>
+        <v>3.0401823</v>
       </c>
       <c r="N3">
-        <v>651.1752003000001</v>
+        <v>651.2598177000002</v>
       </c>
       <c r="O3">
-        <v>195.35256009</v>
+        <v>195.3779453100001</v>
       </c>
       <c r="P3">
-        <v>455.8226402100001</v>
+        <v>455.8818723900001</v>
       </c>
       <c r="Q3">
-        <v>1013.52264021</v>
+        <v>1013.58187239</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06780994180683338</v>
+        <v>0.0677957913711672</v>
       </c>
       <c r="T3">
         <v>0.5079859439068638</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>209.38942102433</v>
+        <v>215.2173571959814</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06733207616292122</v>
+        <v>0.0672985093848654</v>
       </c>
       <c r="C4">
-        <v>4135.692845445167</v>
+        <v>4138.334742976343</v>
       </c>
       <c r="D4">
-        <v>3370.974845445167</v>
+        <v>3373.616742976343</v>
       </c>
       <c r="E4">
         <v>-4361.618</v>
@@ -1615,37 +1615,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M4">
-        <v>6.249599400000001</v>
+        <v>6.0803646</v>
       </c>
       <c r="N4">
-        <v>648.0504006000002</v>
+        <v>648.2196354000001</v>
       </c>
       <c r="O4">
-        <v>194.4151201800001</v>
+        <v>194.46589062</v>
       </c>
       <c r="P4">
-        <v>453.6352804200002</v>
+        <v>453.7537447800001</v>
       </c>
       <c r="Q4">
-        <v>1011.33528042</v>
+        <v>1011.45374478</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06796762873767472</v>
+        <v>0.06795337692333203</v>
       </c>
       <c r="T4">
         <v>0.5116253331023565</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.694710512165</v>
+        <v>107.6086785979907</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06717040993707739</v>
+        <v>0.06712708531227525</v>
       </c>
       <c r="C5">
-        <v>4100.753124189105</v>
+        <v>4105.010393609632</v>
       </c>
       <c r="D5">
-        <v>3396.476124189105</v>
+        <v>3400.733393609632</v>
       </c>
       <c r="E5">
         <v>-4301.177</v>
@@ -1697,37 +1697,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M5">
-        <v>9.374399100000002</v>
+        <v>9.120546900000001</v>
       </c>
       <c r="N5">
-        <v>644.9256009000002</v>
+        <v>645.1794531000002</v>
       </c>
       <c r="O5">
-        <v>193.47768027</v>
+        <v>193.55383593</v>
       </c>
       <c r="P5">
-        <v>451.4479206300001</v>
+        <v>451.6256171700001</v>
       </c>
       <c r="Q5">
-        <v>1009.14792063</v>
+        <v>1009.32561717</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06812856694544062</v>
+        <v>0.06811421166213943</v>
       </c>
       <c r="T5">
         <v>0.5153397612503335</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.79647367477666</v>
+        <v>71.73911906532712</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06700874371123355</v>
+        <v>0.06695566123968512</v>
       </c>
       <c r="C6">
-        <v>4066.202176124406</v>
+        <v>4072.125496041082</v>
       </c>
       <c r="D6">
-        <v>3422.366176124406</v>
+        <v>3428.289496041082</v>
       </c>
       <c r="E6">
         <v>-4240.736</v>
@@ -1779,37 +1779,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M6">
-        <v>12.4991988</v>
+        <v>12.1607292</v>
       </c>
       <c r="N6">
-        <v>641.8008012000001</v>
+        <v>642.1392708000002</v>
       </c>
       <c r="O6">
-        <v>192.54024036</v>
+        <v>192.6417812400001</v>
       </c>
       <c r="P6">
-        <v>449.2605608400001</v>
+        <v>449.4974895600001</v>
       </c>
       <c r="Q6">
-        <v>1006.96056084</v>
+        <v>1007.19748956</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06829285803253496</v>
+        <v>0.068278397124672</v>
       </c>
       <c r="T6">
         <v>0.51913157331806</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.34735525608249</v>
+        <v>53.80433929899534</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06684707748538975</v>
+        <v>0.06678423716709497</v>
       </c>
       <c r="C7">
-        <v>4032.048959952522</v>
+        <v>4039.690820157116</v>
       </c>
       <c r="D7">
-        <v>3448.653959952522</v>
+        <v>3456.295820157115</v>
       </c>
       <c r="E7">
         <v>-4180.295</v>
@@ -1861,37 +1861,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M7">
-        <v>15.6239985</v>
+        <v>15.2009115</v>
       </c>
       <c r="N7">
-        <v>638.6760015000002</v>
+        <v>639.0990885000002</v>
       </c>
       <c r="O7">
-        <v>191.60280045</v>
+        <v>191.7297265500001</v>
       </c>
       <c r="P7">
-        <v>447.0732010500002</v>
+        <v>447.3693619500002</v>
       </c>
       <c r="Q7">
-        <v>1004.77320105</v>
+        <v>1005.06936195</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06846060787935762</v>
+        <v>0.06844603912325788</v>
       </c>
       <c r="T7">
         <v>0.523003213008265</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.877884204866</v>
+        <v>43.04347143919627</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06668541125954591</v>
+        <v>0.06661281309450484</v>
       </c>
       <c r="C8">
-        <v>3998.302711758862</v>
+        <v>4007.717490667452</v>
       </c>
       <c r="D8">
-        <v>3475.348711758862</v>
+        <v>3484.763490667453</v>
       </c>
       <c r="E8">
         <v>-4119.854</v>
@@ -1943,37 +1943,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M8">
-        <v>18.7487982</v>
+        <v>18.2410938</v>
       </c>
       <c r="N8">
-        <v>635.5512018000002</v>
+        <v>636.0589062000001</v>
       </c>
       <c r="O8">
-        <v>190.6653605400001</v>
+        <v>190.81767186</v>
       </c>
       <c r="P8">
-        <v>444.8858412600001</v>
+        <v>445.2412343400001</v>
       </c>
       <c r="Q8">
-        <v>1002.58584126</v>
+        <v>1002.94123434</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06863192687185736</v>
+        <v>0.06861724797287749</v>
       </c>
       <c r="T8">
         <v>0.5269572280110276</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.89823683738833</v>
+        <v>35.86955953266356</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06652374503370208</v>
+        <v>0.06644138902191471</v>
       </c>
       <c r="C9">
-        <v>3964.97295583215</v>
+        <v>3976.217001838934</v>
       </c>
       <c r="D9">
-        <v>3502.45995583215</v>
+        <v>3513.704001838934</v>
       </c>
       <c r="E9">
         <v>-4059.413</v>
@@ -2025,37 +2025,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M9">
-        <v>21.8735979</v>
+        <v>21.2812761</v>
       </c>
       <c r="N9">
-        <v>632.4264021000001</v>
+        <v>633.0187239000002</v>
       </c>
       <c r="O9">
-        <v>189.72792063</v>
+        <v>189.9056171700001</v>
       </c>
       <c r="P9">
-        <v>442.6984814700001</v>
+        <v>443.1131067300001</v>
       </c>
       <c r="Q9">
-        <v>1000.39848147</v>
+        <v>1000.81310673</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06880693014376568</v>
+        <v>0.06879213873324162</v>
       </c>
       <c r="T9">
         <v>0.5309962755944948</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.91277443204714</v>
+        <v>30.74533674228305</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06636207880785827</v>
+        <v>0.06626996494932456</v>
       </c>
       <c r="C10">
-        <v>3932.069515994212</v>
+        <v>3945.201232969649</v>
       </c>
       <c r="D10">
-        <v>3529.997515994212</v>
+        <v>3543.129232969649</v>
       </c>
       <c r="E10">
         <v>-3998.972</v>
@@ -2107,37 +2107,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M10">
-        <v>24.9983976</v>
+        <v>24.3214584</v>
       </c>
       <c r="N10">
-        <v>629.3016024000002</v>
+        <v>629.9785416000002</v>
       </c>
       <c r="O10">
-        <v>188.7904807200001</v>
+        <v>188.9935624800001</v>
       </c>
       <c r="P10">
-        <v>440.5111216800001</v>
+        <v>440.9849791200002</v>
       </c>
       <c r="Q10">
-        <v>998.2111216800001</v>
+        <v>998.6849791200002</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.06898573783462855</v>
+        <v>0.06897083146665714</v>
       </c>
       <c r="T10">
         <v>0.5351231285602113</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.17367762804125</v>
+        <v>26.90216964949767</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06620041258201444</v>
+        <v>0.06609854087673443</v>
       </c>
       <c r="C11">
-        <v>3899.602527468472</v>
+        <v>3914.682464647147</v>
       </c>
       <c r="D11">
-        <v>3557.971527468471</v>
+        <v>3573.051464647147</v>
       </c>
       <c r="E11">
         <v>-3938.531</v>
@@ -2189,37 +2189,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M11">
-        <v>28.1231973</v>
+        <v>27.3616407</v>
       </c>
       <c r="N11">
-        <v>626.1768027000002</v>
+        <v>626.9383593000002</v>
       </c>
       <c r="O11">
-        <v>187.85304081</v>
+        <v>188.0815077900001</v>
       </c>
       <c r="P11">
-        <v>438.3237618900001</v>
+        <v>438.8568515100002</v>
       </c>
       <c r="Q11">
-        <v>996.0237618900002</v>
+        <v>996.5568515100002</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.06916847536485103</v>
+        <v>0.06915345151289498</v>
       </c>
       <c r="T11">
         <v>0.5393406815911083</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.26549122492555</v>
+        <v>23.91303968844237</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06603874635617062</v>
+        <v>0.0659271168041443</v>
       </c>
       <c r="C12">
-        <v>3867.582449317231</v>
+        <v>3884.673395837502</v>
       </c>
       <c r="D12">
-        <v>3586.392449317231</v>
+        <v>3603.483395837502</v>
       </c>
       <c r="E12">
         <v>-3878.09</v>
@@ -2271,37 +2271,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M12">
-        <v>31.24799700000001</v>
+        <v>30.401823</v>
       </c>
       <c r="N12">
-        <v>623.0520030000001</v>
+        <v>623.8981770000001</v>
       </c>
       <c r="O12">
-        <v>186.9156009</v>
+        <v>187.1694531</v>
       </c>
       <c r="P12">
-        <v>436.1364021000001</v>
+        <v>436.7287239000001</v>
       </c>
       <c r="Q12">
-        <v>993.8364021000001</v>
+        <v>994.4287239000001</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.06935527372907846</v>
+        <v>0.06934012978238255</v>
       </c>
       <c r="T12">
         <v>0.5436519580226918</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.938942102433</v>
+        <v>21.52173571959813</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06587708013032678</v>
+        <v>0.06575569273155416</v>
       </c>
       <c r="C13">
-        <v>3836.020077479906</v>
+        <v>3855.187161855154</v>
       </c>
       <c r="D13">
-        <v>3615.271077479907</v>
+        <v>3634.438161855154</v>
       </c>
       <c r="E13">
         <v>-3817.649</v>
@@ -2353,37 +2353,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M13">
-        <v>34.3727967</v>
+        <v>33.4420053</v>
       </c>
       <c r="N13">
-        <v>619.9272033000002</v>
+        <v>620.8579947000002</v>
       </c>
       <c r="O13">
-        <v>185.97816099</v>
+        <v>186.25739841</v>
       </c>
       <c r="P13">
-        <v>433.9490423100002</v>
+        <v>434.6005962900001</v>
       </c>
       <c r="Q13">
-        <v>991.6490423100001</v>
+        <v>992.3005962900002</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.06954626980935594</v>
+        <v>0.06953100306916198</v>
       </c>
       <c r="T13">
         <v>0.5480601170707154</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.03540191130273</v>
+        <v>19.56521429054376</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06571541390448295</v>
+        <v>0.06558426865896402</v>
       </c>
       <c r="C14">
-        <v>3804.926558446244</v>
+        <v>3826.237353266969</v>
       </c>
       <c r="D14">
-        <v>3644.618558446244</v>
+        <v>3665.929353266969</v>
       </c>
       <c r="E14">
         <v>-3757.208</v>
@@ -2435,37 +2435,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M14">
-        <v>37.49759640000001</v>
+        <v>36.4821876</v>
       </c>
       <c r="N14">
-        <v>616.8024036000002</v>
+        <v>617.8178124000002</v>
       </c>
       <c r="O14">
-        <v>185.0407210800001</v>
+        <v>185.34534372</v>
       </c>
       <c r="P14">
-        <v>431.7616825200001</v>
+        <v>432.4724686800001</v>
       </c>
       <c r="Q14">
-        <v>989.4616825200002</v>
+        <v>990.1724686800002</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.06974160670963972</v>
+        <v>0.06972621438518639</v>
       </c>
       <c r="T14">
         <v>0.5525684615516488</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.44911841869417</v>
+        <v>17.93477976633178</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06555374767863913</v>
+        <v>0.06541284458637389</v>
       </c>
       <c r="C15">
-        <v>3774.31340360099</v>
+        <v>3797.838035787684</v>
       </c>
       <c r="D15">
-        <v>3674.446403600989</v>
+        <v>3697.971035787684</v>
       </c>
       <c r="E15">
         <v>-3696.767</v>
@@ -2517,37 +2517,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M15">
-        <v>40.6223961</v>
+        <v>39.5223699</v>
       </c>
       <c r="N15">
-        <v>613.6776039000001</v>
+        <v>614.7776301000001</v>
       </c>
       <c r="O15">
-        <v>184.10328117</v>
+        <v>184.43328903</v>
       </c>
       <c r="P15">
-        <v>429.5743227300001</v>
+        <v>430.3443410700001</v>
       </c>
       <c r="Q15">
-        <v>987.2743227300001</v>
+        <v>988.0443410700002</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0699414341133783</v>
+        <v>0.06992591331767113</v>
       </c>
       <c r="T15">
         <v>0.557180446135592</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.10687854033308</v>
+        <v>16.55518132276779</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06539208145279531</v>
+        <v>0.06524142051378376</v>
       </c>
       <c r="C16">
-        <v>3744.192504278746</v>
+        <v>3770.003771227908</v>
       </c>
       <c r="D16">
-        <v>3704.766504278746</v>
+        <v>3730.577771227908</v>
       </c>
       <c r="E16">
         <v>-3636.326</v>
@@ -2599,37 +2599,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M16">
-        <v>43.74719580000001</v>
+        <v>42.5625522</v>
       </c>
       <c r="N16">
-        <v>610.5528042000002</v>
+        <v>611.7374478000002</v>
       </c>
       <c r="O16">
-        <v>183.1658412600001</v>
+        <v>183.52123434</v>
       </c>
       <c r="P16">
-        <v>427.3869629400001</v>
+        <v>428.2162134600001</v>
       </c>
       <c r="Q16">
-        <v>985.0869629400001</v>
+        <v>985.9162134600001</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07014590866604105</v>
+        <v>0.07013025641137646</v>
       </c>
       <c r="T16">
         <v>0.5618996861749759</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.95638721602357</v>
+        <v>15.37266837114153</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06523041522695147</v>
+        <v>0.06506999644119361</v>
       </c>
       <c r="C17">
-        <v>3714.576147570396</v>
+        <v>3742.749639560228</v>
       </c>
       <c r="D17">
-        <v>3735.591147570395</v>
+        <v>3763.764639560228</v>
       </c>
       <c r="E17">
         <v>-3575.885</v>
@@ -2681,37 +2681,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M17">
-        <v>46.8719955</v>
+        <v>45.6027345</v>
       </c>
       <c r="N17">
-        <v>607.4280045000002</v>
+        <v>608.6972655000002</v>
       </c>
       <c r="O17">
-        <v>182.22840135</v>
+        <v>182.60917965</v>
       </c>
       <c r="P17">
-        <v>425.1996031500001</v>
+        <v>426.0880858500001</v>
       </c>
       <c r="Q17">
-        <v>982.8996031500002</v>
+        <v>983.7880858500002</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07035519438464879</v>
+        <v>0.07033940757787484</v>
       </c>
       <c r="T17">
         <v>0.5667299671564628</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.95929473495533</v>
+        <v>14.34782381306542</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06506874900110765</v>
+        <v>0.06489857236860347</v>
       </c>
       <c r="C18">
-        <v>3685.477032925204</v>
+        <v>3716.091262173677</v>
       </c>
       <c r="D18">
-        <v>3766.933032925203</v>
+        <v>3797.547262173677</v>
       </c>
       <c r="E18">
         <v>-3515.444</v>
@@ -2763,37 +2763,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M18">
-        <v>49.99679520000001</v>
+        <v>48.6429168</v>
       </c>
       <c r="N18">
-        <v>604.3032048000002</v>
+        <v>605.6570832000002</v>
       </c>
       <c r="O18">
-        <v>181.2909614400001</v>
+        <v>181.6971249600001</v>
       </c>
       <c r="P18">
-        <v>423.0122433600002</v>
+        <v>423.9599582400002</v>
       </c>
       <c r="Q18">
-        <v>980.7122433600002</v>
+        <v>981.6599582400002</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07056946309655673</v>
+        <v>0.07055353853405176</v>
       </c>
       <c r="T18">
         <v>0.5716752548279852</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03619</v>
+        <v>0.03521</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.08683881402063</v>
+        <v>13.45108482474884</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06503798277526382</v>
+        <v>0.06490564829601335</v>
       </c>
       <c r="C19">
-        <v>3631.060277451433</v>
+        <v>3654.243810618284</v>
       </c>
       <c r="D19">
-        <v>3772.957277451433</v>
+        <v>3796.140810618283</v>
       </c>
       <c r="E19">
         <v>-3455.003</v>
@@ -2845,37 +2845,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M19">
-        <v>54.25184160000001</v>
+        <v>53.2243446</v>
       </c>
       <c r="N19">
-        <v>600.0481584000001</v>
+        <v>601.0756554000002</v>
       </c>
       <c r="O19">
-        <v>180.01444752</v>
+        <v>180.32269662</v>
       </c>
       <c r="P19">
-        <v>420.0337108800001</v>
+        <v>420.7529587800001</v>
       </c>
       <c r="Q19">
-        <v>977.7337108800002</v>
+        <v>978.4529587800002</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07078889490995642</v>
+        <v>0.07077282927230524</v>
       </c>
       <c r="T19">
         <v>0.5767397060578576</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03696</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.0604200835092</v>
+        <v>12.29324672604799</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06488401654942</v>
+        <v>0.0647447242234232</v>
       </c>
       <c r="C20">
-        <v>3601.058781146833</v>
+        <v>3626.048750552055</v>
       </c>
       <c r="D20">
-        <v>3803.396781146833</v>
+        <v>3828.386750552055</v>
       </c>
       <c r="E20">
         <v>-3394.562</v>
@@ -2927,37 +2927,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M20">
-        <v>57.4431264</v>
+        <v>56.3551884</v>
       </c>
       <c r="N20">
-        <v>596.8568736000002</v>
+        <v>597.9448116000002</v>
       </c>
       <c r="O20">
-        <v>179.0570620800001</v>
+        <v>179.3834434800001</v>
       </c>
       <c r="P20">
-        <v>417.7998115200002</v>
+        <v>418.5613681200001</v>
       </c>
       <c r="Q20">
-        <v>975.4998115200002</v>
+        <v>976.2613681200002</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07101367871880487</v>
+        <v>0.07099746856515024</v>
       </c>
       <c r="T20">
         <v>0.5819276804884583</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03696</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.39039674553647</v>
+        <v>11.61028857460088</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06473005032357618</v>
+        <v>0.06458380015083307</v>
       </c>
       <c r="C21">
-        <v>3571.552439944354</v>
+        <v>3598.406203602122</v>
       </c>
       <c r="D21">
-        <v>3834.331439944354</v>
+        <v>3861.185203602122</v>
       </c>
       <c r="E21">
         <v>-3334.121</v>
@@ -3009,37 +3009,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M21">
-        <v>60.63441120000001</v>
+        <v>59.4860322</v>
       </c>
       <c r="N21">
-        <v>593.6655888000001</v>
+        <v>594.8139678000002</v>
       </c>
       <c r="O21">
-        <v>178.09967664</v>
+        <v>178.4441903400001</v>
       </c>
       <c r="P21">
-        <v>415.5659121600001</v>
+        <v>416.3697774600001</v>
       </c>
       <c r="Q21">
-        <v>973.2659121600002</v>
+        <v>974.0697774600002</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07124401274515577</v>
+        <v>0.07122765450720131</v>
       </c>
       <c r="T21">
         <v>0.5872437530531481</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03696</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.79090217998192</v>
+        <v>10.99922075488505</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06457608409773234</v>
+        <v>0.06442287607824294</v>
       </c>
       <c r="C22">
-        <v>3542.553434844339</v>
+        <v>3571.330492904257</v>
       </c>
       <c r="D22">
-        <v>3865.773434844339</v>
+        <v>3894.550492904256</v>
       </c>
       <c r="E22">
         <v>-3273.68</v>
@@ -3091,37 +3091,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M22">
-        <v>63.82569600000001</v>
+        <v>62.616876</v>
       </c>
       <c r="N22">
-        <v>590.4743040000002</v>
+        <v>591.6831240000001</v>
       </c>
       <c r="O22">
-        <v>177.1422912</v>
+        <v>177.5049372</v>
       </c>
       <c r="P22">
-        <v>413.3320128000001</v>
+        <v>414.1781868000001</v>
       </c>
       <c r="Q22">
-        <v>971.0320128000002</v>
+        <v>971.8781868000001</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07148010512216543</v>
+        <v>0.07146359509780367</v>
       </c>
       <c r="T22">
         <v>0.5926927274319553</v>
       </c>
       <c r="U22">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03696</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.25135707098282</v>
+        <v>10.44925971714079</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06474551787188852</v>
+        <v>0.06426195200565278</v>
       </c>
       <c r="C23">
-        <v>3447.540005231831</v>
+        <v>3544.836440986144</v>
       </c>
       <c r="D23">
-        <v>3831.201005231831</v>
+        <v>3928.497440986143</v>
       </c>
       <c r="E23">
         <v>-3213.239</v>
@@ -3173,45 +3173,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M23">
-        <v>69.809355</v>
+        <v>65.7477198</v>
       </c>
       <c r="N23">
-        <v>584.4906450000002</v>
+        <v>588.5522802000002</v>
       </c>
       <c r="O23">
-        <v>175.3471935000001</v>
+        <v>176.5656840600001</v>
       </c>
       <c r="P23">
-        <v>409.1434515000001</v>
+        <v>411.9865961400001</v>
       </c>
       <c r="Q23">
-        <v>966.8434515000001</v>
+        <v>969.6865961400001</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07172217452137787</v>
+        <v>0.07170550886791492</v>
       </c>
       <c r="T23">
         <v>0.5982796505292131</v>
       </c>
       <c r="U23">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.0385</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.372669322041441</v>
+        <v>9.951675921086471</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0646069516460447</v>
+        <v>0.06436282793306267</v>
       </c>
       <c r="C24">
-        <v>3415.326602863565</v>
+        <v>3463.046817591267</v>
       </c>
       <c r="D24">
-        <v>3859.428602863565</v>
+        <v>3907.148817591267</v>
       </c>
       <c r="E24">
         <v>-3152.798</v>
@@ -3255,37 +3255,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M24">
-        <v>73.13361</v>
+        <v>71.13905699999999</v>
       </c>
       <c r="N24">
-        <v>581.1663900000002</v>
+        <v>583.1609430000002</v>
       </c>
       <c r="O24">
-        <v>174.3499170000001</v>
+        <v>174.9482829000001</v>
       </c>
       <c r="P24">
-        <v>406.8164730000001</v>
+        <v>408.2126601000001</v>
       </c>
       <c r="Q24">
-        <v>964.5164730000001</v>
+        <v>965.9126601000002</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07197045082826242</v>
+        <v>0.07195362555520854</v>
       </c>
       <c r="T24">
         <v>0.6040098280648623</v>
       </c>
       <c r="U24">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.946638898312283</v>
+        <v>9.197479241255619</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06446838542020086</v>
+        <v>0.06421380386047251</v>
       </c>
       <c r="C25">
-        <v>3383.532239590589</v>
+        <v>3434.226618672088</v>
       </c>
       <c r="D25">
-        <v>3888.075239590589</v>
+        <v>3938.769618672088</v>
       </c>
       <c r="E25">
         <v>-3092.357</v>
@@ -3337,37 +3337,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M25">
-        <v>76.45786500000001</v>
+        <v>74.37265050000001</v>
       </c>
       <c r="N25">
-        <v>577.8421350000002</v>
+        <v>579.9273495000002</v>
       </c>
       <c r="O25">
-        <v>173.3526405000001</v>
+        <v>173.9782048500001</v>
       </c>
       <c r="P25">
-        <v>404.4894945000001</v>
+        <v>405.9491446500002</v>
       </c>
       <c r="Q25">
-        <v>962.1894945000001</v>
+        <v>963.6491446500002</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07222517587039073</v>
+        <v>0.07220818683178248</v>
       </c>
       <c r="T25">
         <v>0.609888841380658</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.55765459838566</v>
+        <v>8.797588839461895</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06432981919435704</v>
+        <v>0.06406477978788239</v>
       </c>
       <c r="C26">
-        <v>3352.1663161521</v>
+        <v>3405.922413989938</v>
       </c>
       <c r="D26">
-        <v>3917.1503161521</v>
+        <v>3970.906413989938</v>
       </c>
       <c r="E26">
         <v>-3031.916</v>
@@ -3419,37 +3419,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M26">
-        <v>79.78212000000001</v>
+        <v>77.606244</v>
       </c>
       <c r="N26">
-        <v>574.5178800000002</v>
+        <v>576.6937560000001</v>
       </c>
       <c r="O26">
-        <v>172.3553640000001</v>
+        <v>173.0081268</v>
       </c>
       <c r="P26">
-        <v>402.1625160000002</v>
+        <v>403.6856292000001</v>
       </c>
       <c r="Q26">
-        <v>959.8625160000001</v>
+        <v>961.3856292000002</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07248660420310137</v>
+        <v>0.07246944708931893</v>
       </c>
       <c r="T26">
         <v>0.6159225655731854</v>
       </c>
       <c r="U26">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.201085656786258</v>
+        <v>8.431022637817648</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06419125296851322</v>
+        <v>0.06391575571529225</v>
       </c>
       <c r="C27">
-        <v>3321.238516601325</v>
+        <v>3378.146937580961</v>
       </c>
       <c r="D27">
-        <v>3946.663516601325</v>
+        <v>4003.571937580961</v>
       </c>
       <c r="E27">
         <v>-2971.475</v>
@@ -3501,37 +3501,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M27">
-        <v>83.106375</v>
+        <v>80.8398375</v>
       </c>
       <c r="N27">
-        <v>571.1936250000002</v>
+        <v>573.4601625000001</v>
       </c>
       <c r="O27">
-        <v>171.3580875000001</v>
+        <v>172.03804875</v>
       </c>
       <c r="P27">
-        <v>399.8355375000002</v>
+        <v>401.4221137500001</v>
       </c>
       <c r="Q27">
-        <v>957.5355375000001</v>
+        <v>959.1221137500002</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07275500395801762</v>
+        <v>0.07273767428705633</v>
       </c>
       <c r="T27">
         <v>0.6221171890775133</v>
       </c>
       <c r="U27">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.87304223051481</v>
+        <v>8.093781732304944</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06432568674266939</v>
+        <v>0.06376673164270211</v>
       </c>
       <c r="C28">
-        <v>3232.158099383977</v>
+        <v>3350.913345968353</v>
       </c>
       <c r="D28">
-        <v>3918.024099383977</v>
+        <v>4036.779345968354</v>
       </c>
       <c r="E28">
         <v>-2911.034</v>
@@ -3583,45 +3583,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M28">
-        <v>88.78782900000002</v>
+        <v>84.073431</v>
       </c>
       <c r="N28">
-        <v>565.5121710000002</v>
+        <v>570.2265690000002</v>
       </c>
       <c r="O28">
-        <v>169.6536513000001</v>
+        <v>171.0679707</v>
       </c>
       <c r="P28">
-        <v>395.8585197000001</v>
+        <v>399.1585983000001</v>
       </c>
       <c r="Q28">
-        <v>953.5585197000001</v>
+        <v>956.8585983000002</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07303065776036403</v>
+        <v>0.07301315086851637</v>
       </c>
       <c r="T28">
         <v>0.628479234838715</v>
       </c>
       <c r="U28">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03955</v>
+        <v>0.03745</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.369253279072744</v>
+        <v>7.7824824349086</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06419762051682557</v>
+        <v>0.06376890757011197</v>
       </c>
       <c r="C29">
-        <v>3198.990548073408</v>
+        <v>3289.983516094184</v>
       </c>
       <c r="D29">
-        <v>3945.297548073408</v>
+        <v>4036.290516094184</v>
       </c>
       <c r="E29">
         <v>-2850.593</v>
@@ -3665,37 +3665,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M29">
-        <v>92.20274550000001</v>
+        <v>88.61255010000001</v>
       </c>
       <c r="N29">
-        <v>562.0972545000002</v>
+        <v>565.6874499000002</v>
       </c>
       <c r="O29">
-        <v>168.6291763500001</v>
+        <v>169.7062349700001</v>
       </c>
       <c r="P29">
-        <v>393.4680781500001</v>
+        <v>395.9812149300001</v>
       </c>
       <c r="Q29">
-        <v>951.1680781500002</v>
+        <v>953.6812149300001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07331386372167885</v>
+        <v>0.07329617475357805</v>
       </c>
       <c r="T29">
         <v>0.6350155832235115</v>
       </c>
       <c r="U29">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.096317972440421</v>
+        <v>7.383829934491414</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06406955429098174</v>
+        <v>0.06362548349752183</v>
       </c>
       <c r="C30">
-        <v>3166.205360512252</v>
+        <v>3262.018562202874</v>
       </c>
       <c r="D30">
-        <v>3972.953360512251</v>
+        <v>4068.766562202874</v>
       </c>
       <c r="E30">
         <v>-2790.152</v>
@@ -3747,37 +3747,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M30">
-        <v>95.61766200000001</v>
+        <v>91.89449640000001</v>
       </c>
       <c r="N30">
-        <v>558.6823380000002</v>
+        <v>562.4055036000002</v>
       </c>
       <c r="O30">
-        <v>167.6047014</v>
+        <v>168.72165108</v>
       </c>
       <c r="P30">
-        <v>391.0776366000001</v>
+        <v>393.6838525200002</v>
       </c>
       <c r="Q30">
-        <v>948.7776366000002</v>
+        <v>951.3838525200002</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07360493651525241</v>
+        <v>0.07358706041322477</v>
       </c>
       <c r="T30">
         <v>0.6417334968412187</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.842878044853263</v>
+        <v>7.120121722545292</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0639414880651379</v>
+        <v>0.06348205942493169</v>
       </c>
       <c r="C31">
-        <v>3133.810634362971</v>
+        <v>3234.580452688971</v>
       </c>
       <c r="D31">
-        <v>4000.99963436297</v>
+        <v>4101.769452688971</v>
       </c>
       <c r="E31">
         <v>-2729.711</v>
@@ -3829,37 +3829,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M31">
-        <v>99.0325785</v>
+        <v>95.1764427</v>
       </c>
       <c r="N31">
-        <v>555.2674215000002</v>
+        <v>559.1235573000001</v>
       </c>
       <c r="O31">
-        <v>166.5802264500001</v>
+        <v>167.73706719</v>
       </c>
       <c r="P31">
-        <v>388.6871950500001</v>
+        <v>391.3864901100001</v>
       </c>
       <c r="Q31">
-        <v>946.3871950500002</v>
+        <v>949.0864901100001</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07390420854244775</v>
+        <v>0.07388614003511507</v>
       </c>
       <c r="T31">
         <v>0.6486406474622418</v>
       </c>
       <c r="U31">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.606916732961771</v>
+        <v>6.874600283836834</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06381342183929409</v>
+        <v>0.06333863535234155</v>
       </c>
       <c r="C32">
-        <v>3101.814697568986</v>
+        <v>3207.682112531772</v>
       </c>
       <c r="D32">
-        <v>4029.444697568986</v>
+        <v>4135.312112531772</v>
       </c>
       <c r="E32">
         <v>-2669.27</v>
@@ -3911,37 +3911,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M32">
-        <v>102.447495</v>
+        <v>98.458389</v>
       </c>
       <c r="N32">
-        <v>551.8525050000002</v>
+        <v>555.8416110000002</v>
       </c>
       <c r="O32">
-        <v>165.5557515</v>
+        <v>166.7524833000001</v>
       </c>
       <c r="P32">
-        <v>386.2967535000001</v>
+        <v>389.0891277000001</v>
       </c>
       <c r="Q32">
-        <v>943.9967535000002</v>
+        <v>946.7891277000001</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07421203119899154</v>
+        <v>0.07419376478905937</v>
       </c>
       <c r="T32">
         <v>0.6557451452438654</v>
       </c>
       <c r="U32">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.386686175196379</v>
+        <v>6.645446941042273</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06368535561345025</v>
+        <v>0.06319521127975142</v>
       </c>
       <c r="C33">
-        <v>3070.226116599226</v>
+        <v>3181.336892978026</v>
       </c>
       <c r="D33">
-        <v>4058.297116599226</v>
+        <v>4169.407892978026</v>
       </c>
       <c r="E33">
         <v>-2608.829</v>
@@ -3993,37 +3993,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M33">
-        <v>105.8624115</v>
+        <v>101.7403353</v>
       </c>
       <c r="N33">
-        <v>548.4375885000002</v>
+        <v>552.5596647000002</v>
       </c>
       <c r="O33">
-        <v>164.5312765500001</v>
+        <v>165.7678994100001</v>
       </c>
       <c r="P33">
-        <v>383.9063119500001</v>
+        <v>386.7917652900002</v>
       </c>
       <c r="Q33">
-        <v>941.6063119500002</v>
+        <v>944.4917652900002</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07452877625137717</v>
+        <v>0.07451030620253829</v>
       </c>
       <c r="T33">
         <v>0.6630555704974201</v>
       </c>
       <c r="U33">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.180664040512625</v>
+        <v>6.43107768487962</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06387088938760642</v>
+        <v>0.06305178720716129</v>
       </c>
       <c r="C34">
-        <v>2968.118590700055</v>
+        <v>3155.558589261002</v>
       </c>
       <c r="D34">
-        <v>4016.630590700055</v>
+        <v>4204.070589261001</v>
       </c>
       <c r="E34">
         <v>-2548.388</v>
@@ -4075,45 +4075,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M34">
-        <v>111.9850848</v>
+        <v>105.0222816</v>
       </c>
       <c r="N34">
-        <v>542.3149152000002</v>
+        <v>549.2777184000001</v>
       </c>
       <c r="O34">
-        <v>162.6944745600001</v>
+        <v>164.78331552</v>
       </c>
       <c r="P34">
-        <v>379.6204406400001</v>
+        <v>384.4944028800001</v>
       </c>
       <c r="Q34">
-        <v>937.3204406400002</v>
+        <v>942.1944028800001</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07485483733471533</v>
+        <v>0.07483615765759012</v>
       </c>
       <c r="T34">
         <v>0.6705810082584325</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04053</v>
+        <v>0.03801</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.84274237206275</v>
+        <v>6.230106507227131</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06375262316176258</v>
+        <v>0.06313936313457114</v>
       </c>
       <c r="C35">
-        <v>2934.137887687894</v>
+        <v>3073.884088474751</v>
       </c>
       <c r="D35">
-        <v>4043.090887687894</v>
+        <v>4182.83708847475</v>
       </c>
       <c r="E35">
         <v>-2487.947</v>
@@ -4157,37 +4157,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M35">
-        <v>115.4846187</v>
+        <v>110.2987809</v>
       </c>
       <c r="N35">
-        <v>538.8153813000001</v>
+        <v>544.0012191000002</v>
       </c>
       <c r="O35">
-        <v>161.64461439</v>
+        <v>163.20036573</v>
       </c>
       <c r="P35">
-        <v>377.1707669100001</v>
+        <v>380.8008533700001</v>
       </c>
       <c r="Q35">
-        <v>934.8707669100002</v>
+        <v>938.5008533700002</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07519063158472029</v>
+        <v>0.07517173602174798</v>
       </c>
       <c r="T35">
         <v>0.6783310859526094</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.665689572909332</v>
+        <v>5.932069191165468</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06363435693591876</v>
+        <v>0.06300293906198101</v>
       </c>
       <c r="C36">
-        <v>2900.508120733666</v>
+        <v>3046.61414538164</v>
       </c>
       <c r="D36">
-        <v>4069.902120733665</v>
+        <v>4216.00814538164</v>
       </c>
       <c r="E36">
         <v>-2427.506</v>
@@ -4239,37 +4239,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M36">
-        <v>118.9841526</v>
+        <v>113.6411682</v>
       </c>
       <c r="N36">
-        <v>535.3158474000002</v>
+        <v>540.6588318000001</v>
       </c>
       <c r="O36">
-        <v>160.5947542200001</v>
+        <v>162.19764954</v>
       </c>
       <c r="P36">
-        <v>374.7210931800001</v>
+        <v>378.4611822600001</v>
       </c>
       <c r="Q36">
-        <v>932.4210931800002</v>
+        <v>936.1611822600001</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07553660141805875</v>
+        <v>0.07551748342724396</v>
       </c>
       <c r="T36">
         <v>0.6863160144860037</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.499051644294353</v>
+        <v>5.757596567895895</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06351609071007494</v>
+        <v>0.06286651498939087</v>
       </c>
       <c r="C37">
-        <v>2867.236318004664</v>
+        <v>3019.87451919016</v>
       </c>
       <c r="D37">
-        <v>4097.071318004664</v>
+        <v>4249.70951919016</v>
       </c>
       <c r="E37">
         <v>-2367.065</v>
@@ -4321,37 +4321,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M37">
-        <v>122.4836865</v>
+        <v>116.9835555</v>
       </c>
       <c r="N37">
-        <v>531.8163135000002</v>
+        <v>537.3164445000002</v>
       </c>
       <c r="O37">
-        <v>159.5448940500001</v>
+        <v>161.1949333500001</v>
       </c>
       <c r="P37">
-        <v>372.2714194500002</v>
+        <v>376.1215111500002</v>
       </c>
       <c r="Q37">
-        <v>929.9714194500002</v>
+        <v>933.8215111500002</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07589321647703838</v>
+        <v>0.0758738692144475</v>
       </c>
       <c r="T37">
         <v>0.6945466331281178</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.3419358830288</v>
+        <v>5.593093808813155</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06339782448423112</v>
+        <v>0.06273009091680073</v>
       </c>
       <c r="C38">
-        <v>2834.329696599449</v>
+        <v>2993.678029912644</v>
       </c>
       <c r="D38">
-        <v>4124.605696599448</v>
+        <v>4283.954029912644</v>
       </c>
       <c r="E38">
         <v>-2306.624</v>
@@ -4403,37 +4403,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M38">
-        <v>125.9832204</v>
+        <v>120.3259428</v>
       </c>
       <c r="N38">
-        <v>528.3167796000001</v>
+        <v>533.9740572000002</v>
       </c>
       <c r="O38">
-        <v>158.49503388</v>
+        <v>160.19221716</v>
       </c>
       <c r="P38">
-        <v>369.8217457200001</v>
+        <v>373.7818400400001</v>
       </c>
       <c r="Q38">
-        <v>927.5217457200001</v>
+        <v>931.4818400400002</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.07626097575661112</v>
+        <v>0.07624139205750115</v>
       </c>
       <c r="T38">
         <v>0.703034458602798</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.193548775166888</v>
+        <v>5.437730091901678</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0632795582583873</v>
+        <v>0.06259366684421061</v>
       </c>
       <c r="C39">
-        <v>2801.795668939364</v>
+        <v>2968.037914137106</v>
       </c>
       <c r="D39">
-        <v>4152.512668939364</v>
+        <v>4318.754914137106</v>
       </c>
       <c r="E39">
         <v>-2246.183</v>
@@ -4485,37 +4485,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M39">
-        <v>129.4827543</v>
+        <v>123.6683301</v>
       </c>
       <c r="N39">
-        <v>524.8172457000002</v>
+        <v>530.6316699000001</v>
       </c>
       <c r="O39">
-        <v>157.44517371</v>
+        <v>159.18950097</v>
       </c>
       <c r="P39">
-        <v>367.3720719900001</v>
+        <v>371.4421689300001</v>
       </c>
       <c r="Q39">
-        <v>925.0720719900002</v>
+        <v>929.1421689300001</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.07664040993394808</v>
+        <v>0.07662058229239778</v>
       </c>
       <c r="T39">
         <v>0.7117917388544521</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.053182592054269</v>
+        <v>5.290764413742174</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06316129203254346</v>
+        <v>0.06245724277162047</v>
       </c>
       <c r="C40">
-        <v>2769.6418494213</v>
+        <v>2942.967842086183</v>
       </c>
       <c r="D40">
-        <v>4180.7998494213</v>
+        <v>4354.125842086183</v>
       </c>
       <c r="E40">
         <v>-2185.742</v>
@@ -4567,37 +4567,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M40">
-        <v>132.9822882</v>
+        <v>127.0107174</v>
       </c>
       <c r="N40">
-        <v>521.3177118000001</v>
+        <v>527.2892826000002</v>
       </c>
       <c r="O40">
-        <v>156.39531354</v>
+        <v>158.1867847800001</v>
       </c>
       <c r="P40">
-        <v>364.9223982600001</v>
+        <v>369.1024978200002</v>
       </c>
       <c r="Q40">
-        <v>922.6223982600002</v>
+        <v>926.8024978200002</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.0770320839234572</v>
+        <v>0.07701200447035558</v>
       </c>
       <c r="T40">
         <v>0.72083151201745</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.920204102789683</v>
+        <v>5.151533771275274</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06304302580669964</v>
+        <v>0.06232081869903033</v>
       </c>
       <c r="C41">
-        <v>2737.87606134422</v>
+        <v>2918.481935521245</v>
       </c>
       <c r="D41">
-        <v>4209.475061344219</v>
+        <v>4390.080935521245</v>
       </c>
       <c r="E41">
         <v>-2125.301</v>
@@ -4649,37 +4649,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M41">
-        <v>136.4818221</v>
+        <v>130.3531047</v>
       </c>
       <c r="N41">
-        <v>517.8181779000001</v>
+        <v>523.9468953000002</v>
       </c>
       <c r="O41">
-        <v>155.34545337</v>
+        <v>157.18406859</v>
       </c>
       <c r="P41">
-        <v>362.4727245300001</v>
+        <v>366.7628267100001</v>
       </c>
       <c r="Q41">
-        <v>920.1727245300001</v>
+        <v>924.4628267100002</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.07743659968311417</v>
+        <v>0.07741626016234479</v>
       </c>
       <c r="T41">
         <v>0.7301676711857922</v>
       </c>
       <c r="U41">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.794045023230973</v>
+        <v>5.019443161755396</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0629247595808558</v>
+        <v>0.0621843946264402</v>
       </c>
       <c r="C42">
-        <v>2706.506344122722</v>
+        <v>2894.594786541021</v>
       </c>
       <c r="D42">
-        <v>4238.546344122722</v>
+        <v>4426.634786541021</v>
       </c>
       <c r="E42">
         <v>-2064.86</v>
@@ -4731,37 +4731,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M42">
-        <v>139.981356</v>
+        <v>133.695492</v>
       </c>
       <c r="N42">
-        <v>514.3186440000002</v>
+        <v>520.6045080000001</v>
       </c>
       <c r="O42">
-        <v>154.2955932</v>
+        <v>156.1813524</v>
       </c>
       <c r="P42">
-        <v>360.0230508000001</v>
+        <v>364.4231556000001</v>
       </c>
       <c r="Q42">
-        <v>917.7230508000002</v>
+        <v>922.1231556000001</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.07785459930142635</v>
+        <v>0.07783399104406699</v>
       </c>
       <c r="T42">
         <v>0.7398150356597456</v>
       </c>
       <c r="U42">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.6741938976502</v>
+        <v>4.89395708271151</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06280649335501198</v>
+        <v>0.06204797055385006</v>
       </c>
       <c r="C43">
-        <v>2675.540960801559</v>
+        <v>2871.321477327241</v>
       </c>
       <c r="D43">
-        <v>4268.021960801559</v>
+        <v>4463.802477327241</v>
       </c>
       <c r="E43">
         <v>-2004.419</v>
@@ -4813,37 +4813,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M43">
-        <v>143.4808899</v>
+        <v>137.0378793</v>
       </c>
       <c r="N43">
-        <v>510.8191101000002</v>
+        <v>517.2621207000002</v>
       </c>
       <c r="O43">
-        <v>153.2457330300001</v>
+        <v>155.1786362100001</v>
       </c>
       <c r="P43">
-        <v>357.5733770700002</v>
+        <v>362.0834844900002</v>
       </c>
       <c r="Q43">
-        <v>915.2733770700002</v>
+        <v>919.7834844900002</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.07828676839832541</v>
+        <v>0.07826588229466111</v>
       </c>
       <c r="T43">
         <v>0.7497894294379008</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.560189168439219</v>
+        <v>4.774592275816108</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06345262712916816</v>
+        <v>0.06191154648125992</v>
       </c>
       <c r="C44">
-        <v>2458.878843257107</v>
+        <v>2848.677600893452</v>
       </c>
       <c r="D44">
-        <v>4111.800843257107</v>
+        <v>4501.599600893452</v>
       </c>
       <c r="E44">
         <v>-1943.978</v>
@@ -4895,45 +4895,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M44">
-        <v>153.580581</v>
+        <v>140.3802666</v>
       </c>
       <c r="N44">
-        <v>500.7194190000002</v>
+        <v>513.9197334000002</v>
       </c>
       <c r="O44">
-        <v>150.2158257</v>
+        <v>154.17592002</v>
       </c>
       <c r="P44">
-        <v>350.5035933000001</v>
+        <v>359.7438133800001</v>
       </c>
       <c r="Q44">
-        <v>908.2035933000002</v>
+        <v>917.4438133800002</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.07873383987787613</v>
+        <v>0.07871266634699985</v>
       </c>
       <c r="T44">
         <v>0.7601077678290958</v>
       </c>
       <c r="U44">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.04235</v>
+        <v>0.03871</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.260304237291564</v>
+        <v>4.660911507344297</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06335256090332433</v>
+        <v>0.06177512240866979</v>
       </c>
       <c r="C45">
-        <v>2421.879003442928</v>
+        <v>2826.679282896984</v>
       </c>
       <c r="D45">
-        <v>4135.242003442928</v>
+        <v>4540.042282896984</v>
       </c>
       <c r="E45">
         <v>-1883.537</v>
@@ -4977,45 +4977,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M45">
-        <v>157.2372615</v>
+        <v>143.7226539</v>
       </c>
       <c r="N45">
-        <v>497.0627385000001</v>
+        <v>510.5773461000002</v>
       </c>
       <c r="O45">
-        <v>149.11882155</v>
+        <v>153.17320383</v>
       </c>
       <c r="P45">
-        <v>347.9439169500001</v>
+        <v>357.4041422700001</v>
       </c>
       <c r="Q45">
-        <v>905.6439169500002</v>
+        <v>915.1041422700002</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.0791965980760076</v>
+        <v>0.07917512703275401</v>
       </c>
       <c r="T45">
         <v>0.7707881531813856</v>
       </c>
       <c r="U45">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.04235</v>
+        <v>0.03871</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.161227394563852</v>
+        <v>4.552518216475824</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06325249467748051</v>
+        <v>0.06240869833607965</v>
       </c>
       <c r="C46">
-        <v>2385.147969718944</v>
+        <v>2593.048220577784</v>
       </c>
       <c r="D46">
-        <v>4158.951969718943</v>
+        <v>4366.852220577784</v>
       </c>
       <c r="E46">
         <v>-1823.096</v>
@@ -5059,37 +5059,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M46">
-        <v>160.893942</v>
+        <v>153.7135512</v>
       </c>
       <c r="N46">
-        <v>493.4060580000002</v>
+        <v>500.5864488000002</v>
       </c>
       <c r="O46">
-        <v>148.0218174000001</v>
+        <v>150.1759346400001</v>
       </c>
       <c r="P46">
-        <v>345.3842406000001</v>
+        <v>350.4105141600002</v>
       </c>
       <c r="Q46">
-        <v>903.0842406000002</v>
+        <v>908.1105141600002</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.07967588335264375</v>
+        <v>0.07965410417157079</v>
       </c>
       <c r="T46">
         <v>0.7818499808676856</v>
       </c>
       <c r="U46">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.066654044687402</v>
+        <v>4.256618853003249</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06400292845163669</v>
+        <v>0.06228977426348951</v>
       </c>
       <c r="C47">
-        <v>2153.250051044418</v>
+        <v>2564.100911284045</v>
       </c>
       <c r="D47">
-        <v>3987.495051044418</v>
+        <v>4398.345911284045</v>
       </c>
       <c r="E47">
         <v>-1762.655</v>
@@ -5141,45 +5141,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M47">
-        <v>171.894204</v>
+        <v>157.207041</v>
       </c>
       <c r="N47">
-        <v>482.4057960000001</v>
+        <v>497.0929590000002</v>
       </c>
       <c r="O47">
-        <v>144.7217388</v>
+        <v>149.1278877000001</v>
       </c>
       <c r="P47">
-        <v>337.6840572000001</v>
+        <v>347.9650713000001</v>
       </c>
       <c r="Q47">
-        <v>895.3840572000001</v>
+        <v>905.6650713000001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08017259718479397</v>
+        <v>0.08015049866089001</v>
       </c>
       <c r="T47">
         <v>0.7933140568334875</v>
       </c>
       <c r="U47">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.04424</v>
+        <v>0.04046</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.806411064331174</v>
+        <v>4.16202732293651</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06392176222579285</v>
+        <v>0.06217085019089937</v>
       </c>
       <c r="C48">
-        <v>2110.66878895686</v>
+        <v>2535.611166248241</v>
       </c>
       <c r="D48">
-        <v>4005.35478895686</v>
+        <v>4430.297166248241</v>
       </c>
       <c r="E48">
         <v>-1702.213999999999</v>
@@ -5223,45 +5223,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M48">
-        <v>175.7140752000001</v>
+        <v>160.7005308000001</v>
       </c>
       <c r="N48">
-        <v>478.5859248000002</v>
+        <v>493.5994692000002</v>
       </c>
       <c r="O48">
-        <v>143.5757774400001</v>
+        <v>148.0798407600001</v>
       </c>
       <c r="P48">
-        <v>335.0101473600001</v>
+        <v>345.5196284400001</v>
       </c>
       <c r="Q48">
-        <v>892.7101473600002</v>
+        <v>903.2196284400002</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08068770782554231</v>
+        <v>0.08066527813129512</v>
       </c>
       <c r="T48">
         <v>0.80520272820543</v>
       </c>
       <c r="U48">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.04424</v>
+        <v>0.04046</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.723662997715279</v>
+        <v>4.071548468090063</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06384059599994903</v>
+        <v>0.06320342611830923</v>
       </c>
       <c r="C49">
-        <v>2068.248231928148</v>
+        <v>2212.31283148889</v>
       </c>
       <c r="D49">
-        <v>4023.375231928148</v>
+        <v>4167.439831488889</v>
       </c>
       <c r="E49">
         <v>-1641.773</v>
@@ -5305,37 +5305,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M49">
-        <v>179.5339464</v>
+        <v>174.1365651</v>
       </c>
       <c r="N49">
-        <v>474.7660536000001</v>
+        <v>480.1634349000002</v>
       </c>
       <c r="O49">
-        <v>142.42981608</v>
+        <v>144.04903047</v>
       </c>
       <c r="P49">
-        <v>332.3362375200001</v>
+        <v>336.1144044300001</v>
       </c>
       <c r="Q49">
-        <v>890.0362375200002</v>
+        <v>893.8144044300002</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08122225660367741</v>
+        <v>0.08119948324209289</v>
       </c>
       <c r="T49">
         <v>0.817540028685748</v>
       </c>
       <c r="U49">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.04424</v>
+        <v>0.04291</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.644436125423465</v>
+        <v>3.757395809571991</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06375942977410519</v>
+        <v>0.06310900204571909</v>
       </c>
       <c r="C50">
-        <v>2025.990558839786</v>
+        <v>2174.606050372459</v>
       </c>
       <c r="D50">
-        <v>4041.558558839787</v>
+        <v>4190.174050372459</v>
       </c>
       <c r="E50">
         <v>-1581.332</v>
@@ -5387,37 +5387,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M50">
-        <v>183.3538176</v>
+        <v>177.8415984</v>
       </c>
       <c r="N50">
-        <v>470.9461824000002</v>
+        <v>476.4584016000002</v>
       </c>
       <c r="O50">
-        <v>141.2838547200001</v>
+        <v>142.93752048</v>
       </c>
       <c r="P50">
-        <v>329.6623276800001</v>
+        <v>333.5208811200001</v>
       </c>
       <c r="Q50">
-        <v>887.3623276800001</v>
+        <v>891.2208811200002</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.0817773649502023</v>
+        <v>0.08175423470330595</v>
       </c>
       <c r="T50">
         <v>0.8303518407230012</v>
       </c>
       <c r="U50">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.04424</v>
+        <v>0.04291</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.568510372810477</v>
+        <v>3.679116730205907</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06529036354826137</v>
+        <v>0.06301457797312895</v>
       </c>
       <c r="C51">
-        <v>1648.092242939194</v>
+        <v>2137.148669216631</v>
       </c>
       <c r="D51">
-        <v>3724.101242939194</v>
+        <v>4213.157669216631</v>
       </c>
       <c r="E51">
         <v>-1520.891</v>
@@ -5469,45 +5469,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M51">
-        <v>201.0932511</v>
+        <v>181.5466317</v>
       </c>
       <c r="N51">
-        <v>453.2067489000002</v>
+        <v>472.7533683000001</v>
       </c>
       <c r="O51">
-        <v>135.9620246700001</v>
+        <v>141.82601049</v>
       </c>
       <c r="P51">
-        <v>317.2447242300001</v>
+        <v>330.9273578100001</v>
       </c>
       <c r="Q51">
-        <v>874.9447242300002</v>
+        <v>888.6273578100001</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08235424225149288</v>
+        <v>0.08233074112378226</v>
       </c>
       <c r="T51">
         <v>0.8436660767617151</v>
       </c>
       <c r="U51">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.04753</v>
+        <v>0.04291</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.253714365951689</v>
+        <v>3.604032715303746</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06524209732241754</v>
+        <v>0.06292015390053882</v>
       </c>
       <c r="C52">
-        <v>1596.896557818353</v>
+        <v>2099.944814624494</v>
       </c>
       <c r="D52">
-        <v>3733.346557818353</v>
+        <v>4236.394814624494</v>
       </c>
       <c r="E52">
         <v>-1460.45</v>
@@ -5551,45 +5551,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M52">
-        <v>205.197195</v>
+        <v>185.251665</v>
       </c>
       <c r="N52">
-        <v>449.1028050000002</v>
+        <v>469.0483350000002</v>
       </c>
       <c r="O52">
-        <v>134.7308415000001</v>
+        <v>140.7145005</v>
       </c>
       <c r="P52">
-        <v>314.3719635000001</v>
+        <v>328.3338345000001</v>
       </c>
       <c r="Q52">
-        <v>872.0719635000002</v>
+        <v>886.0338345000002</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08295419464483508</v>
+        <v>0.08293030780107764</v>
       </c>
       <c r="T52">
         <v>0.8575128822419779</v>
       </c>
       <c r="U52">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.04753</v>
+        <v>0.04291</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.188640078632655</v>
+        <v>3.531952060997671</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06519383109657372</v>
+        <v>0.06382532982794868</v>
       </c>
       <c r="C53">
-        <v>1545.746891089</v>
+        <v>1826.765260500712</v>
       </c>
       <c r="D53">
-        <v>3742.637891089</v>
+        <v>4023.656260500713</v>
       </c>
       <c r="E53">
         <v>-1400.009</v>
@@ -5633,37 +5633,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M53">
-        <v>209.3011389</v>
+        <v>197.5876731</v>
       </c>
       <c r="N53">
-        <v>444.9988611000001</v>
+        <v>456.7123269000001</v>
       </c>
       <c r="O53">
-        <v>133.49965833</v>
+        <v>137.01369807</v>
       </c>
       <c r="P53">
-        <v>311.4992027700001</v>
+        <v>319.6986288300001</v>
       </c>
       <c r="Q53">
-        <v>869.1992027700002</v>
+        <v>877.3986288300001</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08357863489096677</v>
+        <v>0.08355434658765037</v>
       </c>
       <c r="T53">
         <v>0.8719248634561287</v>
       </c>
       <c r="U53">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.04753</v>
+        <v>0.04487</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.126117724149661</v>
+        <v>3.311441395784118</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06514556487072989</v>
+        <v>0.06375050575535855</v>
       </c>
       <c r="C54">
-        <v>1494.643587191959</v>
+        <v>1783.09628643784</v>
       </c>
       <c r="D54">
-        <v>3751.975587191959</v>
+        <v>4040.428286437841</v>
       </c>
       <c r="E54">
         <v>-1339.568</v>
@@ -5715,37 +5715,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M54">
-        <v>213.4050828</v>
+        <v>201.4619412</v>
       </c>
       <c r="N54">
-        <v>440.8949172000001</v>
+        <v>452.8380588000001</v>
       </c>
       <c r="O54">
-        <v>132.26847516</v>
+        <v>135.85141764</v>
       </c>
       <c r="P54">
-        <v>308.6264420400001</v>
+        <v>316.9866411600001</v>
       </c>
       <c r="Q54">
-        <v>866.3264420400001</v>
+        <v>874.6866411600001</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08422909348068727</v>
+        <v>0.08420438699033031</v>
       </c>
       <c r="T54">
         <v>0.8869373438875359</v>
       </c>
       <c r="U54">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.3</v>
       </c>
       <c r="W54">
-        <v>0.04753</v>
+        <v>0.04487</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.066000075608321</v>
+        <v>3.247759830480577</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06509729864488606</v>
+        <v>0.06367568168276841</v>
       </c>
       <c r="C55">
-        <v>1443.5869940141</v>
+        <v>1739.567721150253</v>
       </c>
       <c r="D55">
-        <v>3761.3599940141</v>
+        <v>4057.340721150253</v>
       </c>
       <c r="E55">
         <v>-1279.126999999999</v>
@@ -5797,37 +5797,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M55">
-        <v>217.5090267</v>
+        <v>205.3362093</v>
       </c>
       <c r="N55">
-        <v>436.7909733000001</v>
+        <v>448.9637907000001</v>
       </c>
       <c r="O55">
-        <v>131.03729199</v>
+        <v>134.68913721</v>
       </c>
       <c r="P55">
-        <v>305.7536813100001</v>
+        <v>314.2746534900001</v>
       </c>
       <c r="Q55">
-        <v>863.4536813100001</v>
+        <v>871.9746534900002</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08490723115933205</v>
+        <v>0.0848820886867413</v>
       </c>
       <c r="T55">
         <v>0.902588653273471</v>
       </c>
       <c r="U55">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.04753</v>
+        <v>0.04487</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.008151017577975</v>
+        <v>3.186481343113019</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.06856443241904224</v>
+        <v>0.06360085761017828</v>
       </c>
       <c r="C56">
-        <v>810.2725732343492</v>
+        <v>1696.181335219445</v>
       </c>
       <c r="D56">
-        <v>3188.48657323435</v>
+        <v>4074.395335219445</v>
       </c>
       <c r="E56">
         <v>-1218.686</v>
@@ -5879,45 +5879,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M56">
-        <v>251.9664408</v>
+        <v>209.2104774</v>
       </c>
       <c r="N56">
-        <v>402.3335592000002</v>
+        <v>445.0895226000001</v>
       </c>
       <c r="O56">
-        <v>120.7000677600001</v>
+        <v>133.52685678</v>
       </c>
       <c r="P56">
-        <v>281.6334914400002</v>
+        <v>311.5626658200001</v>
       </c>
       <c r="Q56">
-        <v>839.3334914400002</v>
+        <v>869.2626658200002</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.08561485308487443</v>
+        <v>0.08558925567430059</v>
       </c>
       <c r="T56">
         <v>0.9189204543718381</v>
       </c>
       <c r="U56">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.05403999999999999</v>
+        <v>0.04487</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.596774387583444</v>
+        <v>3.127472429351667</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0685812661931984</v>
+        <v>0.06352603353758814</v>
       </c>
       <c r="C57">
-        <v>747.4755030133788</v>
+        <v>1652.938929122415</v>
       </c>
       <c r="D57">
-        <v>3186.130503013379</v>
+        <v>4091.593929122415</v>
       </c>
       <c r="E57">
         <v>-1158.244999999999</v>
@@ -5961,45 +5961,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M57">
-        <v>256.632486</v>
+        <v>213.0847455000001</v>
       </c>
       <c r="N57">
-        <v>397.6675140000002</v>
+        <v>441.2152545000001</v>
       </c>
       <c r="O57">
-        <v>119.3002542</v>
+        <v>132.36457635</v>
       </c>
       <c r="P57">
-        <v>278.3672598000001</v>
+        <v>308.8506781500001</v>
       </c>
       <c r="Q57">
-        <v>836.0672598000001</v>
+        <v>866.5506781500002</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.08635392487377425</v>
+        <v>0.08632785230575141</v>
       </c>
       <c r="T57">
         <v>0.9359781132967994</v>
       </c>
       <c r="U57">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.05403999999999999</v>
+        <v>0.04487</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.5495603078092</v>
+        <v>3.070609294272546</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06859809996735458</v>
+        <v>0.06345120946499799</v>
       </c>
       <c r="C58">
-        <v>684.6819121660437</v>
+        <v>1609.842333865281</v>
       </c>
       <c r="D58">
-        <v>3183.777912166044</v>
+        <v>4108.938333865281</v>
       </c>
       <c r="E58">
         <v>-1097.804</v>
@@ -6043,45 +6043,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M58">
-        <v>261.2985312</v>
+        <v>216.9590136</v>
       </c>
       <c r="N58">
-        <v>393.0014688000002</v>
+        <v>437.3409864000001</v>
       </c>
       <c r="O58">
-        <v>117.90044064</v>
+        <v>131.20229592</v>
       </c>
       <c r="P58">
-        <v>275.1010281600001</v>
+        <v>306.1386904800001</v>
       </c>
       <c r="Q58">
-        <v>832.8010281600002</v>
+        <v>863.8386904800002</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.08712659083489679</v>
+        <v>0.08710002151135909</v>
       </c>
       <c r="T58">
         <v>0.9538111203547134</v>
       </c>
       <c r="U58">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.05403999999999999</v>
+        <v>0.04487</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.50403244516975</v>
+        <v>3.01577698544625</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07049023374151075</v>
+        <v>0.06648858539240786</v>
       </c>
       <c r="C59">
-        <v>380.2523869827578</v>
+        <v>946.1512737101793</v>
       </c>
       <c r="D59">
-        <v>2939.789386982759</v>
+        <v>3505.68827371018</v>
       </c>
       <c r="E59">
         <v>-1037.362999999999</v>
@@ -6125,45 +6125,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M59">
-        <v>282.1567203000001</v>
+        <v>247.7053503000001</v>
       </c>
       <c r="N59">
-        <v>372.1432797000001</v>
+        <v>406.5946497000001</v>
       </c>
       <c r="O59">
-        <v>111.64298391</v>
+        <v>121.97839491</v>
       </c>
       <c r="P59">
-        <v>260.5002957900001</v>
+        <v>284.6162547900001</v>
       </c>
       <c r="Q59">
-        <v>818.2002957900002</v>
+        <v>842.3162547900001</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.08793519474769945</v>
+        <v>0.08790810556373921</v>
       </c>
       <c r="T59">
         <v>0.9724735696013675</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.318924033793428</v>
+        <v>2.641444761720191</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07053996751566693</v>
+        <v>0.06646836131981772</v>
       </c>
       <c r="C60">
-        <v>313.9016451309817</v>
+        <v>889.1406034314791</v>
       </c>
       <c r="D60">
-        <v>2933.879645130982</v>
+        <v>3509.118603431479</v>
       </c>
       <c r="E60">
         <v>-976.922</v>
@@ -6207,45 +6207,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M60">
-        <v>287.1068382</v>
+        <v>252.0510582</v>
       </c>
       <c r="N60">
-        <v>367.1931618000002</v>
+        <v>402.2489418000001</v>
       </c>
       <c r="O60">
-        <v>110.15794854</v>
+        <v>120.67468254</v>
       </c>
       <c r="P60">
-        <v>257.0352132600001</v>
+        <v>281.5742592600001</v>
       </c>
       <c r="Q60">
-        <v>814.7352132600001</v>
+        <v>839.2742592600001</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.08878230360873079</v>
+        <v>0.0887546698090898</v>
       </c>
       <c r="T60">
         <v>0.992024706907386</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.278942584934921</v>
+        <v>2.59590261065605</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0705897012898231</v>
+        <v>0.06644813724722759</v>
       </c>
       <c r="C61">
-        <v>247.5746158494499</v>
+        <v>832.1366529102488</v>
       </c>
       <c r="D61">
-        <v>2927.99361584945</v>
+        <v>3512.555652910249</v>
       </c>
       <c r="E61">
         <v>-916.4809999999998</v>
@@ -6289,45 +6289,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M61">
-        <v>292.0569561</v>
+        <v>256.3967661</v>
       </c>
       <c r="N61">
-        <v>362.2430439000001</v>
+        <v>397.9032339000001</v>
       </c>
       <c r="O61">
-        <v>108.67291317</v>
+        <v>119.37097017</v>
       </c>
       <c r="P61">
-        <v>253.5701307300001</v>
+        <v>278.5322637300001</v>
       </c>
       <c r="Q61">
-        <v>811.2701307300001</v>
+        <v>836.2322637300001</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.08967073485322707</v>
+        <v>0.08964252987128679</v>
       </c>
       <c r="T61">
         <v>1.012529558228332</v>
       </c>
       <c r="U61">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.240316439427549</v>
+        <v>2.551904261322897</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07063943506397927</v>
+        <v>0.06642791317463745</v>
       </c>
       <c r="C62">
-        <v>181.2711567055017</v>
+        <v>775.139441911102</v>
       </c>
       <c r="D62">
-        <v>2922.131156705502</v>
+        <v>3515.999441911102</v>
       </c>
       <c r="E62">
         <v>-856.04</v>
@@ -6371,45 +6371,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M62">
-        <v>297.007074</v>
+        <v>260.742474</v>
       </c>
       <c r="N62">
-        <v>357.2929260000002</v>
+        <v>393.5575260000002</v>
       </c>
       <c r="O62">
-        <v>107.1878778000001</v>
+        <v>118.0672578</v>
       </c>
       <c r="P62">
-        <v>250.1050482000001</v>
+        <v>275.4902682000001</v>
       </c>
       <c r="Q62">
-        <v>807.8050482000002</v>
+        <v>833.1902682000002</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09060358765994819</v>
+        <v>0.09057478293659363</v>
       </c>
       <c r="T62">
         <v>1.034059652115326</v>
       </c>
       <c r="U62">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.05733</v>
+        <v>0.05033</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.202977832103757</v>
+        <v>2.509372523634182</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07068916883813545</v>
+        <v>0.06807298910204732</v>
       </c>
       <c r="C63">
-        <v>114.9911264049128</v>
+        <v>455.0078356716908</v>
       </c>
       <c r="D63">
-        <v>2916.292126404913</v>
+        <v>3256.308835671691</v>
       </c>
       <c r="E63">
         <v>-795.5989999999997</v>
@@ -6453,37 +6453,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M63">
-        <v>301.9571919</v>
+        <v>279.4670958</v>
       </c>
       <c r="N63">
-        <v>352.3428081000002</v>
+        <v>374.8329042000001</v>
       </c>
       <c r="O63">
-        <v>105.70284243</v>
+        <v>112.44987126</v>
       </c>
       <c r="P63">
-        <v>246.6399656700002</v>
+        <v>262.3830329400001</v>
       </c>
       <c r="Q63">
-        <v>804.3399656700002</v>
+        <v>820.0830329400002</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09158427907214217</v>
+        <v>0.09155484385140336</v>
       </c>
       <c r="T63">
         <v>1.05669385338114</v>
       </c>
       <c r="U63">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.166863441413532</v>
+        <v>2.341241633928341</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07073890261229163</v>
+        <v>0.06808006502945718</v>
       </c>
       <c r="C64">
-        <v>48.73438478055687</v>
+        <v>393.5326643209851</v>
       </c>
       <c r="D64">
-        <v>2910.476384780557</v>
+        <v>3255.274664320985</v>
       </c>
       <c r="E64">
         <v>-735.1579999999999</v>
@@ -6535,37 +6535,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M64">
-        <v>306.9073098</v>
+        <v>284.0485236</v>
       </c>
       <c r="N64">
-        <v>347.3926902000002</v>
+        <v>370.2514764000002</v>
       </c>
       <c r="O64">
-        <v>104.2178070600001</v>
+        <v>111.07544292</v>
       </c>
       <c r="P64">
-        <v>243.1748831400001</v>
+        <v>259.1760334800001</v>
       </c>
       <c r="Q64">
-        <v>800.8748831400002</v>
+        <v>816.8760334800002</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.09261658582182006</v>
+        <v>0.09258648691962415</v>
       </c>
       <c r="T64">
         <v>1.080519328397786</v>
       </c>
       <c r="U64">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.131914031068152</v>
+        <v>2.303479672090787</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07078863638644781</v>
+        <v>0.06808714095686705</v>
       </c>
       <c r="C65">
-        <v>-17.49920721882427</v>
+        <v>332.0581496468285</v>
       </c>
       <c r="D65">
-        <v>2904.683792781176</v>
+        <v>3254.241149646828</v>
       </c>
       <c r="E65">
         <v>-674.7169999999996</v>
@@ -6617,37 +6617,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M65">
-        <v>311.8574277</v>
+        <v>288.6299514</v>
       </c>
       <c r="N65">
-        <v>342.4425723000002</v>
+        <v>365.6700486000001</v>
       </c>
       <c r="O65">
-        <v>102.73277169</v>
+        <v>109.70101458</v>
       </c>
       <c r="P65">
-        <v>239.7098006100001</v>
+        <v>255.9690340200001</v>
       </c>
       <c r="Q65">
-        <v>797.4098006100002</v>
+        <v>813.6690340200001</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.0937046929363454</v>
+        <v>0.09367389447801902</v>
       </c>
       <c r="T65">
         <v>1.105632666928846</v>
       </c>
       <c r="U65">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.098074125813102</v>
+        <v>2.26691650269252</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07083837016060397</v>
+        <v>0.0680942168842769</v>
       </c>
       <c r="C66">
-        <v>-83.70978753969302</v>
+        <v>270.5842910239589</v>
       </c>
       <c r="D66">
-        <v>2898.914212460307</v>
+        <v>3253.208291023959</v>
       </c>
       <c r="E66">
         <v>-614.2759999999998</v>
@@ -6699,37 +6699,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M66">
-        <v>316.8075456</v>
+        <v>293.2113792</v>
       </c>
       <c r="N66">
-        <v>337.4924544000002</v>
+        <v>361.0886208000002</v>
       </c>
       <c r="O66">
-        <v>101.24773632</v>
+        <v>108.3265862400001</v>
       </c>
       <c r="P66">
-        <v>236.2447180800001</v>
+        <v>252.7620345600001</v>
       </c>
       <c r="Q66">
-        <v>793.9447180800001</v>
+        <v>810.4620345600001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.09485325044612214</v>
+        <v>0.09482171356743584</v>
       </c>
       <c r="T66">
         <v>1.132141190933853</v>
       </c>
       <c r="U66">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.065291717597272</v>
+        <v>2.23149593233795</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07088810393476014</v>
+        <v>0.06810129281168677</v>
       </c>
       <c r="C67">
-        <v>-149.8974930346767</v>
+        <v>209.1110878279001</v>
       </c>
       <c r="D67">
-        <v>2893.167506965324</v>
+        <v>3252.1760878279</v>
       </c>
       <c r="E67">
         <v>-553.8349999999996</v>
@@ -6781,37 +6781,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M67">
-        <v>321.7576635</v>
+        <v>297.792807</v>
       </c>
       <c r="N67">
-        <v>332.5423365000001</v>
+        <v>356.5071930000001</v>
       </c>
       <c r="O67">
-        <v>99.76270095000004</v>
+        <v>106.9521579</v>
       </c>
       <c r="P67">
-        <v>232.7796355500001</v>
+        <v>249.5550351000001</v>
       </c>
       <c r="Q67">
-        <v>790.4796355500001</v>
+        <v>807.2550351000002</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.09606743981360041</v>
+        <v>0.09603512231910503</v>
       </c>
       <c r="T67">
         <v>1.160164487739146</v>
       </c>
       <c r="U67">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.033517998865007</v>
+        <v>2.197165225686597</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07093783770891632</v>
+        <v>0.06810836873909663</v>
       </c>
       <c r="C68">
-        <v>-216.0624594733799</v>
+        <v>147.6385394349768</v>
       </c>
       <c r="D68">
-        <v>2887.44354052662</v>
+        <v>3251.144539434977</v>
       </c>
       <c r="E68">
         <v>-493.3939999999998</v>
@@ -6863,37 +6863,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M68">
-        <v>326.7077814</v>
+        <v>302.3742348000001</v>
       </c>
       <c r="N68">
-        <v>327.5922186000001</v>
+        <v>351.9257652000001</v>
       </c>
       <c r="O68">
-        <v>98.27766558000003</v>
+        <v>105.57772956</v>
       </c>
       <c r="P68">
-        <v>229.3145530200001</v>
+        <v>246.3480356400001</v>
       </c>
       <c r="Q68">
-        <v>787.0145530200002</v>
+        <v>804.0480356400001</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.09735305208504799</v>
+        <v>0.09731990805616655</v>
       </c>
       <c r="T68">
         <v>1.189836213768281</v>
       </c>
       <c r="U68">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.3</v>
       </c>
       <c r="W68">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.002707120094325</v>
+        <v>2.163874843479224</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07863227148307249</v>
+        <v>0.06811544466650649</v>
       </c>
       <c r="C69">
-        <v>-953.1926465328793</v>
+        <v>86.16664522230076</v>
       </c>
       <c r="D69">
-        <v>2210.754353467121</v>
+        <v>3250.113645222301</v>
       </c>
       <c r="E69">
         <v>-432.9529999999995</v>
@@ -6945,45 +6945,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M69">
-        <v>397.6655154000001</v>
+        <v>306.9556626</v>
       </c>
       <c r="N69">
-        <v>256.6344846000001</v>
+        <v>347.3443374000001</v>
       </c>
       <c r="O69">
-        <v>76.99034538000004</v>
+        <v>104.20330122</v>
       </c>
       <c r="P69">
-        <v>179.6441392200001</v>
+        <v>243.1410361800001</v>
       </c>
       <c r="Q69">
-        <v>737.3441392200001</v>
+        <v>800.8410361800002</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.09871658025173483</v>
+        <v>0.09868255959547423</v>
       </c>
       <c r="T69">
         <v>1.221306226223423</v>
       </c>
       <c r="U69">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.645352625916932</v>
+        <v>2.13157820402431</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07879610525722866</v>
+        <v>0.06812252059391635</v>
       </c>
       <c r="C70">
-        <v>-1024.610585375725</v>
+        <v>24.69540456777122</v>
       </c>
       <c r="D70">
-        <v>2199.777414624275</v>
+        <v>3249.083404567772</v>
       </c>
       <c r="E70">
         <v>-372.5119999999997</v>
@@ -7027,45 +7027,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M70">
-        <v>403.6008216000001</v>
+        <v>311.5370904000001</v>
       </c>
       <c r="N70">
-        <v>250.6991784000001</v>
+        <v>342.7629096000001</v>
       </c>
       <c r="O70">
-        <v>75.20975352000004</v>
+        <v>102.82887288</v>
       </c>
       <c r="P70">
-        <v>175.4894248800001</v>
+        <v>239.9340367200001</v>
       </c>
       <c r="Q70">
-        <v>733.1894248800002</v>
+        <v>797.6340367200002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1001653289288396</v>
+        <v>0.1001303768559886</v>
       </c>
       <c r="T70">
         <v>1.254743114457012</v>
       </c>
       <c r="U70">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.621156263771095</v>
+        <v>2.100231465729835</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07895993903138485</v>
+        <v>0.06812959652132622</v>
       </c>
       <c r="C71">
-        <v>-1095.920056388303</v>
+        <v>-36.77518314991903</v>
       </c>
       <c r="D71">
-        <v>2188.908943611698</v>
+        <v>3248.053816850082</v>
       </c>
       <c r="E71">
         <v>-312.070999999999</v>
@@ -7109,45 +7109,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M71">
-        <v>409.5361278000001</v>
+        <v>316.1185182000001</v>
       </c>
       <c r="N71">
-        <v>244.7638722</v>
+        <v>338.1814818000001</v>
       </c>
       <c r="O71">
-        <v>73.42916166000001</v>
+        <v>101.45444454</v>
       </c>
       <c r="P71">
-        <v>171.33471054</v>
+        <v>236.7270372600001</v>
       </c>
       <c r="Q71">
-        <v>729.0347105400001</v>
+        <v>794.4270372600001</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1017075452625318</v>
+        <v>0.1016716016816975</v>
       </c>
       <c r="T71">
         <v>1.290337221286316</v>
       </c>
       <c r="U71">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.597661245455571</v>
+        <v>2.069793328545344</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.079123772805541</v>
+        <v>0.06813667244873609</v>
       </c>
       <c r="C72">
-        <v>-1167.122659391923</v>
+        <v>-98.24511855129094</v>
       </c>
       <c r="D72">
-        <v>2178.147340608078</v>
+        <v>3247.024881448709</v>
       </c>
       <c r="E72">
         <v>-251.6299999999992</v>
@@ -7191,45 +7191,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M72">
-        <v>415.4714340000001</v>
+        <v>320.6999460000001</v>
       </c>
       <c r="N72">
-        <v>238.8285660000001</v>
+        <v>333.6000540000001</v>
       </c>
       <c r="O72">
-        <v>71.64856980000002</v>
+        <v>100.0800162</v>
       </c>
       <c r="P72">
-        <v>167.1799962000001</v>
+        <v>233.5200378000001</v>
       </c>
       <c r="Q72">
-        <v>724.8799962000001</v>
+        <v>791.2200378000001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.10335257601847</v>
+        <v>0.1033155748291203</v>
       </c>
       <c r="T72">
         <v>1.328304268570907</v>
       </c>
       <c r="U72">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.574837513377635</v>
+        <v>2.040224852423268</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07928760657969718</v>
+        <v>0.06814374837614595</v>
       </c>
       <c r="C73">
-        <v>-1238.219962900229</v>
+        <v>-159.7144022560824</v>
       </c>
       <c r="D73">
-        <v>2167.49103709977</v>
+        <v>3245.996597743917</v>
       </c>
       <c r="E73">
         <v>-191.1890000000003</v>
@@ -7273,45 +7273,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M73">
-        <v>421.4067402</v>
+        <v>325.2813738</v>
       </c>
       <c r="N73">
-        <v>232.8932598000002</v>
+        <v>329.0186262000002</v>
       </c>
       <c r="O73">
-        <v>69.86797794000005</v>
+        <v>98.70558786000005</v>
       </c>
       <c r="P73">
-        <v>163.0252818600001</v>
+        <v>230.3130383400002</v>
       </c>
       <c r="Q73">
-        <v>720.7252818600002</v>
+        <v>788.0130383400002</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1051110571713696</v>
+        <v>0.105072925434986</v>
       </c>
       <c r="T73">
         <v>1.368889732909607</v>
       </c>
       <c r="U73">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.06874</v>
+        <v>0.05306</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.552656703330063</v>
+        <v>2.011489291121532</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07945144035385336</v>
+        <v>0.07530762430355581</v>
       </c>
       <c r="C74">
-        <v>-1309.213504881307</v>
+        <v>-1008.220095225274</v>
       </c>
       <c r="D74">
-        <v>2156.938495118693</v>
+        <v>2457.931904774726</v>
       </c>
       <c r="E74">
         <v>-130.7479999999996</v>
@@ -7355,37 +7355,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M74">
-        <v>427.3420464000001</v>
+        <v>391.65768</v>
       </c>
       <c r="N74">
-        <v>226.9579536000001</v>
+        <v>262.6423200000002</v>
       </c>
       <c r="O74">
-        <v>68.08738608000003</v>
+        <v>78.79269600000005</v>
       </c>
       <c r="P74">
-        <v>158.8705675200001</v>
+        <v>183.8496240000001</v>
       </c>
       <c r="Q74">
-        <v>716.5705675200002</v>
+        <v>741.5496240000002</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1069951441209049</v>
+        <v>0.1069558010841279</v>
       </c>
       <c r="T74">
         <v>1.412374158986787</v>
       </c>
       <c r="U74">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.3</v>
       </c>
       <c r="W74">
-        <v>0.06874</v>
+        <v>0.063</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.531092026894923</v>
+        <v>1.670591522678682</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07961527412800953</v>
+        <v>0.07541410023096567</v>
       </c>
       <c r="C75">
-        <v>-1380.104793497638</v>
+        <v>-1077.498459083371</v>
       </c>
       <c r="D75">
-        <v>2146.488206502362</v>
+        <v>2449.09454091663</v>
       </c>
       <c r="E75">
         <v>-70.30699999999979</v>
@@ -7437,37 +7437,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M75">
-        <v>433.2773526000001</v>
+        <v>397.09737</v>
       </c>
       <c r="N75">
-        <v>221.0226474000001</v>
+        <v>257.2026300000002</v>
       </c>
       <c r="O75">
-        <v>66.30679422000003</v>
+        <v>77.16078900000005</v>
       </c>
       <c r="P75">
-        <v>154.7158531800001</v>
+        <v>180.0418410000001</v>
       </c>
       <c r="Q75">
-        <v>712.4158531800001</v>
+        <v>737.7418410000001</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.109018793066702</v>
+        <v>0.1089781490035766</v>
       </c>
       <c r="T75">
         <v>1.459079653662276</v>
       </c>
       <c r="U75">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.3</v>
       </c>
       <c r="W75">
-        <v>0.06874</v>
+        <v>0.063</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.5101181635128</v>
+        <v>1.647706707299522</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1180125838066119</v>
+        <v>0.07552057615837553</v>
       </c>
       <c r="C76">
-        <v>-2581.889421462277</v>
+        <v>-1146.713502061841</v>
       </c>
       <c r="D76">
-        <v>1005.144578537723</v>
+        <v>2440.320497938159</v>
       </c>
       <c r="E76">
         <v>-9.865999999999985</v>
@@ -7519,45 +7519,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M76">
-        <v>731.7229224</v>
+        <v>402.53706</v>
       </c>
       <c r="N76">
-        <v>-77.42292239999983</v>
+        <v>251.7629400000002</v>
       </c>
       <c r="O76">
-        <v>-23.22687671999995</v>
+        <v>75.52888200000005</v>
       </c>
       <c r="P76">
-        <v>-54.19604567999988</v>
+        <v>176.2340580000001</v>
       </c>
       <c r="Q76">
-        <v>503.5039543200002</v>
+        <v>733.9340580000002</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1131726269518672</v>
+        <v>0.1111560621475982</v>
       </c>
       <c r="T76">
-        <v>1.554949476740721</v>
+        <v>1.509377878697418</v>
       </c>
       <c r="U76">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
-        <v>0.268257278801903</v>
+        <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.1197131091880087</v>
+        <v>0.063</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8941909293396767</v>
+        <v>1.625440400444123</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1191905838066119</v>
+        <v>0.07562705208578539</v>
       </c>
       <c r="C77">
-        <v>-2658.464103088759</v>
+        <v>-1215.865902284967</v>
       </c>
       <c r="D77">
-        <v>989.0108969112418</v>
+        <v>2431.609097715034</v>
       </c>
       <c r="E77">
         <v>50.57500000000073</v>
@@ -7601,45 +7601,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M77">
-        <v>741.6110700000002</v>
+        <v>407.97675</v>
       </c>
       <c r="N77">
-        <v>-87.31106999999997</v>
+        <v>246.3232500000001</v>
       </c>
       <c r="O77">
-        <v>-26.19332099999999</v>
+        <v>73.89697500000004</v>
       </c>
       <c r="P77">
-        <v>-61.11774899999998</v>
+        <v>172.4262750000001</v>
       </c>
       <c r="Q77">
-        <v>496.582251</v>
+        <v>730.1262750000001</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1158675320299419</v>
+        <v>0.1135082083431416</v>
       </c>
       <c r="T77">
-        <v>1.61714745581035</v>
+        <v>1.563699961735371</v>
       </c>
       <c r="U77">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
-        <v>0.2646805150845443</v>
+        <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.1202982677321685</v>
+        <v>0.063</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8822683836151476</v>
+        <v>1.603767861771535</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1203685838066119</v>
+        <v>0.07573352801319526</v>
       </c>
       <c r="C78">
-        <v>-2734.529039833794</v>
+        <v>-1284.956328228455</v>
       </c>
       <c r="D78">
-        <v>973.3869601662062</v>
+        <v>2422.959671771545</v>
       </c>
       <c r="E78">
         <v>111.0160000000005</v>
@@ -7683,45 +7683,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M78">
-        <v>751.4992176000001</v>
+        <v>413.41644</v>
       </c>
       <c r="N78">
-        <v>-97.19921759999988</v>
+        <v>240.8835600000002</v>
       </c>
       <c r="O78">
-        <v>-29.15976527999996</v>
+        <v>72.26506800000004</v>
       </c>
       <c r="P78">
-        <v>-68.03945231999992</v>
+        <v>168.6184920000001</v>
       </c>
       <c r="Q78">
-        <v>489.6605476800001</v>
+        <v>726.3184920000001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1187870125311895</v>
+        <v>0.1160563667216469</v>
       </c>
       <c r="T78">
-        <v>1.684528599802448</v>
+        <v>1.622548885026488</v>
       </c>
       <c r="U78">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
-        <v>0.2611978767281687</v>
+        <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.1208680273672716</v>
+        <v>0.063</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.8706595890938957</v>
+        <v>1.582665653064015</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1215465838066119</v>
+        <v>0.07584000394060512</v>
       </c>
       <c r="C79">
-        <v>-2810.108014135095</v>
+        <v>-1353.985438890446</v>
       </c>
       <c r="D79">
-        <v>958.2489858649056</v>
+        <v>2414.371561109554</v>
       </c>
       <c r="E79">
         <v>171.4570000000003</v>
@@ -7765,45 +7765,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M79">
-        <v>761.3873652000001</v>
+        <v>418.85613</v>
       </c>
       <c r="N79">
-        <v>-107.0873651999999</v>
+        <v>235.4438700000002</v>
       </c>
       <c r="O79">
-        <v>-32.12620955999997</v>
+        <v>70.63316100000004</v>
       </c>
       <c r="P79">
-        <v>-74.96115563999993</v>
+        <v>164.8107090000001</v>
       </c>
       <c r="Q79">
-        <v>482.7388443600001</v>
+        <v>722.5107090000001</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1219603609021108</v>
+        <v>0.1188261040895875</v>
       </c>
       <c r="T79">
-        <v>1.757768973706902</v>
+        <v>1.686515105995092</v>
       </c>
       <c r="U79">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
-        <v>0.2578056965109197</v>
+        <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.1214229880508135</v>
+        <v>0.063</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8593523217030659</v>
+        <v>1.562111553673573</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1227245838066119</v>
+        <v>0.07594647986801498</v>
       </c>
       <c r="C80">
-        <v>-2885.223351641901</v>
+        <v>-1422.953883958879</v>
       </c>
       <c r="D80">
-        <v>943.5746483580988</v>
+        <v>2405.844116041121</v>
       </c>
       <c r="E80">
         <v>231.8980000000001</v>
@@ -7847,45 +7847,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M80">
-        <v>771.2755128</v>
+        <v>424.29582</v>
       </c>
       <c r="N80">
-        <v>-116.9755127999998</v>
+        <v>230.0041800000002</v>
       </c>
       <c r="O80">
-        <v>-35.09265383999995</v>
+        <v>69.00125400000006</v>
       </c>
       <c r="P80">
-        <v>-81.88285895999988</v>
+        <v>161.0029260000001</v>
       </c>
       <c r="Q80">
-        <v>475.8171410400001</v>
+        <v>718.7029260000002</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1254221954885704</v>
+        <v>0.1218476357637045</v>
       </c>
       <c r="T80">
-        <v>1.837667563420852</v>
+        <v>1.756296437960842</v>
       </c>
       <c r="U80">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
-        <v>0.2545004952736003</v>
+        <v>0.3</v>
       </c>
       <c r="W80">
-        <v>0.121963718973239</v>
+        <v>0.063</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8483349842453344</v>
+        <v>1.54208448247263</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1239025838066119</v>
+        <v>0.07605295579542484</v>
       </c>
       <c r="C81">
-        <v>-2959.89603107671</v>
+        <v>-1491.862303975332</v>
       </c>
       <c r="D81">
-        <v>929.3429689232913</v>
+        <v>2397.376696024668</v>
       </c>
       <c r="E81">
         <v>292.3390000000009</v>
@@ -7929,45 +7929,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M81">
-        <v>781.1636604000001</v>
+        <v>429.73551</v>
       </c>
       <c r="N81">
-        <v>-126.8636604</v>
+        <v>224.5644900000001</v>
       </c>
       <c r="O81">
-        <v>-38.05909811999999</v>
+        <v>67.36934700000005</v>
       </c>
       <c r="P81">
-        <v>-88.80456227999997</v>
+        <v>157.1951430000001</v>
       </c>
       <c r="Q81">
-        <v>468.8954377200001</v>
+        <v>714.8951430000002</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1292137286070737</v>
+        <v>0.1251569323591659</v>
       </c>
       <c r="T81">
-        <v>1.925175542631369</v>
+        <v>1.832723611066188</v>
       </c>
       <c r="U81">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V81">
-        <v>0.2512789700169724</v>
+        <v>0.3</v>
       </c>
       <c r="W81">
-        <v>0.1224907605052233</v>
+        <v>0.063</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8375965667232413</v>
+        <v>1.52256442573247</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1250805838066119</v>
+        <v>0.07615943172283471</v>
       </c>
       <c r="C82">
-        <v>-3034.14578430262</v>
+        <v>-1560.711330495408</v>
       </c>
       <c r="D82">
-        <v>915.5342156973809</v>
+        <v>2388.968669504593</v>
       </c>
       <c r="E82">
         <v>352.7800000000007</v>
@@ -8011,45 +8011,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M82">
-        <v>791.0518080000001</v>
+        <v>435.1752</v>
       </c>
       <c r="N82">
-        <v>-136.7518079999999</v>
+        <v>219.1248000000002</v>
       </c>
       <c r="O82">
-        <v>-41.02554239999996</v>
+        <v>65.73744000000005</v>
       </c>
       <c r="P82">
-        <v>-95.72626559999992</v>
+        <v>153.3873600000001</v>
       </c>
       <c r="Q82">
-        <v>461.9737344000001</v>
+        <v>711.0873600000002</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1333844150374274</v>
+        <v>0.1287971586141735</v>
       </c>
       <c r="T82">
-        <v>2.021434319762938</v>
+        <v>1.916793501482068</v>
       </c>
       <c r="U82">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
-        <v>0.2481379828917603</v>
+        <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.123004625998908</v>
+        <v>0.063</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8271266096392009</v>
+        <v>1.503532370410814</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1262585838066119</v>
+        <v>0.1121431342004322</v>
       </c>
       <c r="C83">
-        <v>-3107.991187600144</v>
+        <v>-2916.899642825358</v>
       </c>
       <c r="D83">
-        <v>902.1298123998562</v>
+        <v>1093.221357174642</v>
       </c>
       <c r="E83">
         <v>413.2210000000005</v>
@@ -8093,37 +8093,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M83">
-        <v>800.9399556000001</v>
+        <v>718.6918428000001</v>
       </c>
       <c r="N83">
-        <v>-146.6399555999999</v>
+        <v>-64.39184279999995</v>
       </c>
       <c r="O83">
-        <v>-43.99198667999997</v>
+        <v>-19.31755283999998</v>
       </c>
       <c r="P83">
-        <v>-102.6479689199999</v>
+        <v>-45.07428995999997</v>
       </c>
       <c r="Q83">
-        <v>455.0520310800001</v>
+        <v>512.6257100400001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1379941210920289</v>
+        <v>0.1353233336910831</v>
       </c>
       <c r="T83">
-        <v>2.127825599750461</v>
+        <v>2.067513480163581</v>
       </c>
       <c r="U83">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2450745510042077</v>
+        <v>0.2731212298657246</v>
       </c>
       <c r="W83">
-        <v>0.1235058034557116</v>
+        <v>0.1067058034557116</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8169151700140256</v>
+        <v>0.9104040995524154</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1274365838066119</v>
+        <v>0.1131531342004322</v>
       </c>
       <c r="C84">
-        <v>-3181.449745041358</v>
+        <v>-2993.734142309147</v>
       </c>
       <c r="D84">
-        <v>889.1122549586424</v>
+        <v>1076.827857690854</v>
       </c>
       <c r="E84">
         <v>473.6620000000003</v>
@@ -8175,37 +8175,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M84">
-        <v>810.8281032</v>
+        <v>727.5645816000001</v>
       </c>
       <c r="N84">
-        <v>-156.5281031999998</v>
+        <v>-73.26458159999993</v>
       </c>
       <c r="O84">
-        <v>-46.95843095999994</v>
+        <v>-21.97937447999998</v>
       </c>
       <c r="P84">
-        <v>-109.5696722399999</v>
+        <v>-51.28520711999995</v>
       </c>
       <c r="Q84">
-        <v>448.1303277600002</v>
+        <v>506.4147928800001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1431160167082527</v>
+        <v>0.1402968522294766</v>
       </c>
       <c r="T84">
-        <v>2.246038133069931</v>
+        <v>2.182375340172669</v>
       </c>
       <c r="U84">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.242085836967571</v>
+        <v>0.2697904831600451</v>
       </c>
       <c r="W84">
-        <v>0.1239947570721054</v>
+        <v>0.1071947570721054</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8069527898919034</v>
+        <v>0.8993016105334835</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1729900325401237</v>
+        <v>0.1141631342004322</v>
       </c>
       <c r="C85">
-        <v>-3560.328665967424</v>
+        <v>-3070.084245204856</v>
       </c>
       <c r="D85">
-        <v>570.6743340325773</v>
+        <v>1060.918754795145</v>
       </c>
       <c r="E85">
         <v>534.103000000001</v>
@@ -8257,45 +8257,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M85">
-        <v>1082.5829274</v>
+        <v>736.4373204000002</v>
       </c>
       <c r="N85">
-        <v>-428.2829274000001</v>
+        <v>-82.13732040000002</v>
       </c>
       <c r="O85">
-        <v>-128.48487822</v>
+        <v>-24.64119612000001</v>
       </c>
       <c r="P85">
-        <v>-299.79804918</v>
+        <v>-57.49612428000002</v>
       </c>
       <c r="Q85">
-        <v>257.90195082</v>
+        <v>500.20387572</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1550137161235133</v>
+        <v>0.1458554905959164</v>
       </c>
       <c r="T85">
-        <v>2.520635136588808</v>
+        <v>2.310750360182826</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1813163638848643</v>
+        <v>0.2665399954111288</v>
       </c>
       <c r="W85">
-        <v>0.1766719286736463</v>
+        <v>0.1076719286736463</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.6043878796162143</v>
+        <v>0.8884666513704294</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1746900325401237</v>
+        <v>0.1151731342004322</v>
       </c>
       <c r="C86">
-        <v>-3628.296596861427</v>
+        <v>-3145.971108429763</v>
       </c>
       <c r="D86">
-        <v>563.1474031385733</v>
+        <v>1045.472891570237</v>
       </c>
       <c r="E86">
         <v>594.5439999999999</v>
@@ -8339,45 +8339,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M86">
-        <v>1095.6260952</v>
+        <v>745.3100592000001</v>
       </c>
       <c r="N86">
-        <v>-441.3260951999998</v>
+        <v>-91.01005919999989</v>
       </c>
       <c r="O86">
-        <v>-132.3978285599999</v>
+        <v>-27.30301775999996</v>
       </c>
       <c r="P86">
-        <v>-308.9282666399999</v>
+        <v>-63.70704143999993</v>
       </c>
       <c r="Q86">
-        <v>248.7717333600002</v>
+        <v>493.9929585600001</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1618395733812328</v>
+        <v>0.1521089587581611</v>
       </c>
       <c r="T86">
-        <v>2.678174832625607</v>
+        <v>2.455172257694251</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1791578357433778</v>
+        <v>0.2633669002276631</v>
       </c>
       <c r="W86">
-        <v>0.1771377390465791</v>
+        <v>0.1081377390465791</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5971927858112595</v>
+        <v>0.8778896674255434</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1763900325401237</v>
+        <v>0.1161831342004322</v>
       </c>
       <c r="C87">
-        <v>-3696.068559008492</v>
+        <v>-3221.414674491669</v>
       </c>
       <c r="D87">
-        <v>555.8164409915088</v>
+        <v>1030.470325508331</v>
       </c>
       <c r="E87">
         <v>654.9850000000006</v>
@@ -8421,45 +8421,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M87">
-        <v>1108.669263</v>
+        <v>754.1827980000002</v>
       </c>
       <c r="N87">
-        <v>-454.369263</v>
+        <v>-99.88279799999998</v>
       </c>
       <c r="O87">
-        <v>-136.3107789</v>
+        <v>-29.96483939999999</v>
       </c>
       <c r="P87">
-        <v>-318.0584841</v>
+        <v>-69.91795859999999</v>
       </c>
       <c r="Q87">
-        <v>239.6415159</v>
+        <v>487.7820414</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1695755449399817</v>
+        <v>0.1591962226753718</v>
       </c>
       <c r="T87">
-        <v>2.856719821467315</v>
+        <v>2.618850408207202</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1770500964993381</v>
+        <v>0.2602684661073376</v>
       </c>
       <c r="W87">
-        <v>0.1775925891754429</v>
+        <v>0.1085925891754429</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5901669883311269</v>
+        <v>0.8675615536911252</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1780900325401237</v>
+        <v>0.1171931342004322</v>
       </c>
       <c r="C88">
-        <v>-3763.652107328592</v>
+        <v>-3296.43375739025</v>
       </c>
       <c r="D88">
-        <v>548.6738926714081</v>
+        <v>1015.89224260975</v>
       </c>
       <c r="E88">
         <v>715.4260000000004</v>
@@ -8503,45 +8503,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M88">
-        <v>1121.7124308</v>
+        <v>763.0555368000001</v>
       </c>
       <c r="N88">
-        <v>-467.4124308</v>
+        <v>-108.7555368</v>
       </c>
       <c r="O88">
-        <v>-140.22372924</v>
+        <v>-32.62666103999999</v>
       </c>
       <c r="P88">
-        <v>-327.18870156</v>
+        <v>-76.12887575999997</v>
       </c>
       <c r="Q88">
-        <v>230.51129844</v>
+        <v>481.5711242400001</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1784166552928375</v>
+        <v>0.1672959528664698</v>
       </c>
       <c r="T88">
-        <v>3.060771237286409</v>
+        <v>2.805911151650573</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1749913744470202</v>
+        <v>0.2572420885944616</v>
       </c>
       <c r="W88">
-        <v>0.1780368613943331</v>
+        <v>0.1090368613943331</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5833045814900673</v>
+        <v>0.8574736286482052</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1797900325401237</v>
+        <v>0.1182031342004322</v>
       </c>
       <c r="C89">
-        <v>-3831.054413329186</v>
+        <v>-3371.046121328659</v>
       </c>
       <c r="D89">
-        <v>541.7125866708137</v>
+        <v>1001.720878671341</v>
       </c>
       <c r="E89">
         <v>775.8670000000002</v>
@@ -8585,45 +8585,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M89">
-        <v>1134.7555986</v>
+        <v>771.9282756000001</v>
       </c>
       <c r="N89">
-        <v>-480.4555986</v>
+        <v>-117.6282755999999</v>
       </c>
       <c r="O89">
-        <v>-144.13667958</v>
+        <v>-35.28848267999998</v>
       </c>
       <c r="P89">
-        <v>-336.3189190200001</v>
+        <v>-82.33979291999995</v>
       </c>
       <c r="Q89">
-        <v>221.38108098</v>
+        <v>475.3602070800001</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.1886179364692097</v>
+        <v>0.1766417953946598</v>
       </c>
       <c r="T89">
-        <v>3.296215178616133</v>
+        <v>3.02175047100831</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1729799793384337</v>
+        <v>0.2542852829784332</v>
       </c>
       <c r="W89">
-        <v>0.178470920458766</v>
+        <v>0.109470920458766</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5765999311281125</v>
+        <v>0.8476176099281109</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1814900325401237</v>
+        <v>0.1192131342004322</v>
       </c>
       <c r="C90">
-        <v>-3898.282289123236</v>
+        <v>-3445.268552927749</v>
       </c>
       <c r="D90">
-        <v>534.925710876764</v>
+        <v>987.9394470722508</v>
       </c>
       <c r="E90">
         <v>836.308</v>
@@ -8667,45 +8667,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M90">
-        <v>1147.7987664</v>
+        <v>780.8010144000001</v>
       </c>
       <c r="N90">
-        <v>-493.4987664</v>
+        <v>-126.5010143999999</v>
       </c>
       <c r="O90">
-        <v>-148.04962992</v>
+        <v>-37.95030431999997</v>
       </c>
       <c r="P90">
-        <v>-345.44913648</v>
+        <v>-88.55071007999994</v>
       </c>
       <c r="Q90">
-        <v>212.2508635200001</v>
+        <v>469.1492899200001</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2005194311749771</v>
+        <v>0.1875452783442148</v>
       </c>
       <c r="T90">
-        <v>3.570899776834144</v>
+        <v>3.273563010259003</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1710142977550425</v>
+        <v>0.251395677490042</v>
       </c>
       <c r="W90">
-        <v>0.1788951145444619</v>
+        <v>0.1098951145444619</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.5700476591834749</v>
+        <v>0.8379855916334733</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1831900325401237</v>
+        <v>0.1202231342004322</v>
       </c>
       <c r="C91">
-        <v>-3965.342209664106</v>
+        <v>-3519.116927560155</v>
       </c>
       <c r="D91">
-        <v>528.3067903358951</v>
+        <v>974.5320724398454</v>
       </c>
       <c r="E91">
         <v>896.7490000000007</v>
@@ -8749,45 +8749,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M91">
-        <v>1160.8419342</v>
+        <v>789.6737532000002</v>
       </c>
       <c r="N91">
-        <v>-506.5419342</v>
+        <v>-135.3737532</v>
       </c>
       <c r="O91">
-        <v>-151.96258026</v>
+        <v>-40.61212596</v>
       </c>
       <c r="P91">
-        <v>-354.57935394</v>
+        <v>-94.76162724000001</v>
       </c>
       <c r="Q91">
-        <v>203.12064606</v>
+        <v>462.93837276</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.214584834009066</v>
+        <v>0.2004312127391434</v>
       </c>
       <c r="T91">
-        <v>3.895527029273611</v>
+        <v>3.571159647555276</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1690927887915027</v>
+        <v>0.248571006956446</v>
       </c>
       <c r="W91">
-        <v>0.1793097761787937</v>
+        <v>0.1103097761787937</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.5636426293050089</v>
+        <v>0.8285700231881532</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1848900325401237</v>
+        <v>0.1212331342004322</v>
       </c>
       <c r="C92">
-        <v>-4032.240333349887</v>
+        <v>-3592.606270355365</v>
       </c>
       <c r="D92">
-        <v>521.849666650113</v>
+        <v>961.4837296446357</v>
       </c>
       <c r="E92">
         <v>957.1900000000005</v>
@@ -8831,45 +8831,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M92">
-        <v>1173.885102</v>
+        <v>798.5464920000002</v>
       </c>
       <c r="N92">
-        <v>-519.585102</v>
+        <v>-144.246492</v>
       </c>
       <c r="O92">
-        <v>-155.8755306</v>
+        <v>-43.27394759999999</v>
       </c>
       <c r="P92">
-        <v>-363.7095714</v>
+        <v>-100.9725444</v>
       </c>
       <c r="Q92">
-        <v>193.9904286</v>
+        <v>456.7274556</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2314633174099726</v>
+        <v>0.2158943340130578</v>
       </c>
       <c r="T92">
-        <v>4.285079732200973</v>
+        <v>3.928275612310804</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1672139800271526</v>
+        <v>0.2458091068791521</v>
       </c>
       <c r="W92">
-        <v>0.1797152231101405</v>
+        <v>0.1107152231101405</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5573799334238421</v>
+        <v>0.8193636895971739</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1865900325401237</v>
+        <v>0.1222431342004322</v>
       </c>
       <c r="C93">
-        <v>-4098.982521134983</v>
+        <v>-3665.750812368632</v>
       </c>
       <c r="D93">
-        <v>515.5484788650162</v>
+        <v>948.7801876313683</v>
       </c>
       <c r="E93">
         <v>1017.631</v>
@@ -8913,45 +8913,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M93">
-        <v>1186.9282698</v>
+        <v>807.4192308000002</v>
       </c>
       <c r="N93">
-        <v>-532.6282698</v>
+        <v>-153.1192308</v>
       </c>
       <c r="O93">
-        <v>-159.78848094</v>
+        <v>-45.93576923999999</v>
       </c>
       <c r="P93">
-        <v>-372.83978886</v>
+        <v>-107.18346156</v>
       </c>
       <c r="Q93">
-        <v>184.86021114</v>
+        <v>450.5165384400001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2520925748999696</v>
+        <v>0.2347937044589531</v>
       </c>
       <c r="T93">
-        <v>4.761199702445526</v>
+        <v>4.364750680345338</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.165376463763118</v>
+        <v>0.2431079079024581</v>
       </c>
       <c r="W93">
-        <v>0.1801117591199192</v>
+        <v>0.1111117591199191</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.5512548792103933</v>
+        <v>0.8103596930081939</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1882900325401237</v>
+        <v>0.1232531342004322</v>
       </c>
       <c r="C94">
-        <v>-4165.574354273603</v>
+        <v>-3738.564042355193</v>
       </c>
       <c r="D94">
-        <v>509.3976457263981</v>
+        <v>936.4079576448078</v>
       </c>
       <c r="E94">
         <v>1078.072000000001</v>
@@ -8995,45 +8995,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M94">
-        <v>1199.9714376</v>
+        <v>816.2919696000002</v>
       </c>
       <c r="N94">
-        <v>-545.6714376000002</v>
+        <v>-161.9919696000001</v>
       </c>
       <c r="O94">
-        <v>-163.7014312800001</v>
+        <v>-48.59759088000002</v>
       </c>
       <c r="P94">
-        <v>-381.9700063200002</v>
+        <v>-113.39437872</v>
       </c>
       <c r="Q94">
-        <v>175.7299936799999</v>
+        <v>444.30562128</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.2778791467624658</v>
+        <v>0.2584179175163223</v>
       </c>
       <c r="T94">
-        <v>5.356349665251218</v>
+        <v>4.910344515388506</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1635788935048232</v>
+        <v>0.2404654306426488</v>
       </c>
       <c r="W94">
-        <v>0.1804996747816592</v>
+        <v>0.1114996747816592</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5452629783494106</v>
+        <v>0.801551435475496</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1899900325401237</v>
+        <v>0.1757825560278822</v>
       </c>
       <c r="C95">
-        <v>-4232.021150808075</v>
+        <v>-4177.432503030406</v>
       </c>
       <c r="D95">
-        <v>503.3918491919262</v>
+        <v>557.980496969595</v>
       </c>
       <c r="E95">
         <v>1138.513000000001</v>
@@ -9077,37 +9077,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M95">
-        <v>1213.0146054</v>
+        <v>1128.6994104</v>
       </c>
       <c r="N95">
-        <v>-558.7146054000002</v>
+        <v>-474.3994104000001</v>
       </c>
       <c r="O95">
-        <v>-167.61438162</v>
+        <v>-142.31982312</v>
       </c>
       <c r="P95">
-        <v>-391.1002237800002</v>
+        <v>-332.0795872800001</v>
       </c>
       <c r="Q95">
-        <v>166.5997762199999</v>
+        <v>225.62041272</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3110333105856752</v>
+        <v>0.3073550746965109</v>
       </c>
       <c r="T95">
-        <v>6.121542474572822</v>
+        <v>6.040532902921729</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.161819980671438</v>
+        <v>0.1739081266379299</v>
       </c>
       <c r="W95">
-        <v>0.1808792481711037</v>
+        <v>0.1658792481711037</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.53939993557146</v>
+        <v>0.5796937554597663</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1916900325401237</v>
+        <v>0.1773325560278822</v>
       </c>
       <c r="C96">
-        <v>-4298.32798090439</v>
+        <v>-4244.448831575831</v>
       </c>
       <c r="D96">
-        <v>497.5260190956111</v>
+        <v>551.4051684241697</v>
       </c>
       <c r="E96">
         <v>1198.954000000001</v>
@@ -9159,37 +9159,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M96">
-        <v>1226.0577732</v>
+        <v>1140.8359632</v>
       </c>
       <c r="N96">
-        <v>-571.7577732</v>
+        <v>-486.5359632</v>
       </c>
       <c r="O96">
-        <v>-171.52733196</v>
+        <v>-145.96078896</v>
       </c>
       <c r="P96">
-        <v>-400.23044124</v>
+        <v>-340.57517424</v>
       </c>
       <c r="Q96">
-        <v>157.46955876</v>
+        <v>217.12482576</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.3552388623499545</v>
+        <v>0.3509475871459294</v>
       </c>
       <c r="T96">
-        <v>7.141799553668293</v>
+        <v>7.047288386742019</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1600984915153589</v>
+        <v>0.1720580401843349</v>
       </c>
       <c r="W96">
-        <v>0.1812507455309856</v>
+        <v>0.1662507455309856</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5336616383845296</v>
+        <v>0.5735268006144497</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1933900325401237</v>
+        <v>0.1788825560278822</v>
       </c>
       <c r="C97">
-        <v>-4364.49968112788</v>
+        <v>-4311.311995656286</v>
       </c>
       <c r="D97">
-        <v>491.7953188721212</v>
+        <v>544.9830043437144</v>
       </c>
       <c r="E97">
         <v>1259.395</v>
@@ -9241,37 +9241,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M97">
-        <v>1239.100941</v>
+        <v>1152.972516</v>
       </c>
       <c r="N97">
-        <v>-584.800941</v>
+        <v>-498.6725159999999</v>
       </c>
       <c r="O97">
-        <v>-175.4402823</v>
+        <v>-149.6017548</v>
       </c>
       <c r="P97">
-        <v>-409.3606587</v>
+        <v>-349.0707611999999</v>
       </c>
       <c r="Q97">
-        <v>148.3393413000001</v>
+        <v>208.6292388000002</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4171266348199457</v>
+        <v>0.4119771045751155</v>
       </c>
       <c r="T97">
-        <v>8.570159464401957</v>
+        <v>8.456746064090428</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1584132442362498</v>
+        <v>0.1702469029192366</v>
       </c>
       <c r="W97">
-        <v>0.1816144218938173</v>
+        <v>0.1666144218938173</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5280441474541662</v>
+        <v>0.5674896763974555</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1950900325401237</v>
+        <v>0.1804325560278822</v>
       </c>
       <c r="C98">
-        <v>-4430.540867743539</v>
+        <v>-4378.027285335209</v>
       </c>
       <c r="D98">
-        <v>486.1951322564617</v>
+        <v>538.7087146647916</v>
       </c>
       <c r="E98">
         <v>1319.836</v>
@@ -9323,37 +9323,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M98">
-        <v>1252.1441088</v>
+        <v>1165.1090688</v>
       </c>
       <c r="N98">
-        <v>-597.8441088</v>
+        <v>-510.8090688</v>
       </c>
       <c r="O98">
-        <v>-179.35323264</v>
+        <v>-153.24272064</v>
       </c>
       <c r="P98">
-        <v>-418.49087616</v>
+        <v>-357.56634816</v>
       </c>
       <c r="Q98">
-        <v>139.2091238400001</v>
+        <v>200.1336518400001</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5099582935249311</v>
+        <v>0.5035213807188933</v>
       </c>
       <c r="T98">
-        <v>10.71269933050242</v>
+        <v>10.57093258011301</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1567631062754556</v>
+        <v>0.1684734976804946</v>
       </c>
       <c r="W98">
-        <v>0.1819705216657567</v>
+        <v>0.1669705216657567</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5225436875848519</v>
+        <v>0.5615783256016487</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1967900325401237</v>
+        <v>0.1819825560278822</v>
       </c>
       <c r="C99">
-        <v>-4496.45594911786</v>
+        <v>-4444.599749834667</v>
       </c>
       <c r="D99">
-        <v>480.7210508821406</v>
+        <v>532.5772501653333</v>
       </c>
       <c r="E99">
         <v>1380.277</v>
@@ -9405,37 +9405,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M99">
-        <v>1265.1872766</v>
+        <v>1177.2456216</v>
       </c>
       <c r="N99">
-        <v>-610.8872766</v>
+        <v>-522.9456215999999</v>
       </c>
       <c r="O99">
-        <v>-183.26618298</v>
+        <v>-156.88368648</v>
       </c>
       <c r="P99">
-        <v>-427.62109362</v>
+        <v>-366.0619351199999</v>
       </c>
       <c r="Q99">
-        <v>130.07890638</v>
+        <v>191.6380648800001</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.6646777246999079</v>
+        <v>0.6560951742918577</v>
       </c>
       <c r="T99">
-        <v>14.28359910733656</v>
+        <v>14.09457677348401</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1551469917777705</v>
+        <v>0.1667366574982214</v>
       </c>
       <c r="W99">
-        <v>0.1823192791743571</v>
+        <v>0.1673192791743572</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5171566392592349</v>
+        <v>0.5557888583274049</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1984900325401237</v>
+        <v>0.1835325560278822</v>
       </c>
       <c r="C100">
-        <v>-4562.249137292191</v>
+        <v>-4511.034211087133</v>
       </c>
       <c r="D100">
-        <v>475.3688627078085</v>
+        <v>526.583788912867</v>
       </c>
       <c r="E100">
         <v>1440.718</v>
@@ -9487,37 +9487,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M100">
-        <v>1278.2304444</v>
+        <v>1189.3821744</v>
       </c>
       <c r="N100">
-        <v>-623.9304443999999</v>
+        <v>-535.0821743999998</v>
       </c>
       <c r="O100">
-        <v>-187.17913332</v>
+        <v>-160.5246523199999</v>
       </c>
       <c r="P100">
-        <v>-436.7513110799999</v>
+        <v>-374.5575220799998</v>
       </c>
       <c r="Q100">
-        <v>120.9486889200001</v>
+        <v>183.1424779200002</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>0.9741165870498621</v>
+        <v>0.9612427614377866</v>
       </c>
       <c r="T100">
-        <v>21.42539866100485</v>
+        <v>21.14186516022602</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1535638592086095</v>
+        <v>0.1650352630339539</v>
       </c>
       <c r="W100">
-        <v>0.1826609191827821</v>
+        <v>0.1676609191827821</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5118795306953652</v>
+        <v>0.5501175434465131</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2001900325401237</v>
+        <v>0.1850825560278822</v>
       </c>
       <c r="C101">
-        <v>-4627.924458791497</v>
+        <v>-4577.3352763824</v>
       </c>
       <c r="D101">
-        <v>470.1345412085032</v>
+        <v>520.723723617601</v>
       </c>
       <c r="E101">
         <v>1501.159000000001</v>
@@ -9569,37 +9569,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M101">
-        <v>1291.2736122</v>
+        <v>1201.5187272</v>
       </c>
       <c r="N101">
-        <v>-636.9736122000002</v>
+        <v>-547.2187271999999</v>
       </c>
       <c r="O101">
-        <v>-191.09208366</v>
+        <v>-164.16561816</v>
       </c>
       <c r="P101">
-        <v>-445.8815285400001</v>
+        <v>-383.0531090399999</v>
       </c>
       <c r="Q101">
-        <v>111.81847146</v>
+        <v>174.6468909600001</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>1.902433174099724</v>
+        <v>1.876685522875573</v>
       </c>
       <c r="T101">
-        <v>42.85079732200969</v>
+        <v>42.28373032045204</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.1520127091155933</v>
+        <v>0.1633682401750251</v>
       </c>
       <c r="W101">
-        <v>0.182995657372855</v>
+        <v>0.167995657372855</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.506709030385311</v>
+        <v>0.5445608005834169</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/germany/germany_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_food_wholesalers.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06764135753004567</v>
+        <v>0.06746993345745553</v>
       </c>
       <c r="C2">
-        <v>4206.260408129141</v>
+        <v>4172.088115043628</v>
       </c>
       <c r="D2">
-        <v>3320.660408129141</v>
+        <v>3346.929115043628</v>
       </c>
       <c r="E2">
-        <v>-4482.5</v>
+        <v>-4422.059</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.441</v>
       </c>
       <c r="G2">
         <v>885.6</v>
@@ -1451,28 +1451,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.0401823</v>
       </c>
       <c r="N2">
-        <v>654.3000000000002</v>
+        <v>651.2598177000002</v>
       </c>
       <c r="O2">
-        <v>196.29</v>
+        <v>195.3779453100001</v>
       </c>
       <c r="P2">
-        <v>458.0100000000001</v>
+        <v>455.8818723900001</v>
       </c>
       <c r="Q2">
-        <v>1015.71</v>
+        <v>1013.58187239</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06764135753004567</v>
+        <v>0.0677957913711672</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5079859439068638</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>215.2173571959814</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06746993345745553</v>
+        <v>0.0672985093848654</v>
       </c>
       <c r="C3">
-        <v>4172.088115043628</v>
+        <v>4138.334742976343</v>
       </c>
       <c r="D3">
-        <v>3346.929115043628</v>
+        <v>3373.616742976343</v>
       </c>
       <c r="E3">
-        <v>-4422.059</v>
+        <v>-4361.618</v>
       </c>
       <c r="F3">
-        <v>60.441</v>
+        <v>120.882</v>
       </c>
       <c r="G3">
         <v>885.6</v>
@@ -1533,28 +1533,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M3">
-        <v>3.0401823</v>
+        <v>6.0803646</v>
       </c>
       <c r="N3">
-        <v>651.2598177000002</v>
+        <v>648.2196354000001</v>
       </c>
       <c r="O3">
-        <v>195.3779453100001</v>
+        <v>194.46589062</v>
       </c>
       <c r="P3">
-        <v>455.8818723900001</v>
+        <v>453.7537447800001</v>
       </c>
       <c r="Q3">
-        <v>1013.58187239</v>
+        <v>1011.45374478</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0677957913711672</v>
+        <v>0.06795337692333203</v>
       </c>
       <c r="T3">
-        <v>0.5079859439068638</v>
+        <v>0.5116253331023565</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>215.2173571959814</v>
+        <v>107.6086785979907</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0672985093848654</v>
+        <v>0.06712708531227525</v>
       </c>
       <c r="C4">
-        <v>4138.334742976343</v>
+        <v>4105.010393609632</v>
       </c>
       <c r="D4">
-        <v>3373.616742976343</v>
+        <v>3400.733393609632</v>
       </c>
       <c r="E4">
-        <v>-4361.618</v>
+        <v>-4301.177</v>
       </c>
       <c r="F4">
-        <v>120.882</v>
+        <v>181.323</v>
       </c>
       <c r="G4">
         <v>885.6</v>
@@ -1615,28 +1615,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M4">
-        <v>6.0803646</v>
+        <v>9.120546900000001</v>
       </c>
       <c r="N4">
-        <v>648.2196354000001</v>
+        <v>645.1794531000002</v>
       </c>
       <c r="O4">
-        <v>194.46589062</v>
+        <v>193.55383593</v>
       </c>
       <c r="P4">
-        <v>453.7537447800001</v>
+        <v>451.6256171700001</v>
       </c>
       <c r="Q4">
-        <v>1011.45374478</v>
+        <v>1009.32561717</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06795337692333203</v>
+        <v>0.06811421166213943</v>
       </c>
       <c r="T4">
-        <v>0.5116253331023565</v>
+        <v>0.5153397612503335</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>107.6086785979907</v>
+        <v>71.73911906532712</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06712708531227525</v>
+        <v>0.06695566123968512</v>
       </c>
       <c r="C5">
-        <v>4105.010393609632</v>
+        <v>4072.125496041082</v>
       </c>
       <c r="D5">
-        <v>3400.733393609632</v>
+        <v>3428.289496041082</v>
       </c>
       <c r="E5">
-        <v>-4301.177</v>
+        <v>-4240.736</v>
       </c>
       <c r="F5">
-        <v>181.323</v>
+        <v>241.764</v>
       </c>
       <c r="G5">
         <v>885.6</v>
@@ -1697,28 +1697,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M5">
-        <v>9.120546900000001</v>
+        <v>12.1607292</v>
       </c>
       <c r="N5">
-        <v>645.1794531000002</v>
+        <v>642.1392708000002</v>
       </c>
       <c r="O5">
-        <v>193.55383593</v>
+        <v>192.6417812400001</v>
       </c>
       <c r="P5">
-        <v>451.6256171700001</v>
+        <v>449.4974895600001</v>
       </c>
       <c r="Q5">
-        <v>1009.32561717</v>
+        <v>1007.19748956</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06811421166213943</v>
+        <v>0.068278397124672</v>
       </c>
       <c r="T5">
-        <v>0.5153397612503335</v>
+        <v>0.51913157331806</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>71.73911906532712</v>
+        <v>53.80433929899534</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06695566123968512</v>
+        <v>0.06678423716709497</v>
       </c>
       <c r="C6">
-        <v>4072.125496041082</v>
+        <v>4039.690820157116</v>
       </c>
       <c r="D6">
-        <v>3428.289496041082</v>
+        <v>3456.295820157115</v>
       </c>
       <c r="E6">
-        <v>-4240.736</v>
+        <v>-4180.295</v>
       </c>
       <c r="F6">
-        <v>241.764</v>
+        <v>302.205</v>
       </c>
       <c r="G6">
         <v>885.6</v>
@@ -1779,28 +1779,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M6">
-        <v>12.1607292</v>
+        <v>15.2009115</v>
       </c>
       <c r="N6">
-        <v>642.1392708000002</v>
+        <v>639.0990885000002</v>
       </c>
       <c r="O6">
-        <v>192.6417812400001</v>
+        <v>191.7297265500001</v>
       </c>
       <c r="P6">
-        <v>449.4974895600001</v>
+        <v>447.3693619500002</v>
       </c>
       <c r="Q6">
-        <v>1007.19748956</v>
+        <v>1005.06936195</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.068278397124672</v>
+        <v>0.06844603912325788</v>
       </c>
       <c r="T6">
-        <v>0.51913157331806</v>
+        <v>0.523003213008265</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.80433929899534</v>
+        <v>43.04347143919627</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06678423716709497</v>
+        <v>0.06661281309450484</v>
       </c>
       <c r="C7">
-        <v>4039.690820157116</v>
+        <v>4007.717490667452</v>
       </c>
       <c r="D7">
-        <v>3456.295820157115</v>
+        <v>3484.763490667453</v>
       </c>
       <c r="E7">
-        <v>-4180.295</v>
+        <v>-4119.854</v>
       </c>
       <c r="F7">
-        <v>302.205</v>
+        <v>362.6460000000001</v>
       </c>
       <c r="G7">
         <v>885.6</v>
@@ -1861,28 +1861,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M7">
-        <v>15.2009115</v>
+        <v>18.2410938</v>
       </c>
       <c r="N7">
-        <v>639.0990885000002</v>
+        <v>636.0589062000001</v>
       </c>
       <c r="O7">
-        <v>191.7297265500001</v>
+        <v>190.81767186</v>
       </c>
       <c r="P7">
-        <v>447.3693619500002</v>
+        <v>445.2412343400001</v>
       </c>
       <c r="Q7">
-        <v>1005.06936195</v>
+        <v>1002.94123434</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06844603912325788</v>
+        <v>0.06861724797287749</v>
       </c>
       <c r="T7">
-        <v>0.523003213008265</v>
+        <v>0.5269572280110276</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.04347143919627</v>
+        <v>35.86955953266356</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06661281309450484</v>
+        <v>0.06644138902191471</v>
       </c>
       <c r="C8">
-        <v>4007.717490667452</v>
+        <v>3976.217001838934</v>
       </c>
       <c r="D8">
-        <v>3484.763490667453</v>
+        <v>3513.704001838934</v>
       </c>
       <c r="E8">
-        <v>-4119.854</v>
+        <v>-4059.413</v>
       </c>
       <c r="F8">
-        <v>362.646</v>
+        <v>423.087</v>
       </c>
       <c r="G8">
         <v>885.6</v>
@@ -1943,28 +1943,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M8">
-        <v>18.2410938</v>
+        <v>21.2812761</v>
       </c>
       <c r="N8">
-        <v>636.0589062000001</v>
+        <v>633.0187239000002</v>
       </c>
       <c r="O8">
-        <v>190.81767186</v>
+        <v>189.9056171700001</v>
       </c>
       <c r="P8">
-        <v>445.2412343400001</v>
+        <v>443.1131067300001</v>
       </c>
       <c r="Q8">
-        <v>1002.94123434</v>
+        <v>1000.81310673</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06861724797287749</v>
+        <v>0.06879213873324162</v>
       </c>
       <c r="T8">
-        <v>0.5269572280110276</v>
+        <v>0.5309962755944948</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.86955953266356</v>
+        <v>30.74533674228305</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06644138902191471</v>
+        <v>0.06626996494932456</v>
       </c>
       <c r="C9">
-        <v>3976.217001838934</v>
+        <v>3945.201232969649</v>
       </c>
       <c r="D9">
-        <v>3513.704001838934</v>
+        <v>3543.129232969649</v>
       </c>
       <c r="E9">
-        <v>-4059.413</v>
+        <v>-3998.972</v>
       </c>
       <c r="F9">
-        <v>423.087</v>
+        <v>483.528</v>
       </c>
       <c r="G9">
         <v>885.6</v>
@@ -2025,28 +2025,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M9">
-        <v>21.2812761</v>
+        <v>24.3214584</v>
       </c>
       <c r="N9">
-        <v>633.0187239000002</v>
+        <v>629.9785416000002</v>
       </c>
       <c r="O9">
-        <v>189.9056171700001</v>
+        <v>188.9935624800001</v>
       </c>
       <c r="P9">
-        <v>443.1131067300001</v>
+        <v>440.9849791200002</v>
       </c>
       <c r="Q9">
-        <v>1000.81310673</v>
+        <v>998.6849791200002</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06879213873324162</v>
+        <v>0.06897083146665714</v>
       </c>
       <c r="T9">
-        <v>0.5309962755944948</v>
+        <v>0.5351231285602113</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.74533674228305</v>
+        <v>26.90216964949767</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06626996494932456</v>
+        <v>0.06609854087673443</v>
       </c>
       <c r="C10">
-        <v>3945.201232969649</v>
+        <v>3914.682464647147</v>
       </c>
       <c r="D10">
-        <v>3543.129232969649</v>
+        <v>3573.051464647147</v>
       </c>
       <c r="E10">
-        <v>-3998.972</v>
+        <v>-3938.531</v>
       </c>
       <c r="F10">
-        <v>483.528</v>
+        <v>543.9690000000001</v>
       </c>
       <c r="G10">
         <v>885.6</v>
@@ -2107,28 +2107,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M10">
-        <v>24.3214584</v>
+        <v>27.3616407</v>
       </c>
       <c r="N10">
-        <v>629.9785416000002</v>
+        <v>626.9383593000002</v>
       </c>
       <c r="O10">
-        <v>188.9935624800001</v>
+        <v>188.0815077900001</v>
       </c>
       <c r="P10">
-        <v>440.9849791200002</v>
+        <v>438.8568515100002</v>
       </c>
       <c r="Q10">
-        <v>998.6849791200002</v>
+        <v>996.5568515100002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06897083146665714</v>
+        <v>0.06915345151289498</v>
       </c>
       <c r="T10">
-        <v>0.5351231285602113</v>
+        <v>0.5393406815911083</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.90216964949767</v>
+        <v>23.91303968844237</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06609854087673443</v>
+        <v>0.0659271168041443</v>
       </c>
       <c r="C11">
-        <v>3914.682464647147</v>
+        <v>3884.673395837502</v>
       </c>
       <c r="D11">
-        <v>3573.051464647147</v>
+        <v>3603.483395837502</v>
       </c>
       <c r="E11">
-        <v>-3938.531</v>
+        <v>-3878.09</v>
       </c>
       <c r="F11">
-        <v>543.9690000000001</v>
+        <v>604.41</v>
       </c>
       <c r="G11">
         <v>885.6</v>
@@ -2189,28 +2189,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M11">
-        <v>27.3616407</v>
+        <v>30.401823</v>
       </c>
       <c r="N11">
-        <v>626.9383593000002</v>
+        <v>623.8981770000001</v>
       </c>
       <c r="O11">
-        <v>188.0815077900001</v>
+        <v>187.1694531</v>
       </c>
       <c r="P11">
-        <v>438.8568515100002</v>
+        <v>436.7287239000001</v>
       </c>
       <c r="Q11">
-        <v>996.5568515100002</v>
+        <v>994.4287239000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06915345151289498</v>
+        <v>0.06934012978238255</v>
       </c>
       <c r="T11">
-        <v>0.5393406815911083</v>
+        <v>0.5436519580226918</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.91303968844237</v>
+        <v>21.52173571959814</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0659271168041443</v>
+        <v>0.06575569273155416</v>
       </c>
       <c r="C12">
-        <v>3884.673395837502</v>
+        <v>3855.187161855154</v>
       </c>
       <c r="D12">
-        <v>3603.483395837502</v>
+        <v>3634.438161855154</v>
       </c>
       <c r="E12">
-        <v>-3878.09</v>
+        <v>-3817.649</v>
       </c>
       <c r="F12">
-        <v>604.4100000000001</v>
+        <v>664.851</v>
       </c>
       <c r="G12">
         <v>885.6</v>
@@ -2271,28 +2271,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M12">
-        <v>30.401823</v>
+        <v>33.4420053</v>
       </c>
       <c r="N12">
-        <v>623.8981770000001</v>
+        <v>620.8579947000002</v>
       </c>
       <c r="O12">
-        <v>187.1694531</v>
+        <v>186.25739841</v>
       </c>
       <c r="P12">
-        <v>436.7287239000001</v>
+        <v>434.6005962900001</v>
       </c>
       <c r="Q12">
-        <v>994.4287239000001</v>
+        <v>992.3005962900002</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06934012978238255</v>
+        <v>0.06953100306916198</v>
       </c>
       <c r="T12">
-        <v>0.5436519580226918</v>
+        <v>0.5480601170707154</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.52173571959813</v>
+        <v>19.56521429054376</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06575569273155416</v>
+        <v>0.06558426865896402</v>
       </c>
       <c r="C13">
-        <v>3855.187161855154</v>
+        <v>3826.237353266969</v>
       </c>
       <c r="D13">
-        <v>3634.438161855154</v>
+        <v>3665.929353266969</v>
       </c>
       <c r="E13">
-        <v>-3817.649</v>
+        <v>-3757.208</v>
       </c>
       <c r="F13">
-        <v>664.851</v>
+        <v>725.292</v>
       </c>
       <c r="G13">
         <v>885.6</v>
@@ -2353,28 +2353,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M13">
-        <v>33.4420053</v>
+        <v>36.4821876</v>
       </c>
       <c r="N13">
-        <v>620.8579947000002</v>
+        <v>617.8178124000002</v>
       </c>
       <c r="O13">
-        <v>186.25739841</v>
+        <v>185.34534372</v>
       </c>
       <c r="P13">
-        <v>434.6005962900001</v>
+        <v>432.4724686800001</v>
       </c>
       <c r="Q13">
-        <v>992.3005962900002</v>
+        <v>990.1724686800002</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06953100306916198</v>
+        <v>0.06972621438518639</v>
       </c>
       <c r="T13">
-        <v>0.5480601170707154</v>
+        <v>0.5525684615516488</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.56521429054376</v>
+        <v>17.93477976633178</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06558426865896402</v>
+        <v>0.06541284458637389</v>
       </c>
       <c r="C14">
-        <v>3826.237353266969</v>
+        <v>3797.838035787684</v>
       </c>
       <c r="D14">
-        <v>3665.929353266969</v>
+        <v>3697.971035787684</v>
       </c>
       <c r="E14">
-        <v>-3757.208</v>
+        <v>-3696.767</v>
       </c>
       <c r="F14">
-        <v>725.292</v>
+        <v>785.7330000000001</v>
       </c>
       <c r="G14">
         <v>885.6</v>
@@ -2435,28 +2435,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M14">
-        <v>36.4821876</v>
+        <v>39.5223699</v>
       </c>
       <c r="N14">
-        <v>617.8178124000002</v>
+        <v>614.7776301000001</v>
       </c>
       <c r="O14">
-        <v>185.34534372</v>
+        <v>184.43328903</v>
       </c>
       <c r="P14">
-        <v>432.4724686800001</v>
+        <v>430.3443410700001</v>
       </c>
       <c r="Q14">
-        <v>990.1724686800002</v>
+        <v>988.0443410700002</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06972621438518639</v>
+        <v>0.06992591331767113</v>
       </c>
       <c r="T14">
-        <v>0.5525684615516488</v>
+        <v>0.557180446135592</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.93477976633178</v>
+        <v>16.55518132276779</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06541284458637389</v>
+        <v>0.06524142051378376</v>
       </c>
       <c r="C15">
-        <v>3797.838035787684</v>
+        <v>3770.003771227908</v>
       </c>
       <c r="D15">
-        <v>3697.971035787684</v>
+        <v>3730.577771227908</v>
       </c>
       <c r="E15">
-        <v>-3696.767</v>
+        <v>-3636.326</v>
       </c>
       <c r="F15">
-        <v>785.7330000000001</v>
+        <v>846.1740000000001</v>
       </c>
       <c r="G15">
         <v>885.6</v>
@@ -2517,28 +2517,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M15">
-        <v>39.5223699</v>
+        <v>42.5625522</v>
       </c>
       <c r="N15">
-        <v>614.7776301000001</v>
+        <v>611.7374478000002</v>
       </c>
       <c r="O15">
-        <v>184.43328903</v>
+        <v>183.52123434</v>
       </c>
       <c r="P15">
-        <v>430.3443410700001</v>
+        <v>428.2162134600001</v>
       </c>
       <c r="Q15">
-        <v>988.0443410700002</v>
+        <v>985.9162134600001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06992591331767113</v>
+        <v>0.07013025641137646</v>
       </c>
       <c r="T15">
-        <v>0.557180446135592</v>
+        <v>0.5618996861749759</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.55518132276779</v>
+        <v>15.37266837114153</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06524142051378376</v>
+        <v>0.06506999644119361</v>
       </c>
       <c r="C16">
-        <v>3770.003771227908</v>
+        <v>3742.749639560228</v>
       </c>
       <c r="D16">
-        <v>3730.577771227908</v>
+        <v>3763.764639560228</v>
       </c>
       <c r="E16">
-        <v>-3636.326</v>
+        <v>-3575.885</v>
       </c>
       <c r="F16">
-        <v>846.1740000000001</v>
+        <v>906.6150000000002</v>
       </c>
       <c r="G16">
         <v>885.6</v>
@@ -2599,28 +2599,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M16">
-        <v>42.5625522</v>
+        <v>45.60273450000001</v>
       </c>
       <c r="N16">
-        <v>611.7374478000002</v>
+        <v>608.6972655000002</v>
       </c>
       <c r="O16">
-        <v>183.52123434</v>
+        <v>182.60917965</v>
       </c>
       <c r="P16">
-        <v>428.2162134600001</v>
+        <v>426.0880858500001</v>
       </c>
       <c r="Q16">
-        <v>985.9162134600001</v>
+        <v>983.7880858500002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07013025641137646</v>
+        <v>0.07033940757787484</v>
       </c>
       <c r="T16">
-        <v>0.5618996861749759</v>
+        <v>0.5667299671564628</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.37266837114153</v>
+        <v>14.34782381306542</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06506999644119361</v>
+        <v>0.06489857236860347</v>
       </c>
       <c r="C17">
-        <v>3742.749639560228</v>
+        <v>3716.091262173677</v>
       </c>
       <c r="D17">
-        <v>3763.764639560228</v>
+        <v>3797.547262173677</v>
       </c>
       <c r="E17">
-        <v>-3575.885</v>
+        <v>-3515.444</v>
       </c>
       <c r="F17">
-        <v>906.615</v>
+        <v>967.056</v>
       </c>
       <c r="G17">
         <v>885.6</v>
@@ -2681,28 +2681,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M17">
-        <v>45.6027345</v>
+        <v>48.6429168</v>
       </c>
       <c r="N17">
-        <v>608.6972655000002</v>
+        <v>605.6570832000002</v>
       </c>
       <c r="O17">
-        <v>182.60917965</v>
+        <v>181.6971249600001</v>
       </c>
       <c r="P17">
-        <v>426.0880858500001</v>
+        <v>423.9599582400002</v>
       </c>
       <c r="Q17">
-        <v>983.7880858500002</v>
+        <v>981.6599582400002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07033940757787484</v>
+        <v>0.07055353853405176</v>
       </c>
       <c r="T17">
-        <v>0.5667299671564628</v>
+        <v>0.5716752548279852</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.34782381306542</v>
+        <v>13.45108482474884</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06489857236860347</v>
+        <v>0.06490564829601335</v>
       </c>
       <c r="C18">
-        <v>3716.091262173677</v>
+        <v>3654.243810618284</v>
       </c>
       <c r="D18">
-        <v>3797.547262173677</v>
+        <v>3796.140810618283</v>
       </c>
       <c r="E18">
-        <v>-3515.444</v>
+        <v>-3455.003</v>
       </c>
       <c r="F18">
-        <v>967.056</v>
+        <v>1027.497</v>
       </c>
       <c r="G18">
         <v>885.6</v>
@@ -2763,45 +2763,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M18">
-        <v>48.6429168</v>
+        <v>53.2243446</v>
       </c>
       <c r="N18">
-        <v>605.6570832000002</v>
+        <v>601.0756554000002</v>
       </c>
       <c r="O18">
-        <v>181.6971249600001</v>
+        <v>180.32269662</v>
       </c>
       <c r="P18">
-        <v>423.9599582400002</v>
+        <v>420.7529587800001</v>
       </c>
       <c r="Q18">
-        <v>981.6599582400002</v>
+        <v>978.4529587800002</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07055353853405176</v>
+        <v>0.07077282927230524</v>
       </c>
       <c r="T18">
-        <v>0.5716752548279852</v>
+        <v>0.5767397060578576</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.45108482474884</v>
+        <v>12.29324672604799</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06490564829601335</v>
+        <v>0.0647447242234232</v>
       </c>
       <c r="C19">
-        <v>3654.243810618284</v>
+        <v>3626.048750552055</v>
       </c>
       <c r="D19">
-        <v>3796.140810618283</v>
+        <v>3828.386750552055</v>
       </c>
       <c r="E19">
-        <v>-3455.003</v>
+        <v>-3394.562</v>
       </c>
       <c r="F19">
-        <v>1027.497</v>
+        <v>1087.938</v>
       </c>
       <c r="G19">
         <v>885.6</v>
@@ -2845,28 +2845,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M19">
-        <v>53.2243446</v>
+        <v>56.3551884</v>
       </c>
       <c r="N19">
-        <v>601.0756554000002</v>
+        <v>597.9448116000002</v>
       </c>
       <c r="O19">
-        <v>180.32269662</v>
+        <v>179.3834434800001</v>
       </c>
       <c r="P19">
-        <v>420.7529587800001</v>
+        <v>418.5613681200001</v>
       </c>
       <c r="Q19">
-        <v>978.4529587800002</v>
+        <v>976.2613681200002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07077282927230524</v>
+        <v>0.07099746856515024</v>
       </c>
       <c r="T19">
-        <v>0.5767397060578576</v>
+        <v>0.5819276804884583</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.29324672604799</v>
+        <v>11.61028857460088</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0647447242234232</v>
+        <v>0.06458380015083307</v>
       </c>
       <c r="C20">
-        <v>3626.048750552055</v>
+        <v>3598.406203602122</v>
       </c>
       <c r="D20">
-        <v>3828.386750552055</v>
+        <v>3861.185203602122</v>
       </c>
       <c r="E20">
-        <v>-3394.562</v>
+        <v>-3334.121</v>
       </c>
       <c r="F20">
-        <v>1087.938</v>
+        <v>1148.379</v>
       </c>
       <c r="G20">
         <v>885.6</v>
@@ -2927,28 +2927,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M20">
-        <v>56.3551884</v>
+        <v>59.4860322</v>
       </c>
       <c r="N20">
-        <v>597.9448116000002</v>
+        <v>594.8139678000002</v>
       </c>
       <c r="O20">
-        <v>179.3834434800001</v>
+        <v>178.4441903400001</v>
       </c>
       <c r="P20">
-        <v>418.5613681200001</v>
+        <v>416.3697774600001</v>
       </c>
       <c r="Q20">
-        <v>976.2613681200002</v>
+        <v>974.0697774600002</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07099746856515024</v>
+        <v>0.07122765450720131</v>
       </c>
       <c r="T20">
-        <v>0.5819276804884583</v>
+        <v>0.5872437530531481</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.61028857460088</v>
+        <v>10.99922075488505</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06458380015083307</v>
+        <v>0.06442287607824294</v>
       </c>
       <c r="C21">
-        <v>3598.406203602122</v>
+        <v>3571.330492904257</v>
       </c>
       <c r="D21">
-        <v>3861.185203602122</v>
+        <v>3894.550492904256</v>
       </c>
       <c r="E21">
-        <v>-3334.121</v>
+        <v>-3273.68</v>
       </c>
       <c r="F21">
-        <v>1148.379</v>
+        <v>1208.82</v>
       </c>
       <c r="G21">
         <v>885.6</v>
@@ -3009,28 +3009,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M21">
-        <v>59.4860322</v>
+        <v>62.616876</v>
       </c>
       <c r="N21">
-        <v>594.8139678000002</v>
+        <v>591.6831240000001</v>
       </c>
       <c r="O21">
-        <v>178.4441903400001</v>
+        <v>177.5049372</v>
       </c>
       <c r="P21">
-        <v>416.3697774600001</v>
+        <v>414.1781868000001</v>
       </c>
       <c r="Q21">
-        <v>974.0697774600002</v>
+        <v>971.8781868000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07122765450720131</v>
+        <v>0.07146359509780367</v>
       </c>
       <c r="T21">
-        <v>0.5872437530531481</v>
+        <v>0.5926927274319553</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.99922075488505</v>
+        <v>10.44925971714079</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06442287607824294</v>
+        <v>0.06426195200565279</v>
       </c>
       <c r="C22">
-        <v>3571.330492904257</v>
+        <v>3544.83644098614</v>
       </c>
       <c r="D22">
-        <v>3894.550492904256</v>
+        <v>3928.49744098614</v>
       </c>
       <c r="E22">
-        <v>-3273.68</v>
+        <v>-3213.239</v>
       </c>
       <c r="F22">
-        <v>1208.82</v>
+        <v>1269.261</v>
       </c>
       <c r="G22">
         <v>885.6</v>
@@ -3091,28 +3091,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M22">
-        <v>62.616876</v>
+        <v>65.74771980000001</v>
       </c>
       <c r="N22">
-        <v>591.6831240000001</v>
+        <v>588.5522802000002</v>
       </c>
       <c r="O22">
-        <v>177.5049372</v>
+        <v>176.5656840600001</v>
       </c>
       <c r="P22">
-        <v>414.1781868000001</v>
+        <v>411.9865961400001</v>
       </c>
       <c r="Q22">
-        <v>971.8781868000001</v>
+        <v>969.6865961400001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07146359509780367</v>
+        <v>0.07170550886791494</v>
       </c>
       <c r="T22">
-        <v>0.5926927274319553</v>
+        <v>0.5982796505292132</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.44925971714079</v>
+        <v>9.951675921086469</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06426195200565278</v>
+        <v>0.06436282793306267</v>
       </c>
       <c r="C23">
-        <v>3544.836440986144</v>
+        <v>3463.046817591267</v>
       </c>
       <c r="D23">
-        <v>3928.497440986143</v>
+        <v>3907.148817591267</v>
       </c>
       <c r="E23">
-        <v>-3213.239</v>
+        <v>-3152.798</v>
       </c>
       <c r="F23">
-        <v>1269.261</v>
+        <v>1329.702</v>
       </c>
       <c r="G23">
         <v>885.6</v>
@@ -3173,45 +3173,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M23">
-        <v>65.7477198</v>
+        <v>71.13905699999999</v>
       </c>
       <c r="N23">
-        <v>588.5522802000002</v>
+        <v>583.1609430000002</v>
       </c>
       <c r="O23">
-        <v>176.5656840600001</v>
+        <v>174.9482829000001</v>
       </c>
       <c r="P23">
-        <v>411.9865961400001</v>
+        <v>408.2126601000001</v>
       </c>
       <c r="Q23">
-        <v>969.6865961400001</v>
+        <v>965.9126601000002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07170550886791492</v>
+        <v>0.07195362555520854</v>
       </c>
       <c r="T23">
-        <v>0.5982796505292131</v>
+        <v>0.6040098280648623</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.951675921086471</v>
+        <v>9.197479241255619</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06436282793306267</v>
+        <v>0.06421380386047251</v>
       </c>
       <c r="C24">
-        <v>3463.046817591267</v>
+        <v>3434.226618672088</v>
       </c>
       <c r="D24">
-        <v>3907.148817591267</v>
+        <v>3938.769618672088</v>
       </c>
       <c r="E24">
-        <v>-3152.798</v>
+        <v>-3092.357</v>
       </c>
       <c r="F24">
-        <v>1329.702</v>
+        <v>1390.143</v>
       </c>
       <c r="G24">
         <v>885.6</v>
@@ -3255,28 +3255,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M24">
-        <v>71.13905699999999</v>
+        <v>74.37265050000001</v>
       </c>
       <c r="N24">
-        <v>583.1609430000002</v>
+        <v>579.9273495000002</v>
       </c>
       <c r="O24">
-        <v>174.9482829000001</v>
+        <v>173.9782048500001</v>
       </c>
       <c r="P24">
-        <v>408.2126601000001</v>
+        <v>405.9491446500002</v>
       </c>
       <c r="Q24">
-        <v>965.9126601000002</v>
+        <v>963.6491446500002</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07195362555520854</v>
+        <v>0.07220818683178248</v>
       </c>
       <c r="T24">
-        <v>0.6040098280648623</v>
+        <v>0.609888841380658</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.197479241255619</v>
+        <v>8.797588839461895</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06421380386047251</v>
+        <v>0.06406477978788239</v>
       </c>
       <c r="C25">
-        <v>3434.226618672088</v>
+        <v>3405.922413989937</v>
       </c>
       <c r="D25">
-        <v>3938.769618672088</v>
+        <v>3970.906413989938</v>
       </c>
       <c r="E25">
-        <v>-3092.357</v>
+        <v>-3031.916</v>
       </c>
       <c r="F25">
-        <v>1390.143</v>
+        <v>1450.584</v>
       </c>
       <c r="G25">
         <v>885.6</v>
@@ -3337,28 +3337,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M25">
-        <v>74.37265050000001</v>
+        <v>77.60624400000002</v>
       </c>
       <c r="N25">
-        <v>579.9273495000002</v>
+        <v>576.6937560000001</v>
       </c>
       <c r="O25">
-        <v>173.9782048500001</v>
+        <v>173.0081268</v>
       </c>
       <c r="P25">
-        <v>405.9491446500002</v>
+        <v>403.6856292000001</v>
       </c>
       <c r="Q25">
-        <v>963.6491446500002</v>
+        <v>961.3856292000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07220818683178248</v>
+        <v>0.07246944708931893</v>
       </c>
       <c r="T25">
-        <v>0.609888841380658</v>
+        <v>0.6159225655731854</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.797588839461895</v>
+        <v>8.431022637817648</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06406477978788239</v>
+        <v>0.06391575571529225</v>
       </c>
       <c r="C26">
-        <v>3405.922413989938</v>
+        <v>3378.146937580961</v>
       </c>
       <c r="D26">
-        <v>3970.906413989938</v>
+        <v>4003.571937580961</v>
       </c>
       <c r="E26">
-        <v>-3031.916</v>
+        <v>-2971.475</v>
       </c>
       <c r="F26">
-        <v>1450.584</v>
+        <v>1511.025</v>
       </c>
       <c r="G26">
         <v>885.6</v>
@@ -3419,28 +3419,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M26">
-        <v>77.606244</v>
+        <v>80.8398375</v>
       </c>
       <c r="N26">
-        <v>576.6937560000001</v>
+        <v>573.4601625000001</v>
       </c>
       <c r="O26">
-        <v>173.0081268</v>
+        <v>172.03804875</v>
       </c>
       <c r="P26">
-        <v>403.6856292000001</v>
+        <v>401.4221137500001</v>
       </c>
       <c r="Q26">
-        <v>961.3856292000002</v>
+        <v>959.1221137500002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07246944708931893</v>
+        <v>0.07273767428705633</v>
       </c>
       <c r="T26">
-        <v>0.6159225655731854</v>
+        <v>0.6221171890775133</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.431022637817648</v>
+        <v>8.093781732304944</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06391575571529225</v>
+        <v>0.06376673164270211</v>
       </c>
       <c r="C27">
-        <v>3378.146937580961</v>
+        <v>3350.913345968353</v>
       </c>
       <c r="D27">
-        <v>4003.571937580961</v>
+        <v>4036.779345968354</v>
       </c>
       <c r="E27">
-        <v>-2971.475</v>
+        <v>-2911.034</v>
       </c>
       <c r="F27">
-        <v>1511.025</v>
+        <v>1571.466</v>
       </c>
       <c r="G27">
         <v>885.6</v>
@@ -3501,28 +3501,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M27">
-        <v>80.8398375</v>
+        <v>84.073431</v>
       </c>
       <c r="N27">
-        <v>573.4601625000001</v>
+        <v>570.2265690000002</v>
       </c>
       <c r="O27">
-        <v>172.03804875</v>
+        <v>171.0679707</v>
       </c>
       <c r="P27">
-        <v>401.4221137500001</v>
+        <v>399.1585983000001</v>
       </c>
       <c r="Q27">
-        <v>959.1221137500002</v>
+        <v>956.8585983000002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07273767428705633</v>
+        <v>0.07301315086851637</v>
       </c>
       <c r="T27">
-        <v>0.6221171890775133</v>
+        <v>0.628479234838715</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.093781732304944</v>
+        <v>7.7824824349086</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06376673164270211</v>
+        <v>0.06376890757011197</v>
       </c>
       <c r="C28">
-        <v>3350.913345968353</v>
+        <v>3289.983516094184</v>
       </c>
       <c r="D28">
-        <v>4036.779345968354</v>
+        <v>4036.290516094184</v>
       </c>
       <c r="E28">
-        <v>-2911.034</v>
+        <v>-2850.593</v>
       </c>
       <c r="F28">
-        <v>1571.466</v>
+        <v>1631.907</v>
       </c>
       <c r="G28">
         <v>885.6</v>
@@ -3583,45 +3583,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M28">
-        <v>84.073431</v>
+        <v>88.61255010000001</v>
       </c>
       <c r="N28">
-        <v>570.2265690000002</v>
+        <v>565.6874499000002</v>
       </c>
       <c r="O28">
-        <v>171.0679707</v>
+        <v>169.7062349700001</v>
       </c>
       <c r="P28">
-        <v>399.1585983000001</v>
+        <v>395.9812149300001</v>
       </c>
       <c r="Q28">
-        <v>956.8585983000002</v>
+        <v>953.6812149300001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07301315086851637</v>
+        <v>0.07329617475357805</v>
       </c>
       <c r="T28">
-        <v>0.628479234838715</v>
+        <v>0.6350155832235115</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.7824824349086</v>
+        <v>7.383829934491414</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06376890757011197</v>
+        <v>0.06362548349752183</v>
       </c>
       <c r="C29">
-        <v>3289.983516094184</v>
+        <v>3262.018562202874</v>
       </c>
       <c r="D29">
-        <v>4036.290516094184</v>
+        <v>4068.766562202874</v>
       </c>
       <c r="E29">
-        <v>-2850.593</v>
+        <v>-2790.152</v>
       </c>
       <c r="F29">
-        <v>1631.907</v>
+        <v>1692.348</v>
       </c>
       <c r="G29">
         <v>885.6</v>
@@ -3665,28 +3665,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M29">
-        <v>88.61255010000001</v>
+        <v>91.89449640000001</v>
       </c>
       <c r="N29">
-        <v>565.6874499000002</v>
+        <v>562.4055036000002</v>
       </c>
       <c r="O29">
-        <v>169.7062349700001</v>
+        <v>168.72165108</v>
       </c>
       <c r="P29">
-        <v>395.9812149300001</v>
+        <v>393.6838525200002</v>
       </c>
       <c r="Q29">
-        <v>953.6812149300001</v>
+        <v>951.3838525200002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07329617475357805</v>
+        <v>0.07358706041322477</v>
       </c>
       <c r="T29">
-        <v>0.6350155832235115</v>
+        <v>0.6417334968412187</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.383829934491414</v>
+        <v>7.120121722545292</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06362548349752183</v>
+        <v>0.06348205942493169</v>
       </c>
       <c r="C30">
-        <v>3262.018562202874</v>
+        <v>3234.580452688971</v>
       </c>
       <c r="D30">
-        <v>4068.766562202874</v>
+        <v>4101.769452688971</v>
       </c>
       <c r="E30">
-        <v>-2790.152</v>
+        <v>-2729.711</v>
       </c>
       <c r="F30">
-        <v>1692.348</v>
+        <v>1752.789</v>
       </c>
       <c r="G30">
         <v>885.6</v>
@@ -3747,28 +3747,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M30">
-        <v>91.89449640000001</v>
+        <v>95.17644270000001</v>
       </c>
       <c r="N30">
-        <v>562.4055036000002</v>
+        <v>559.1235573000001</v>
       </c>
       <c r="O30">
-        <v>168.72165108</v>
+        <v>167.73706719</v>
       </c>
       <c r="P30">
-        <v>393.6838525200002</v>
+        <v>391.3864901100001</v>
       </c>
       <c r="Q30">
-        <v>951.3838525200002</v>
+        <v>949.0864901100001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07358706041322477</v>
+        <v>0.07388614003511507</v>
       </c>
       <c r="T30">
-        <v>0.6417334968412187</v>
+        <v>0.6486406474622418</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.120121722545292</v>
+        <v>6.874600283836833</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06348205942493169</v>
+        <v>0.06333863535234155</v>
       </c>
       <c r="C31">
-        <v>3234.580452688971</v>
+        <v>3207.682112531772</v>
       </c>
       <c r="D31">
-        <v>4101.769452688971</v>
+        <v>4135.312112531772</v>
       </c>
       <c r="E31">
-        <v>-2729.711</v>
+        <v>-2669.27</v>
       </c>
       <c r="F31">
-        <v>1752.789</v>
+        <v>1813.23</v>
       </c>
       <c r="G31">
         <v>885.6</v>
@@ -3829,28 +3829,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M31">
-        <v>95.1764427</v>
+        <v>98.458389</v>
       </c>
       <c r="N31">
-        <v>559.1235573000001</v>
+        <v>555.8416110000002</v>
       </c>
       <c r="O31">
-        <v>167.73706719</v>
+        <v>166.7524833000001</v>
       </c>
       <c r="P31">
-        <v>391.3864901100001</v>
+        <v>389.0891277000001</v>
       </c>
       <c r="Q31">
-        <v>949.0864901100001</v>
+        <v>946.7891277000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07388614003511507</v>
+        <v>0.07419376478905937</v>
       </c>
       <c r="T31">
-        <v>0.6486406474622418</v>
+        <v>0.6557451452438654</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.874600283836834</v>
+        <v>6.645446941042273</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06333863535234155</v>
+        <v>0.06319521127975142</v>
       </c>
       <c r="C32">
-        <v>3207.682112531772</v>
+        <v>3181.336892978026</v>
       </c>
       <c r="D32">
-        <v>4135.312112531772</v>
+        <v>4169.407892978026</v>
       </c>
       <c r="E32">
-        <v>-2669.27</v>
+        <v>-2608.829</v>
       </c>
       <c r="F32">
-        <v>1813.23</v>
+        <v>1873.671</v>
       </c>
       <c r="G32">
         <v>885.6</v>
@@ -3911,28 +3911,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M32">
-        <v>98.458389</v>
+        <v>101.7403353</v>
       </c>
       <c r="N32">
-        <v>555.8416110000002</v>
+        <v>552.5596647000002</v>
       </c>
       <c r="O32">
-        <v>166.7524833000001</v>
+        <v>165.7678994100001</v>
       </c>
       <c r="P32">
-        <v>389.0891277000001</v>
+        <v>386.7917652900002</v>
       </c>
       <c r="Q32">
-        <v>946.7891277000001</v>
+        <v>944.4917652900002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07419376478905937</v>
+        <v>0.07451030620253829</v>
       </c>
       <c r="T32">
-        <v>0.6557451452438654</v>
+        <v>0.6630555704974201</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.645446941042273</v>
+        <v>6.43107768487962</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06319521127975142</v>
+        <v>0.06305178720716129</v>
       </c>
       <c r="C33">
-        <v>3181.336892978026</v>
+        <v>3155.558589261002</v>
       </c>
       <c r="D33">
-        <v>4169.407892978026</v>
+        <v>4204.070589261001</v>
       </c>
       <c r="E33">
-        <v>-2608.829</v>
+        <v>-2548.388</v>
       </c>
       <c r="F33">
-        <v>1873.671</v>
+        <v>1934.112</v>
       </c>
       <c r="G33">
         <v>885.6</v>
@@ -3993,28 +3993,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M33">
-        <v>101.7403353</v>
+        <v>105.0222816</v>
       </c>
       <c r="N33">
-        <v>552.5596647000002</v>
+        <v>549.2777184000001</v>
       </c>
       <c r="O33">
-        <v>165.7678994100001</v>
+        <v>164.78331552</v>
       </c>
       <c r="P33">
-        <v>386.7917652900002</v>
+        <v>384.4944028800001</v>
       </c>
       <c r="Q33">
-        <v>944.4917652900002</v>
+        <v>942.1944028800001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07451030620253829</v>
+        <v>0.07483615765759012</v>
       </c>
       <c r="T33">
-        <v>0.6630555704974201</v>
+        <v>0.6705810082584325</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.43107768487962</v>
+        <v>6.230106507227131</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06305178720716129</v>
+        <v>0.06313936313457114</v>
       </c>
       <c r="C34">
-        <v>3155.558589261002</v>
+        <v>3073.884088474751</v>
       </c>
       <c r="D34">
-        <v>4204.070589261001</v>
+        <v>4182.83708847475</v>
       </c>
       <c r="E34">
-        <v>-2548.388</v>
+        <v>-2487.947</v>
       </c>
       <c r="F34">
-        <v>1934.112</v>
+        <v>1994.553</v>
       </c>
       <c r="G34">
         <v>885.6</v>
@@ -4075,45 +4075,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M34">
-        <v>105.0222816</v>
+        <v>110.2987809</v>
       </c>
       <c r="N34">
-        <v>549.2777184000001</v>
+        <v>544.0012191000002</v>
       </c>
       <c r="O34">
-        <v>164.78331552</v>
+        <v>163.20036573</v>
       </c>
       <c r="P34">
-        <v>384.4944028800001</v>
+        <v>380.8008533700001</v>
       </c>
       <c r="Q34">
-        <v>942.1944028800001</v>
+        <v>938.5008533700002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07483615765759012</v>
+        <v>0.07517173602174798</v>
       </c>
       <c r="T34">
-        <v>0.6705810082584325</v>
+        <v>0.6783310859526094</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.230106507227131</v>
+        <v>5.932069191165468</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06313936313457114</v>
+        <v>0.06300293906198101</v>
       </c>
       <c r="C35">
-        <v>3073.884088474751</v>
+        <v>3046.61414538164</v>
       </c>
       <c r="D35">
-        <v>4182.83708847475</v>
+        <v>4216.00814538164</v>
       </c>
       <c r="E35">
-        <v>-2487.947</v>
+        <v>-2427.506</v>
       </c>
       <c r="F35">
-        <v>1994.553</v>
+        <v>2054.994</v>
       </c>
       <c r="G35">
         <v>885.6</v>
@@ -4157,28 +4157,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M35">
-        <v>110.2987809</v>
+        <v>113.6411682</v>
       </c>
       <c r="N35">
-        <v>544.0012191000002</v>
+        <v>540.6588318000001</v>
       </c>
       <c r="O35">
-        <v>163.20036573</v>
+        <v>162.19764954</v>
       </c>
       <c r="P35">
-        <v>380.8008533700001</v>
+        <v>378.4611822600001</v>
       </c>
       <c r="Q35">
-        <v>938.5008533700002</v>
+        <v>936.1611822600001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07517173602174798</v>
+        <v>0.07551748342724396</v>
       </c>
       <c r="T35">
-        <v>0.6783310859526094</v>
+        <v>0.6863160144860037</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.932069191165468</v>
+        <v>5.757596567895895</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06300293906198101</v>
+        <v>0.06286651498939087</v>
       </c>
       <c r="C36">
-        <v>3046.61414538164</v>
+        <v>3019.87451919016</v>
       </c>
       <c r="D36">
-        <v>4216.00814538164</v>
+        <v>4249.70951919016</v>
       </c>
       <c r="E36">
-        <v>-2427.506</v>
+        <v>-2367.065</v>
       </c>
       <c r="F36">
-        <v>2054.994</v>
+        <v>2115.435</v>
       </c>
       <c r="G36">
         <v>885.6</v>
@@ -4239,28 +4239,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M36">
-        <v>113.6411682</v>
+        <v>116.9835555</v>
       </c>
       <c r="N36">
-        <v>540.6588318000001</v>
+        <v>537.3164445000002</v>
       </c>
       <c r="O36">
-        <v>162.19764954</v>
+        <v>161.1949333500001</v>
       </c>
       <c r="P36">
-        <v>378.4611822600001</v>
+        <v>376.1215111500002</v>
       </c>
       <c r="Q36">
-        <v>936.1611822600001</v>
+        <v>933.8215111500002</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07551748342724396</v>
+        <v>0.0758738692144475</v>
       </c>
       <c r="T36">
-        <v>0.6863160144860037</v>
+        <v>0.6945466331281178</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.757596567895895</v>
+        <v>5.593093808813155</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06286651498939087</v>
+        <v>0.06273009091680073</v>
       </c>
       <c r="C37">
-        <v>3019.87451919016</v>
+        <v>2993.678029912644</v>
       </c>
       <c r="D37">
-        <v>4249.70951919016</v>
+        <v>4283.954029912644</v>
       </c>
       <c r="E37">
-        <v>-2367.065</v>
+        <v>-2306.624</v>
       </c>
       <c r="F37">
-        <v>2115.435</v>
+        <v>2175.876</v>
       </c>
       <c r="G37">
         <v>885.6</v>
@@ -4321,28 +4321,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M37">
-        <v>116.9835555</v>
+        <v>120.3259428</v>
       </c>
       <c r="N37">
-        <v>537.3164445000002</v>
+        <v>533.9740572000002</v>
       </c>
       <c r="O37">
-        <v>161.1949333500001</v>
+        <v>160.19221716</v>
       </c>
       <c r="P37">
-        <v>376.1215111500002</v>
+        <v>373.7818400400001</v>
       </c>
       <c r="Q37">
-        <v>933.8215111500002</v>
+        <v>931.4818400400002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0758738692144475</v>
+        <v>0.07624139205750115</v>
       </c>
       <c r="T37">
-        <v>0.6945466331281178</v>
+        <v>0.703034458602798</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.593093808813155</v>
+        <v>5.437730091901678</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06273009091680073</v>
+        <v>0.06259366684421061</v>
       </c>
       <c r="C38">
-        <v>2993.678029912644</v>
+        <v>2968.037914137106</v>
       </c>
       <c r="D38">
-        <v>4283.954029912644</v>
+        <v>4318.754914137106</v>
       </c>
       <c r="E38">
-        <v>-2306.624</v>
+        <v>-2246.183</v>
       </c>
       <c r="F38">
-        <v>2175.876</v>
+        <v>2236.317</v>
       </c>
       <c r="G38">
         <v>885.6</v>
@@ -4403,28 +4403,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M38">
-        <v>120.3259428</v>
+        <v>123.6683301</v>
       </c>
       <c r="N38">
-        <v>533.9740572000002</v>
+        <v>530.6316699000001</v>
       </c>
       <c r="O38">
-        <v>160.19221716</v>
+        <v>159.18950097</v>
       </c>
       <c r="P38">
-        <v>373.7818400400001</v>
+        <v>371.4421689300001</v>
       </c>
       <c r="Q38">
-        <v>931.4818400400002</v>
+        <v>929.1421689300001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07624139205750115</v>
+        <v>0.07662058229239778</v>
       </c>
       <c r="T38">
-        <v>0.703034458602798</v>
+        <v>0.7117917388544521</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.437730091901678</v>
+        <v>5.290764413742174</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06259366684421061</v>
+        <v>0.06245724277162047</v>
       </c>
       <c r="C39">
-        <v>2968.037914137106</v>
+        <v>2942.967842086183</v>
       </c>
       <c r="D39">
-        <v>4318.754914137106</v>
+        <v>4354.125842086183</v>
       </c>
       <c r="E39">
-        <v>-2246.183</v>
+        <v>-2185.742</v>
       </c>
       <c r="F39">
-        <v>2236.317</v>
+        <v>2296.758</v>
       </c>
       <c r="G39">
         <v>885.6</v>
@@ -4485,28 +4485,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M39">
-        <v>123.6683301</v>
+        <v>127.0107174</v>
       </c>
       <c r="N39">
-        <v>530.6316699000001</v>
+        <v>527.2892826000002</v>
       </c>
       <c r="O39">
-        <v>159.18950097</v>
+        <v>158.1867847800001</v>
       </c>
       <c r="P39">
-        <v>371.4421689300001</v>
+        <v>369.1024978200002</v>
       </c>
       <c r="Q39">
-        <v>929.1421689300001</v>
+        <v>926.8024978200002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07662058229239778</v>
+        <v>0.07701200447035558</v>
       </c>
       <c r="T39">
-        <v>0.7117917388544521</v>
+        <v>0.72083151201745</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.290764413742174</v>
+        <v>5.151533771275274</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06245724277162047</v>
+        <v>0.06232081869903033</v>
       </c>
       <c r="C40">
-        <v>2942.967842086183</v>
+        <v>2918.481935521245</v>
       </c>
       <c r="D40">
-        <v>4354.125842086183</v>
+        <v>4390.080935521245</v>
       </c>
       <c r="E40">
-        <v>-2185.742</v>
+        <v>-2125.301</v>
       </c>
       <c r="F40">
-        <v>2296.758</v>
+        <v>2357.199</v>
       </c>
       <c r="G40">
         <v>885.6</v>
@@ -4567,28 +4567,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M40">
-        <v>127.0107174</v>
+        <v>130.3531047</v>
       </c>
       <c r="N40">
-        <v>527.2892826000002</v>
+        <v>523.9468953000002</v>
       </c>
       <c r="O40">
-        <v>158.1867847800001</v>
+        <v>157.18406859</v>
       </c>
       <c r="P40">
-        <v>369.1024978200002</v>
+        <v>366.7628267100001</v>
       </c>
       <c r="Q40">
-        <v>926.8024978200002</v>
+        <v>924.4628267100002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07701200447035558</v>
+        <v>0.07741626016234479</v>
       </c>
       <c r="T40">
-        <v>0.72083151201745</v>
+        <v>0.7301676711857922</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.151533771275274</v>
+        <v>5.019443161755396</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06232081869903033</v>
+        <v>0.0621843946264402</v>
       </c>
       <c r="C41">
-        <v>2918.481935521245</v>
+        <v>2894.594786541021</v>
       </c>
       <c r="D41">
-        <v>4390.080935521245</v>
+        <v>4426.634786541021</v>
       </c>
       <c r="E41">
-        <v>-2125.301</v>
+        <v>-2064.86</v>
       </c>
       <c r="F41">
-        <v>2357.199</v>
+        <v>2417.64</v>
       </c>
       <c r="G41">
         <v>885.6</v>
@@ -4649,28 +4649,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M41">
-        <v>130.3531047</v>
+        <v>133.695492</v>
       </c>
       <c r="N41">
-        <v>523.9468953000002</v>
+        <v>520.6045080000001</v>
       </c>
       <c r="O41">
-        <v>157.18406859</v>
+        <v>156.1813524</v>
       </c>
       <c r="P41">
-        <v>366.7628267100001</v>
+        <v>364.4231556000001</v>
       </c>
       <c r="Q41">
-        <v>924.4628267100002</v>
+        <v>922.1231556000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07741626016234479</v>
+        <v>0.07783399104406699</v>
       </c>
       <c r="T41">
-        <v>0.7301676711857922</v>
+        <v>0.7398150356597456</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.019443161755396</v>
+        <v>4.89395708271151</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0621843946264402</v>
+        <v>0.06204797055385006</v>
       </c>
       <c r="C42">
-        <v>2894.594786541021</v>
+        <v>2871.321477327241</v>
       </c>
       <c r="D42">
-        <v>4426.634786541021</v>
+        <v>4463.802477327241</v>
       </c>
       <c r="E42">
-        <v>-2064.86</v>
+        <v>-2004.419</v>
       </c>
       <c r="F42">
-        <v>2417.64</v>
+        <v>2478.081</v>
       </c>
       <c r="G42">
         <v>885.6</v>
@@ -4731,28 +4731,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M42">
-        <v>133.695492</v>
+        <v>137.0378793</v>
       </c>
       <c r="N42">
-        <v>520.6045080000001</v>
+        <v>517.2621207000002</v>
       </c>
       <c r="O42">
-        <v>156.1813524</v>
+        <v>155.1786362100001</v>
       </c>
       <c r="P42">
-        <v>364.4231556000001</v>
+        <v>362.0834844900002</v>
       </c>
       <c r="Q42">
-        <v>922.1231556000001</v>
+        <v>919.7834844900002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07783399104406699</v>
+        <v>0.07826588229466111</v>
       </c>
       <c r="T42">
-        <v>0.7398150356597456</v>
+        <v>0.7497894294379008</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.89395708271151</v>
+        <v>4.774592275816108</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06204797055385006</v>
+        <v>0.06191154648125992</v>
       </c>
       <c r="C43">
-        <v>2871.321477327241</v>
+        <v>2848.677600893452</v>
       </c>
       <c r="D43">
-        <v>4463.802477327241</v>
+        <v>4501.599600893452</v>
       </c>
       <c r="E43">
-        <v>-2004.419</v>
+        <v>-1943.978</v>
       </c>
       <c r="F43">
-        <v>2478.081</v>
+        <v>2538.522</v>
       </c>
       <c r="G43">
         <v>885.6</v>
@@ -4813,28 +4813,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M43">
-        <v>137.0378793</v>
+        <v>140.3802666</v>
       </c>
       <c r="N43">
-        <v>517.2621207000002</v>
+        <v>513.9197334000002</v>
       </c>
       <c r="O43">
-        <v>155.1786362100001</v>
+        <v>154.17592002</v>
       </c>
       <c r="P43">
-        <v>362.0834844900002</v>
+        <v>359.7438133800001</v>
       </c>
       <c r="Q43">
-        <v>919.7834844900002</v>
+        <v>917.4438133800002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07826588229466111</v>
+        <v>0.07871266634699986</v>
       </c>
       <c r="T43">
-        <v>0.7497894294379008</v>
+        <v>0.7601077678290959</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.774592275816108</v>
+        <v>4.660911507344295</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06191154648125992</v>
+        <v>0.06177512240866979</v>
       </c>
       <c r="C44">
-        <v>2848.677600893452</v>
+        <v>2826.679282896984</v>
       </c>
       <c r="D44">
-        <v>4501.599600893452</v>
+        <v>4540.042282896984</v>
       </c>
       <c r="E44">
-        <v>-1943.978</v>
+        <v>-1883.537</v>
       </c>
       <c r="F44">
-        <v>2538.522</v>
+        <v>2598.963</v>
       </c>
       <c r="G44">
         <v>885.6</v>
@@ -4895,28 +4895,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M44">
-        <v>140.3802666</v>
+        <v>143.7226539</v>
       </c>
       <c r="N44">
-        <v>513.9197334000002</v>
+        <v>510.5773461000002</v>
       </c>
       <c r="O44">
-        <v>154.17592002</v>
+        <v>153.17320383</v>
       </c>
       <c r="P44">
-        <v>359.7438133800001</v>
+        <v>357.4041422700001</v>
       </c>
       <c r="Q44">
-        <v>917.4438133800002</v>
+        <v>915.1041422700002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07871266634699985</v>
+        <v>0.07917512703275401</v>
       </c>
       <c r="T44">
-        <v>0.7601077678290958</v>
+        <v>0.7707881531813856</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.660911507344297</v>
+        <v>4.552518216475824</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06177512240866979</v>
+        <v>0.06240869833607965</v>
       </c>
       <c r="C45">
-        <v>2826.679282896984</v>
+        <v>2593.048220577784</v>
       </c>
       <c r="D45">
-        <v>4540.042282896984</v>
+        <v>4366.852220577784</v>
       </c>
       <c r="E45">
-        <v>-1883.537</v>
+        <v>-1823.096</v>
       </c>
       <c r="F45">
-        <v>2598.963</v>
+        <v>2659.404</v>
       </c>
       <c r="G45">
         <v>885.6</v>
@@ -4977,45 +4977,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M45">
-        <v>143.7226539</v>
+        <v>153.7135512</v>
       </c>
       <c r="N45">
-        <v>510.5773461000002</v>
+        <v>500.5864488000002</v>
       </c>
       <c r="O45">
-        <v>153.17320383</v>
+        <v>150.1759346400001</v>
       </c>
       <c r="P45">
-        <v>357.4041422700001</v>
+        <v>350.4105141600002</v>
       </c>
       <c r="Q45">
-        <v>915.1041422700002</v>
+        <v>908.1105141600002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07917512703275401</v>
+        <v>0.07965410417157079</v>
       </c>
       <c r="T45">
-        <v>0.7707881531813856</v>
+        <v>0.7818499808676856</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.552518216475824</v>
+        <v>4.256618853003249</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06240869833607965</v>
+        <v>0.06228977426348951</v>
       </c>
       <c r="C46">
-        <v>2593.048220577784</v>
+        <v>2564.100911284045</v>
       </c>
       <c r="D46">
-        <v>4366.852220577784</v>
+        <v>4398.345911284045</v>
       </c>
       <c r="E46">
-        <v>-1823.096</v>
+        <v>-1762.655</v>
       </c>
       <c r="F46">
-        <v>2659.404</v>
+        <v>2719.845</v>
       </c>
       <c r="G46">
         <v>885.6</v>
@@ -5059,28 +5059,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M46">
-        <v>153.7135512</v>
+        <v>157.207041</v>
       </c>
       <c r="N46">
-        <v>500.5864488000002</v>
+        <v>497.0929590000002</v>
       </c>
       <c r="O46">
-        <v>150.1759346400001</v>
+        <v>149.1278877000001</v>
       </c>
       <c r="P46">
-        <v>350.4105141600002</v>
+        <v>347.9650713000001</v>
       </c>
       <c r="Q46">
-        <v>908.1105141600002</v>
+        <v>905.6650713000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07965410417157079</v>
+        <v>0.08015049866089001</v>
       </c>
       <c r="T46">
-        <v>0.7818499808676856</v>
+        <v>0.7933140568334875</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.256618853003249</v>
+        <v>4.16202732293651</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06228977426348951</v>
+        <v>0.06217085019089937</v>
       </c>
       <c r="C47">
-        <v>2564.100911284045</v>
+        <v>2535.611166248241</v>
       </c>
       <c r="D47">
-        <v>4398.345911284045</v>
+        <v>4430.297166248241</v>
       </c>
       <c r="E47">
-        <v>-1762.655</v>
+        <v>-1702.213999999999</v>
       </c>
       <c r="F47">
-        <v>2719.845</v>
+        <v>2780.286000000001</v>
       </c>
       <c r="G47">
         <v>885.6</v>
@@ -5141,28 +5141,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M47">
-        <v>157.207041</v>
+        <v>160.7005308000001</v>
       </c>
       <c r="N47">
-        <v>497.0929590000002</v>
+        <v>493.5994692000002</v>
       </c>
       <c r="O47">
-        <v>149.1278877000001</v>
+        <v>148.0798407600001</v>
       </c>
       <c r="P47">
-        <v>347.9650713000001</v>
+        <v>345.5196284400001</v>
       </c>
       <c r="Q47">
-        <v>905.6650713000001</v>
+        <v>903.2196284400002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08015049866089001</v>
+        <v>0.08066527813129512</v>
       </c>
       <c r="T47">
-        <v>0.7933140568334875</v>
+        <v>0.80520272820543</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.16202732293651</v>
+        <v>4.071548468090063</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06217085019089937</v>
+        <v>0.06320342611830923</v>
       </c>
       <c r="C48">
-        <v>2535.611166248241</v>
+        <v>2212.31283148889</v>
       </c>
       <c r="D48">
-        <v>4430.297166248241</v>
+        <v>4167.439831488889</v>
       </c>
       <c r="E48">
-        <v>-1702.213999999999</v>
+        <v>-1641.773</v>
       </c>
       <c r="F48">
-        <v>2780.286000000001</v>
+        <v>2840.727</v>
       </c>
       <c r="G48">
         <v>885.6</v>
@@ -5223,45 +5223,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M48">
-        <v>160.7005308000001</v>
+        <v>174.1365651</v>
       </c>
       <c r="N48">
-        <v>493.5994692000002</v>
+        <v>480.1634349000002</v>
       </c>
       <c r="O48">
-        <v>148.0798407600001</v>
+        <v>144.04903047</v>
       </c>
       <c r="P48">
-        <v>345.5196284400001</v>
+        <v>336.1144044300001</v>
       </c>
       <c r="Q48">
-        <v>903.2196284400002</v>
+        <v>893.8144044300002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08066527813129512</v>
+        <v>0.08119948324209289</v>
       </c>
       <c r="T48">
-        <v>0.80520272820543</v>
+        <v>0.817540028685748</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.071548468090063</v>
+        <v>3.757395809571991</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06320342611830923</v>
+        <v>0.06310900204571909</v>
       </c>
       <c r="C49">
-        <v>2212.31283148889</v>
+        <v>2174.606050372458</v>
       </c>
       <c r="D49">
-        <v>4167.439831488889</v>
+        <v>4190.174050372459</v>
       </c>
       <c r="E49">
-        <v>-1641.773</v>
+        <v>-1581.331999999999</v>
       </c>
       <c r="F49">
-        <v>2840.727</v>
+        <v>2901.168000000001</v>
       </c>
       <c r="G49">
         <v>885.6</v>
@@ -5305,28 +5305,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M49">
-        <v>174.1365651</v>
+        <v>177.8415984</v>
       </c>
       <c r="N49">
-        <v>480.1634349000002</v>
+        <v>476.4584016000001</v>
       </c>
       <c r="O49">
-        <v>144.04903047</v>
+        <v>142.93752048</v>
       </c>
       <c r="P49">
-        <v>336.1144044300001</v>
+        <v>333.5208811200001</v>
       </c>
       <c r="Q49">
-        <v>893.8144044300002</v>
+        <v>891.2208811200002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08119948324209289</v>
+        <v>0.08175423470330595</v>
       </c>
       <c r="T49">
-        <v>0.817540028685748</v>
+        <v>0.8303518407230012</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.757395809571991</v>
+        <v>3.679116730205907</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06310900204571909</v>
+        <v>0.06301457797312895</v>
       </c>
       <c r="C50">
-        <v>2174.606050372459</v>
+        <v>2137.148669216631</v>
       </c>
       <c r="D50">
-        <v>4190.174050372459</v>
+        <v>4213.157669216631</v>
       </c>
       <c r="E50">
-        <v>-1581.332</v>
+        <v>-1520.891</v>
       </c>
       <c r="F50">
-        <v>2901.168</v>
+        <v>2961.609</v>
       </c>
       <c r="G50">
         <v>885.6</v>
@@ -5387,28 +5387,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M50">
-        <v>177.8415984</v>
+        <v>181.5466317</v>
       </c>
       <c r="N50">
-        <v>476.4584016000002</v>
+        <v>472.7533683000001</v>
       </c>
       <c r="O50">
-        <v>142.93752048</v>
+        <v>141.82601049</v>
       </c>
       <c r="P50">
-        <v>333.5208811200001</v>
+        <v>330.9273578100001</v>
       </c>
       <c r="Q50">
-        <v>891.2208811200002</v>
+        <v>888.6273578100001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08175423470330595</v>
+        <v>0.08233074112378226</v>
       </c>
       <c r="T50">
-        <v>0.8303518407230012</v>
+        <v>0.8436660767617151</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.679116730205907</v>
+        <v>3.604032715303746</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06301457797312895</v>
+        <v>0.06292015390053882</v>
       </c>
       <c r="C51">
-        <v>2137.148669216631</v>
+        <v>2099.944814624494</v>
       </c>
       <c r="D51">
-        <v>4213.157669216631</v>
+        <v>4236.394814624494</v>
       </c>
       <c r="E51">
-        <v>-1520.891</v>
+        <v>-1460.45</v>
       </c>
       <c r="F51">
-        <v>2961.609</v>
+        <v>3022.05</v>
       </c>
       <c r="G51">
         <v>885.6</v>
@@ -5469,28 +5469,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M51">
-        <v>181.5466317</v>
+        <v>185.251665</v>
       </c>
       <c r="N51">
-        <v>472.7533683000001</v>
+        <v>469.0483350000002</v>
       </c>
       <c r="O51">
-        <v>141.82601049</v>
+        <v>140.7145005</v>
       </c>
       <c r="P51">
-        <v>330.9273578100001</v>
+        <v>328.3338345000001</v>
       </c>
       <c r="Q51">
-        <v>888.6273578100001</v>
+        <v>886.0338345000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08233074112378226</v>
+        <v>0.08293030780107764</v>
       </c>
       <c r="T51">
-        <v>0.8436660767617151</v>
+        <v>0.8575128822419779</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.604032715303746</v>
+        <v>3.531952060997671</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06292015390053882</v>
+        <v>0.06382532982794868</v>
       </c>
       <c r="C52">
-        <v>2099.944814624494</v>
+        <v>1826.765260500712</v>
       </c>
       <c r="D52">
-        <v>4236.394814624494</v>
+        <v>4023.656260500713</v>
       </c>
       <c r="E52">
-        <v>-1460.45</v>
+        <v>-1400.009</v>
       </c>
       <c r="F52">
-        <v>3022.05</v>
+        <v>3082.491</v>
       </c>
       <c r="G52">
         <v>885.6</v>
@@ -5551,45 +5551,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M52">
-        <v>185.251665</v>
+        <v>197.5876731</v>
       </c>
       <c r="N52">
-        <v>469.0483350000002</v>
+        <v>456.7123269000001</v>
       </c>
       <c r="O52">
-        <v>140.7145005</v>
+        <v>137.01369807</v>
       </c>
       <c r="P52">
-        <v>328.3338345000001</v>
+        <v>319.6986288300001</v>
       </c>
       <c r="Q52">
-        <v>886.0338345000002</v>
+        <v>877.3986288300001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08293030780107764</v>
+        <v>0.08355434658765037</v>
       </c>
       <c r="T52">
-        <v>0.8575128822419779</v>
+        <v>0.8719248634561287</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.531952060997671</v>
+        <v>3.311441395784118</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06382532982794868</v>
+        <v>0.06375050575535855</v>
       </c>
       <c r="C53">
-        <v>1826.765260500712</v>
+        <v>1783.09628643784</v>
       </c>
       <c r="D53">
-        <v>4023.656260500713</v>
+        <v>4040.428286437841</v>
       </c>
       <c r="E53">
-        <v>-1400.009</v>
+        <v>-1339.568</v>
       </c>
       <c r="F53">
-        <v>3082.491</v>
+        <v>3142.932</v>
       </c>
       <c r="G53">
         <v>885.6</v>
@@ -5633,28 +5633,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M53">
-        <v>197.5876731</v>
+        <v>201.4619412</v>
       </c>
       <c r="N53">
-        <v>456.7123269000001</v>
+        <v>452.8380588000001</v>
       </c>
       <c r="O53">
-        <v>137.01369807</v>
+        <v>135.85141764</v>
       </c>
       <c r="P53">
-        <v>319.6986288300001</v>
+        <v>316.9866411600001</v>
       </c>
       <c r="Q53">
-        <v>877.3986288300001</v>
+        <v>874.6866411600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08355434658765037</v>
+        <v>0.08420438699033031</v>
       </c>
       <c r="T53">
-        <v>0.8719248634561287</v>
+        <v>0.8869373438875359</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.311441395784118</v>
+        <v>3.247759830480577</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06375050575535855</v>
+        <v>0.06367568168276841</v>
       </c>
       <c r="C54">
-        <v>1783.09628643784</v>
+        <v>1739.567721150253</v>
       </c>
       <c r="D54">
-        <v>4040.428286437841</v>
+        <v>4057.340721150253</v>
       </c>
       <c r="E54">
-        <v>-1339.568</v>
+        <v>-1279.126999999999</v>
       </c>
       <c r="F54">
-        <v>3142.932</v>
+        <v>3203.373000000001</v>
       </c>
       <c r="G54">
         <v>885.6</v>
@@ -5715,28 +5715,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M54">
-        <v>201.4619412</v>
+        <v>205.3362093</v>
       </c>
       <c r="N54">
-        <v>452.8380588000001</v>
+        <v>448.9637907000001</v>
       </c>
       <c r="O54">
-        <v>135.85141764</v>
+        <v>134.68913721</v>
       </c>
       <c r="P54">
-        <v>316.9866411600001</v>
+        <v>314.2746534900001</v>
       </c>
       <c r="Q54">
-        <v>874.6866411600001</v>
+        <v>871.9746534900002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08420438699033031</v>
+        <v>0.0848820886867413</v>
       </c>
       <c r="T54">
-        <v>0.8869373438875359</v>
+        <v>0.902588653273471</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.247759830480577</v>
+        <v>3.186481343113019</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06367568168276841</v>
+        <v>0.06360085761017828</v>
       </c>
       <c r="C55">
-        <v>1739.567721150253</v>
+        <v>1696.181335219445</v>
       </c>
       <c r="D55">
-        <v>4057.340721150253</v>
+        <v>4074.395335219445</v>
       </c>
       <c r="E55">
-        <v>-1279.126999999999</v>
+        <v>-1218.686</v>
       </c>
       <c r="F55">
-        <v>3203.373000000001</v>
+        <v>3263.814</v>
       </c>
       <c r="G55">
         <v>885.6</v>
@@ -5797,28 +5797,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M55">
-        <v>205.3362093</v>
+        <v>209.2104774</v>
       </c>
       <c r="N55">
-        <v>448.9637907000001</v>
+        <v>445.0895226000001</v>
       </c>
       <c r="O55">
-        <v>134.68913721</v>
+        <v>133.52685678</v>
       </c>
       <c r="P55">
-        <v>314.2746534900001</v>
+        <v>311.5626658200001</v>
       </c>
       <c r="Q55">
-        <v>871.9746534900002</v>
+        <v>869.2626658200002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0848820886867413</v>
+        <v>0.08558925567430059</v>
       </c>
       <c r="T55">
-        <v>0.902588653273471</v>
+        <v>0.9189204543718381</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.186481343113019</v>
+        <v>3.127472429351667</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06360085761017828</v>
+        <v>0.06352603353758814</v>
       </c>
       <c r="C56">
-        <v>1696.181335219445</v>
+        <v>1652.938929122415</v>
       </c>
       <c r="D56">
-        <v>4074.395335219445</v>
+        <v>4091.593929122415</v>
       </c>
       <c r="E56">
-        <v>-1218.686</v>
+        <v>-1158.244999999999</v>
       </c>
       <c r="F56">
-        <v>3263.814</v>
+        <v>3324.255000000001</v>
       </c>
       <c r="G56">
         <v>885.6</v>
@@ -5879,28 +5879,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M56">
-        <v>209.2104774</v>
+        <v>213.0847455000001</v>
       </c>
       <c r="N56">
-        <v>445.0895226000001</v>
+        <v>441.2152545000001</v>
       </c>
       <c r="O56">
-        <v>133.52685678</v>
+        <v>132.36457635</v>
       </c>
       <c r="P56">
-        <v>311.5626658200001</v>
+        <v>308.8506781500001</v>
       </c>
       <c r="Q56">
-        <v>869.2626658200002</v>
+        <v>866.5506781500002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08558925567430059</v>
+        <v>0.08632785230575141</v>
       </c>
       <c r="T56">
-        <v>0.9189204543718381</v>
+        <v>0.9359781132967994</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.127472429351667</v>
+        <v>3.070609294272546</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06352603353758814</v>
+        <v>0.06345120946499799</v>
       </c>
       <c r="C57">
-        <v>1652.938929122415</v>
+        <v>1609.842333865281</v>
       </c>
       <c r="D57">
-        <v>4091.593929122415</v>
+        <v>4108.938333865281</v>
       </c>
       <c r="E57">
-        <v>-1158.244999999999</v>
+        <v>-1097.804</v>
       </c>
       <c r="F57">
-        <v>3324.255000000001</v>
+        <v>3384.696</v>
       </c>
       <c r="G57">
         <v>885.6</v>
@@ -5961,28 +5961,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M57">
-        <v>213.0847455000001</v>
+        <v>216.9590136</v>
       </c>
       <c r="N57">
-        <v>441.2152545000001</v>
+        <v>437.3409864000001</v>
       </c>
       <c r="O57">
-        <v>132.36457635</v>
+        <v>131.20229592</v>
       </c>
       <c r="P57">
-        <v>308.8506781500001</v>
+        <v>306.1386904800001</v>
       </c>
       <c r="Q57">
-        <v>866.5506781500002</v>
+        <v>863.8386904800002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08632785230575141</v>
+        <v>0.08710002151135909</v>
       </c>
       <c r="T57">
-        <v>0.9359781132967994</v>
+        <v>0.9538111203547134</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.070609294272546</v>
+        <v>3.01577698544625</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06345120946499799</v>
+        <v>0.06648858539240786</v>
       </c>
       <c r="C58">
-        <v>1609.842333865281</v>
+        <v>946.1512737101793</v>
       </c>
       <c r="D58">
-        <v>4108.938333865281</v>
+        <v>3505.68827371018</v>
       </c>
       <c r="E58">
-        <v>-1097.804</v>
+        <v>-1037.362999999999</v>
       </c>
       <c r="F58">
-        <v>3384.696</v>
+        <v>3445.137000000001</v>
       </c>
       <c r="G58">
         <v>885.6</v>
@@ -6043,45 +6043,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M58">
-        <v>216.9590136</v>
+        <v>247.7053503000001</v>
       </c>
       <c r="N58">
-        <v>437.3409864000001</v>
+        <v>406.5946497000001</v>
       </c>
       <c r="O58">
-        <v>131.20229592</v>
+        <v>121.97839491</v>
       </c>
       <c r="P58">
-        <v>306.1386904800001</v>
+        <v>284.6162547900001</v>
       </c>
       <c r="Q58">
-        <v>863.8386904800002</v>
+        <v>842.3162547900001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08710002151135909</v>
+        <v>0.08790810556373921</v>
       </c>
       <c r="T58">
-        <v>0.9538111203547134</v>
+        <v>0.9724735696013675</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.01577698544625</v>
+        <v>2.641444761720191</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06648858539240786</v>
+        <v>0.06646836131981773</v>
       </c>
       <c r="C59">
-        <v>946.1512737101793</v>
+        <v>889.1406034314759</v>
       </c>
       <c r="D59">
-        <v>3505.68827371018</v>
+        <v>3509.118603431476</v>
       </c>
       <c r="E59">
-        <v>-1037.362999999999</v>
+        <v>-976.9219999999996</v>
       </c>
       <c r="F59">
-        <v>3445.137000000001</v>
+        <v>3505.578</v>
       </c>
       <c r="G59">
         <v>885.6</v>
@@ -6125,28 +6125,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M59">
-        <v>247.7053503000001</v>
+        <v>252.0510582000001</v>
       </c>
       <c r="N59">
-        <v>406.5946497000001</v>
+        <v>402.2489418000001</v>
       </c>
       <c r="O59">
-        <v>121.97839491</v>
+        <v>120.67468254</v>
       </c>
       <c r="P59">
-        <v>284.6162547900001</v>
+        <v>281.5742592600001</v>
       </c>
       <c r="Q59">
-        <v>842.3162547900001</v>
+        <v>839.2742592600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08790810556373921</v>
+        <v>0.08875466980908983</v>
       </c>
       <c r="T59">
-        <v>0.9724735696013675</v>
+        <v>0.9920247069073862</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.641444761720191</v>
+        <v>2.59590261065605</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06646836131981772</v>
+        <v>0.06644813724722759</v>
       </c>
       <c r="C60">
-        <v>889.1406034314791</v>
+        <v>832.1366529102488</v>
       </c>
       <c r="D60">
-        <v>3509.118603431479</v>
+        <v>3512.555652910249</v>
       </c>
       <c r="E60">
-        <v>-976.922</v>
+        <v>-916.4809999999998</v>
       </c>
       <c r="F60">
-        <v>3505.578</v>
+        <v>3566.019</v>
       </c>
       <c r="G60">
         <v>885.6</v>
@@ -6207,28 +6207,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M60">
-        <v>252.0510582</v>
+        <v>256.3967661</v>
       </c>
       <c r="N60">
-        <v>402.2489418000001</v>
+        <v>397.9032339000001</v>
       </c>
       <c r="O60">
-        <v>120.67468254</v>
+        <v>119.37097017</v>
       </c>
       <c r="P60">
-        <v>281.5742592600001</v>
+        <v>278.5322637300001</v>
       </c>
       <c r="Q60">
-        <v>839.2742592600001</v>
+        <v>836.2322637300001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0887546698090898</v>
+        <v>0.08964252987128679</v>
       </c>
       <c r="T60">
-        <v>0.992024706907386</v>
+        <v>1.012529558228332</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.59590261065605</v>
+        <v>2.551904261322897</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06644813724722759</v>
+        <v>0.06642791317463745</v>
       </c>
       <c r="C61">
-        <v>832.1366529102488</v>
+        <v>775.139441911102</v>
       </c>
       <c r="D61">
-        <v>3512.555652910249</v>
+        <v>3515.999441911102</v>
       </c>
       <c r="E61">
-        <v>-916.4809999999998</v>
+        <v>-856.04</v>
       </c>
       <c r="F61">
-        <v>3566.019</v>
+        <v>3626.46</v>
       </c>
       <c r="G61">
         <v>885.6</v>
@@ -6289,28 +6289,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M61">
-        <v>256.3967661</v>
+        <v>260.742474</v>
       </c>
       <c r="N61">
-        <v>397.9032339000001</v>
+        <v>393.5575260000002</v>
       </c>
       <c r="O61">
-        <v>119.37097017</v>
+        <v>118.0672578</v>
       </c>
       <c r="P61">
-        <v>278.5322637300001</v>
+        <v>275.4902682000001</v>
       </c>
       <c r="Q61">
-        <v>836.2322637300001</v>
+        <v>833.1902682000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08964252987128679</v>
+        <v>0.09057478293659363</v>
       </c>
       <c r="T61">
-        <v>1.012529558228332</v>
+        <v>1.034059652115326</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.551904261322897</v>
+        <v>2.509372523634182</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06642791317463745</v>
+        <v>0.06807298910204732</v>
       </c>
       <c r="C62">
-        <v>775.139441911102</v>
+        <v>455.0078356716908</v>
       </c>
       <c r="D62">
-        <v>3515.999441911102</v>
+        <v>3256.308835671691</v>
       </c>
       <c r="E62">
-        <v>-856.04</v>
+        <v>-795.5989999999997</v>
       </c>
       <c r="F62">
-        <v>3626.46</v>
+        <v>3686.901</v>
       </c>
       <c r="G62">
         <v>885.6</v>
@@ -6371,45 +6371,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M62">
-        <v>260.742474</v>
+        <v>279.4670958</v>
       </c>
       <c r="N62">
-        <v>393.5575260000002</v>
+        <v>374.8329042000001</v>
       </c>
       <c r="O62">
-        <v>118.0672578</v>
+        <v>112.44987126</v>
       </c>
       <c r="P62">
-        <v>275.4902682000001</v>
+        <v>262.3830329400001</v>
       </c>
       <c r="Q62">
-        <v>833.1902682000002</v>
+        <v>820.0830329400002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09057478293659363</v>
+        <v>0.09155484385140336</v>
       </c>
       <c r="T62">
-        <v>1.034059652115326</v>
+        <v>1.05669385338114</v>
       </c>
       <c r="U62">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.509372523634182</v>
+        <v>2.341241633928341</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06807298910204732</v>
+        <v>0.06808006502945718</v>
       </c>
       <c r="C63">
-        <v>455.0078356716908</v>
+        <v>393.5326643209851</v>
       </c>
       <c r="D63">
-        <v>3256.308835671691</v>
+        <v>3255.274664320985</v>
       </c>
       <c r="E63">
-        <v>-795.5989999999997</v>
+        <v>-735.1579999999999</v>
       </c>
       <c r="F63">
-        <v>3686.901</v>
+        <v>3747.342</v>
       </c>
       <c r="G63">
         <v>885.6</v>
@@ -6453,28 +6453,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M63">
-        <v>279.4670958</v>
+        <v>284.0485236</v>
       </c>
       <c r="N63">
-        <v>374.8329042000001</v>
+        <v>370.2514764000002</v>
       </c>
       <c r="O63">
-        <v>112.44987126</v>
+        <v>111.07544292</v>
       </c>
       <c r="P63">
-        <v>262.3830329400001</v>
+        <v>259.1760334800001</v>
       </c>
       <c r="Q63">
-        <v>820.0830329400002</v>
+        <v>816.8760334800002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09155484385140336</v>
+        <v>0.09258648691962415</v>
       </c>
       <c r="T63">
-        <v>1.05669385338114</v>
+        <v>1.080519328397786</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.341241633928341</v>
+        <v>2.303479672090787</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06808006502945718</v>
+        <v>0.06808714095686705</v>
       </c>
       <c r="C64">
-        <v>393.5326643209851</v>
+        <v>332.0581496468285</v>
       </c>
       <c r="D64">
-        <v>3255.274664320985</v>
+        <v>3254.241149646828</v>
       </c>
       <c r="E64">
-        <v>-735.1579999999999</v>
+        <v>-674.7169999999996</v>
       </c>
       <c r="F64">
-        <v>3747.342</v>
+        <v>3807.783</v>
       </c>
       <c r="G64">
         <v>885.6</v>
@@ -6535,28 +6535,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M64">
-        <v>284.0485236</v>
+        <v>288.6299514</v>
       </c>
       <c r="N64">
-        <v>370.2514764000002</v>
+        <v>365.6700486000001</v>
       </c>
       <c r="O64">
-        <v>111.07544292</v>
+        <v>109.70101458</v>
       </c>
       <c r="P64">
-        <v>259.1760334800001</v>
+        <v>255.9690340200001</v>
       </c>
       <c r="Q64">
-        <v>816.8760334800002</v>
+        <v>813.6690340200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09258648691962415</v>
+        <v>0.09367389447801902</v>
       </c>
       <c r="T64">
-        <v>1.080519328397786</v>
+        <v>1.105632666928846</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.303479672090787</v>
+        <v>2.26691650269252</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06808714095686705</v>
+        <v>0.0680942168842769</v>
       </c>
       <c r="C65">
-        <v>332.0581496468285</v>
+        <v>270.5842910239589</v>
       </c>
       <c r="D65">
-        <v>3254.241149646828</v>
+        <v>3253.208291023959</v>
       </c>
       <c r="E65">
-        <v>-674.7169999999996</v>
+        <v>-614.2759999999998</v>
       </c>
       <c r="F65">
-        <v>3807.783</v>
+        <v>3868.224</v>
       </c>
       <c r="G65">
         <v>885.6</v>
@@ -6617,28 +6617,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M65">
-        <v>288.6299514</v>
+        <v>293.2113792</v>
       </c>
       <c r="N65">
-        <v>365.6700486000001</v>
+        <v>361.0886208000002</v>
       </c>
       <c r="O65">
-        <v>109.70101458</v>
+        <v>108.3265862400001</v>
       </c>
       <c r="P65">
-        <v>255.9690340200001</v>
+        <v>252.7620345600001</v>
       </c>
       <c r="Q65">
-        <v>813.6690340200001</v>
+        <v>810.4620345600001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09367389447801902</v>
+        <v>0.09482171356743584</v>
       </c>
       <c r="T65">
-        <v>1.105632666928846</v>
+        <v>1.132141190933853</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.26691650269252</v>
+        <v>2.23149593233795</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0680942168842769</v>
+        <v>0.06810129281168677</v>
       </c>
       <c r="C66">
-        <v>270.5842910239589</v>
+        <v>209.1110878279001</v>
       </c>
       <c r="D66">
-        <v>3253.208291023959</v>
+        <v>3252.1760878279</v>
       </c>
       <c r="E66">
-        <v>-614.2759999999998</v>
+        <v>-553.8349999999996</v>
       </c>
       <c r="F66">
-        <v>3868.224</v>
+        <v>3928.665</v>
       </c>
       <c r="G66">
         <v>885.6</v>
@@ -6699,28 +6699,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M66">
-        <v>293.2113792</v>
+        <v>297.792807</v>
       </c>
       <c r="N66">
-        <v>361.0886208000002</v>
+        <v>356.5071930000001</v>
       </c>
       <c r="O66">
-        <v>108.3265862400001</v>
+        <v>106.9521579</v>
       </c>
       <c r="P66">
-        <v>252.7620345600001</v>
+        <v>249.5550351000001</v>
       </c>
       <c r="Q66">
-        <v>810.4620345600001</v>
+        <v>807.2550351000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09482171356743584</v>
+        <v>0.09603512231910503</v>
       </c>
       <c r="T66">
-        <v>1.132141190933853</v>
+        <v>1.160164487739146</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.23149593233795</v>
+        <v>2.197165225686597</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06810129281168677</v>
+        <v>0.06810836873909663</v>
       </c>
       <c r="C67">
-        <v>209.1110878279001</v>
+        <v>147.6385394349768</v>
       </c>
       <c r="D67">
-        <v>3252.1760878279</v>
+        <v>3251.144539434977</v>
       </c>
       <c r="E67">
-        <v>-553.8349999999996</v>
+        <v>-493.3939999999998</v>
       </c>
       <c r="F67">
-        <v>3928.665</v>
+        <v>3989.106</v>
       </c>
       <c r="G67">
         <v>885.6</v>
@@ -6781,28 +6781,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M67">
-        <v>297.792807</v>
+        <v>302.3742348000001</v>
       </c>
       <c r="N67">
-        <v>356.5071930000001</v>
+        <v>351.9257652000001</v>
       </c>
       <c r="O67">
-        <v>106.9521579</v>
+        <v>105.57772956</v>
       </c>
       <c r="P67">
-        <v>249.5550351000001</v>
+        <v>246.3480356400001</v>
       </c>
       <c r="Q67">
-        <v>807.2550351000002</v>
+        <v>804.0480356400001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09603512231910503</v>
+        <v>0.09731990805616655</v>
       </c>
       <c r="T67">
-        <v>1.160164487739146</v>
+        <v>1.189836213768281</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.197165225686597</v>
+        <v>2.163874843479224</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06810836873909663</v>
+        <v>0.06811544466650649</v>
       </c>
       <c r="C68">
-        <v>147.6385394349768</v>
+        <v>86.16664522230076</v>
       </c>
       <c r="D68">
-        <v>3251.144539434977</v>
+        <v>3250.113645222301</v>
       </c>
       <c r="E68">
-        <v>-493.3939999999998</v>
+        <v>-432.9529999999995</v>
       </c>
       <c r="F68">
-        <v>3989.106</v>
+        <v>4049.547</v>
       </c>
       <c r="G68">
         <v>885.6</v>
@@ -6863,28 +6863,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M68">
-        <v>302.3742348000001</v>
+        <v>306.9556626</v>
       </c>
       <c r="N68">
-        <v>351.9257652000001</v>
+        <v>347.3443374000001</v>
       </c>
       <c r="O68">
-        <v>105.57772956</v>
+        <v>104.20330122</v>
       </c>
       <c r="P68">
-        <v>246.3480356400001</v>
+        <v>243.1410361800001</v>
       </c>
       <c r="Q68">
-        <v>804.0480356400001</v>
+        <v>800.8410361800002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09731990805616655</v>
+        <v>0.09868255959547423</v>
       </c>
       <c r="T68">
-        <v>1.189836213768281</v>
+        <v>1.221306226223423</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.163874843479224</v>
+        <v>2.13157820402431</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06811544466650649</v>
+        <v>0.06812252059391635</v>
       </c>
       <c r="C69">
-        <v>86.16664522230076</v>
+        <v>24.69540456777122</v>
       </c>
       <c r="D69">
-        <v>3250.113645222301</v>
+        <v>3249.083404567772</v>
       </c>
       <c r="E69">
-        <v>-432.9529999999995</v>
+        <v>-372.5119999999997</v>
       </c>
       <c r="F69">
-        <v>4049.547</v>
+        <v>4109.988</v>
       </c>
       <c r="G69">
         <v>885.6</v>
@@ -6945,28 +6945,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M69">
-        <v>306.9556626</v>
+        <v>311.5370904000001</v>
       </c>
       <c r="N69">
-        <v>347.3443374000001</v>
+        <v>342.7629096000001</v>
       </c>
       <c r="O69">
-        <v>104.20330122</v>
+        <v>102.82887288</v>
       </c>
       <c r="P69">
-        <v>243.1410361800001</v>
+        <v>239.9340367200001</v>
       </c>
       <c r="Q69">
-        <v>800.8410361800002</v>
+        <v>797.6340367200002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09868255959547423</v>
+        <v>0.1001303768559886</v>
       </c>
       <c r="T69">
-        <v>1.221306226223423</v>
+        <v>1.254743114457012</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.13157820402431</v>
+        <v>2.100231465729835</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06812252059391635</v>
+        <v>0.06812959652132622</v>
       </c>
       <c r="C70">
-        <v>24.69540456777122</v>
+        <v>-36.77518314991903</v>
       </c>
       <c r="D70">
-        <v>3249.083404567772</v>
+        <v>3248.053816850082</v>
       </c>
       <c r="E70">
-        <v>-372.5119999999997</v>
+        <v>-312.070999999999</v>
       </c>
       <c r="F70">
-        <v>4109.988</v>
+        <v>4170.429000000001</v>
       </c>
       <c r="G70">
         <v>885.6</v>
@@ -7027,28 +7027,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M70">
-        <v>311.5370904000001</v>
+        <v>316.1185182000001</v>
       </c>
       <c r="N70">
-        <v>342.7629096000001</v>
+        <v>338.1814818000001</v>
       </c>
       <c r="O70">
-        <v>102.82887288</v>
+        <v>101.45444454</v>
       </c>
       <c r="P70">
-        <v>239.9340367200001</v>
+        <v>236.7270372600001</v>
       </c>
       <c r="Q70">
-        <v>797.6340367200002</v>
+        <v>794.4270372600001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1001303768559886</v>
+        <v>0.1016716016816975</v>
       </c>
       <c r="T70">
-        <v>1.254743114457012</v>
+        <v>1.290337221286316</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.100231465729835</v>
+        <v>2.069793328545344</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06812959652132622</v>
+        <v>0.06813667244873609</v>
       </c>
       <c r="C71">
-        <v>-36.77518314991903</v>
+        <v>-98.24511855129094</v>
       </c>
       <c r="D71">
-        <v>3248.053816850082</v>
+        <v>3247.024881448709</v>
       </c>
       <c r="E71">
-        <v>-312.070999999999</v>
+        <v>-251.6299999999992</v>
       </c>
       <c r="F71">
-        <v>4170.429000000001</v>
+        <v>4230.870000000001</v>
       </c>
       <c r="G71">
         <v>885.6</v>
@@ -7109,28 +7109,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M71">
-        <v>316.1185182000001</v>
+        <v>320.6999460000001</v>
       </c>
       <c r="N71">
-        <v>338.1814818000001</v>
+        <v>333.6000540000001</v>
       </c>
       <c r="O71">
-        <v>101.45444454</v>
+        <v>100.0800162</v>
       </c>
       <c r="P71">
-        <v>236.7270372600001</v>
+        <v>233.5200378000001</v>
       </c>
       <c r="Q71">
-        <v>794.4270372600001</v>
+        <v>791.2200378000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1016716016816975</v>
+        <v>0.1033155748291203</v>
       </c>
       <c r="T71">
-        <v>1.290337221286316</v>
+        <v>1.328304268570907</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.069793328545344</v>
+        <v>2.040224852423268</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06813667244873609</v>
+        <v>0.06814374837614595</v>
       </c>
       <c r="C72">
-        <v>-98.24511855129094</v>
+        <v>-159.7144022560833</v>
       </c>
       <c r="D72">
-        <v>3247.024881448709</v>
+        <v>3245.996597743917</v>
       </c>
       <c r="E72">
-        <v>-251.6299999999992</v>
+        <v>-191.1889999999994</v>
       </c>
       <c r="F72">
-        <v>4230.870000000001</v>
+        <v>4291.311000000001</v>
       </c>
       <c r="G72">
         <v>885.6</v>
@@ -7191,28 +7191,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M72">
-        <v>320.6999460000001</v>
+        <v>325.2813738000001</v>
       </c>
       <c r="N72">
-        <v>333.6000540000001</v>
+        <v>329.0186262000001</v>
       </c>
       <c r="O72">
-        <v>100.0800162</v>
+        <v>98.70558786000002</v>
       </c>
       <c r="P72">
-        <v>233.5200378000001</v>
+        <v>230.31303834</v>
       </c>
       <c r="Q72">
-        <v>791.2200378000001</v>
+        <v>788.0130383400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1033155748291203</v>
+        <v>0.105072925434986</v>
       </c>
       <c r="T72">
-        <v>1.328304268570907</v>
+        <v>1.368889732909608</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.040224852423268</v>
+        <v>2.011489291121531</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06814374837614595</v>
+        <v>0.07530762430355581</v>
       </c>
       <c r="C73">
-        <v>-159.7144022560824</v>
+        <v>-1008.220095225274</v>
       </c>
       <c r="D73">
-        <v>3245.996597743917</v>
+        <v>2457.931904774726</v>
       </c>
       <c r="E73">
-        <v>-191.1890000000003</v>
+        <v>-130.7479999999996</v>
       </c>
       <c r="F73">
-        <v>4291.311</v>
+        <v>4351.752</v>
       </c>
       <c r="G73">
         <v>885.6</v>
@@ -7273,45 +7273,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M73">
-        <v>325.2813738</v>
+        <v>391.65768</v>
       </c>
       <c r="N73">
-        <v>329.0186262000002</v>
+        <v>262.6423200000002</v>
       </c>
       <c r="O73">
-        <v>98.70558786000005</v>
+        <v>78.79269600000005</v>
       </c>
       <c r="P73">
-        <v>230.3130383400002</v>
+        <v>183.8496240000001</v>
       </c>
       <c r="Q73">
-        <v>788.0130383400002</v>
+        <v>741.5496240000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.105072925434986</v>
+        <v>0.1069558010841279</v>
       </c>
       <c r="T73">
-        <v>1.368889732909607</v>
+        <v>1.412374158986787</v>
       </c>
       <c r="U73">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
         <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.011489291121532</v>
+        <v>1.670591522678682</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07530762430355581</v>
+        <v>0.07541410023096567</v>
       </c>
       <c r="C74">
-        <v>-1008.220095225274</v>
+        <v>-1077.498459083371</v>
       </c>
       <c r="D74">
-        <v>2457.931904774726</v>
+        <v>2449.09454091663</v>
       </c>
       <c r="E74">
-        <v>-130.7479999999996</v>
+        <v>-70.30699999999979</v>
       </c>
       <c r="F74">
-        <v>4351.752</v>
+        <v>4412.193</v>
       </c>
       <c r="G74">
         <v>885.6</v>
@@ -7355,28 +7355,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M74">
-        <v>391.65768</v>
+        <v>397.09737</v>
       </c>
       <c r="N74">
-        <v>262.6423200000002</v>
+        <v>257.2026300000002</v>
       </c>
       <c r="O74">
-        <v>78.79269600000005</v>
+        <v>77.16078900000005</v>
       </c>
       <c r="P74">
-        <v>183.8496240000001</v>
+        <v>180.0418410000001</v>
       </c>
       <c r="Q74">
-        <v>741.5496240000002</v>
+        <v>737.7418410000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1069558010841279</v>
+        <v>0.1089781490035766</v>
       </c>
       <c r="T74">
-        <v>1.412374158986787</v>
+        <v>1.459079653662276</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.670591522678682</v>
+        <v>1.647706707299522</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07541410023096567</v>
+        <v>0.07552057615837553</v>
       </c>
       <c r="C75">
-        <v>-1077.498459083371</v>
+        <v>-1146.713502061841</v>
       </c>
       <c r="D75">
-        <v>2449.09454091663</v>
+        <v>2440.320497938159</v>
       </c>
       <c r="E75">
-        <v>-70.30699999999979</v>
+        <v>-9.865999999999985</v>
       </c>
       <c r="F75">
-        <v>4412.193</v>
+        <v>4472.634</v>
       </c>
       <c r="G75">
         <v>885.6</v>
@@ -7437,28 +7437,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M75">
-        <v>397.09737</v>
+        <v>402.53706</v>
       </c>
       <c r="N75">
-        <v>257.2026300000002</v>
+        <v>251.7629400000002</v>
       </c>
       <c r="O75">
-        <v>77.16078900000005</v>
+        <v>75.52888200000005</v>
       </c>
       <c r="P75">
-        <v>180.0418410000001</v>
+        <v>176.2340580000001</v>
       </c>
       <c r="Q75">
-        <v>737.7418410000001</v>
+        <v>733.9340580000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1089781490035766</v>
+        <v>0.1111560621475982</v>
       </c>
       <c r="T75">
-        <v>1.459079653662276</v>
+        <v>1.509377878697418</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.647706707299522</v>
+        <v>1.625440400444123</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07552057615837553</v>
+        <v>0.07562705208578539</v>
       </c>
       <c r="C76">
-        <v>-1146.713502061841</v>
+        <v>-1215.865902284967</v>
       </c>
       <c r="D76">
-        <v>2440.320497938159</v>
+        <v>2431.609097715034</v>
       </c>
       <c r="E76">
-        <v>-9.865999999999985</v>
+        <v>50.57500000000073</v>
       </c>
       <c r="F76">
-        <v>4472.634</v>
+        <v>4533.075000000001</v>
       </c>
       <c r="G76">
         <v>885.6</v>
@@ -7519,28 +7519,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M76">
-        <v>402.53706</v>
+        <v>407.97675</v>
       </c>
       <c r="N76">
-        <v>251.7629400000002</v>
+        <v>246.3232500000001</v>
       </c>
       <c r="O76">
-        <v>75.52888200000005</v>
+        <v>73.89697500000004</v>
       </c>
       <c r="P76">
-        <v>176.2340580000001</v>
+        <v>172.4262750000001</v>
       </c>
       <c r="Q76">
-        <v>733.9340580000002</v>
+        <v>730.1262750000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1111560621475982</v>
+        <v>0.1135082083431416</v>
       </c>
       <c r="T76">
-        <v>1.509377878697418</v>
+        <v>1.563699961735371</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.625440400444123</v>
+        <v>1.603767861771535</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07562705208578539</v>
+        <v>0.07573352801319526</v>
       </c>
       <c r="C77">
-        <v>-1215.865902284967</v>
+        <v>-1284.956328228455</v>
       </c>
       <c r="D77">
-        <v>2431.609097715034</v>
+        <v>2422.959671771545</v>
       </c>
       <c r="E77">
-        <v>50.57500000000073</v>
+        <v>111.0160000000005</v>
       </c>
       <c r="F77">
-        <v>4533.075000000001</v>
+        <v>4593.516000000001</v>
       </c>
       <c r="G77">
         <v>885.6</v>
@@ -7601,28 +7601,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M77">
-        <v>407.97675</v>
+        <v>413.41644</v>
       </c>
       <c r="N77">
-        <v>246.3232500000001</v>
+        <v>240.8835600000002</v>
       </c>
       <c r="O77">
-        <v>73.89697500000004</v>
+        <v>72.26506800000004</v>
       </c>
       <c r="P77">
-        <v>172.4262750000001</v>
+        <v>168.6184920000001</v>
       </c>
       <c r="Q77">
-        <v>730.1262750000001</v>
+        <v>726.3184920000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1135082083431416</v>
+        <v>0.1160563667216469</v>
       </c>
       <c r="T77">
-        <v>1.563699961735371</v>
+        <v>1.622548885026488</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.603767861771535</v>
+        <v>1.582665653064015</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07573352801319526</v>
+        <v>0.07584000394060512</v>
       </c>
       <c r="C78">
-        <v>-1284.956328228455</v>
+        <v>-1353.985438890446</v>
       </c>
       <c r="D78">
-        <v>2422.959671771545</v>
+        <v>2414.371561109554</v>
       </c>
       <c r="E78">
-        <v>111.0160000000005</v>
+        <v>171.4570000000003</v>
       </c>
       <c r="F78">
-        <v>4593.516000000001</v>
+        <v>4653.957</v>
       </c>
       <c r="G78">
         <v>885.6</v>
@@ -7683,28 +7683,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M78">
-        <v>413.41644</v>
+        <v>418.85613</v>
       </c>
       <c r="N78">
-        <v>240.8835600000002</v>
+        <v>235.4438700000002</v>
       </c>
       <c r="O78">
-        <v>72.26506800000004</v>
+        <v>70.63316100000004</v>
       </c>
       <c r="P78">
-        <v>168.6184920000001</v>
+        <v>164.8107090000001</v>
       </c>
       <c r="Q78">
-        <v>726.3184920000001</v>
+        <v>722.5107090000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1160563667216469</v>
+        <v>0.1188261040895875</v>
       </c>
       <c r="T78">
-        <v>1.622548885026488</v>
+        <v>1.686515105995092</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.582665653064015</v>
+        <v>1.562111553673573</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07584000394060512</v>
+        <v>0.07594647986801498</v>
       </c>
       <c r="C79">
-        <v>-1353.985438890446</v>
+        <v>-1422.953883958879</v>
       </c>
       <c r="D79">
-        <v>2414.371561109554</v>
+        <v>2405.844116041121</v>
       </c>
       <c r="E79">
-        <v>171.4570000000003</v>
+        <v>231.8980000000001</v>
       </c>
       <c r="F79">
-        <v>4653.957</v>
+        <v>4714.398</v>
       </c>
       <c r="G79">
         <v>885.6</v>
@@ -7765,28 +7765,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M79">
-        <v>418.85613</v>
+        <v>424.29582</v>
       </c>
       <c r="N79">
-        <v>235.4438700000002</v>
+        <v>230.0041800000002</v>
       </c>
       <c r="O79">
-        <v>70.63316100000004</v>
+        <v>69.00125400000006</v>
       </c>
       <c r="P79">
-        <v>164.8107090000001</v>
+        <v>161.0029260000001</v>
       </c>
       <c r="Q79">
-        <v>722.5107090000001</v>
+        <v>718.7029260000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1188261040895875</v>
+        <v>0.1218476357637045</v>
       </c>
       <c r="T79">
-        <v>1.686515105995092</v>
+        <v>1.756296437960842</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.562111553673573</v>
+        <v>1.54208448247263</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07594647986801498</v>
+        <v>0.07605295579542484</v>
       </c>
       <c r="C80">
-        <v>-1422.953883958879</v>
+        <v>-1491.862303975332</v>
       </c>
       <c r="D80">
-        <v>2405.844116041121</v>
+        <v>2397.376696024668</v>
       </c>
       <c r="E80">
-        <v>231.8980000000001</v>
+        <v>292.3390000000009</v>
       </c>
       <c r="F80">
-        <v>4714.398</v>
+        <v>4774.839000000001</v>
       </c>
       <c r="G80">
         <v>885.6</v>
@@ -7847,28 +7847,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M80">
-        <v>424.29582</v>
+        <v>429.73551</v>
       </c>
       <c r="N80">
-        <v>230.0041800000002</v>
+        <v>224.5644900000001</v>
       </c>
       <c r="O80">
-        <v>69.00125400000006</v>
+        <v>67.36934700000005</v>
       </c>
       <c r="P80">
-        <v>161.0029260000001</v>
+        <v>157.1951430000001</v>
       </c>
       <c r="Q80">
-        <v>718.7029260000002</v>
+        <v>714.8951430000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1218476357637045</v>
+        <v>0.1251569323591659</v>
       </c>
       <c r="T80">
-        <v>1.756296437960842</v>
+        <v>1.832723611066188</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.54208448247263</v>
+        <v>1.52256442573247</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07605295579542484</v>
+        <v>0.07615943172283471</v>
       </c>
       <c r="C81">
-        <v>-1491.862303975332</v>
+        <v>-1560.711330495408</v>
       </c>
       <c r="D81">
-        <v>2397.376696024668</v>
+        <v>2388.968669504593</v>
       </c>
       <c r="E81">
-        <v>292.3390000000009</v>
+        <v>352.7800000000007</v>
       </c>
       <c r="F81">
-        <v>4774.839000000001</v>
+        <v>4835.280000000001</v>
       </c>
       <c r="G81">
         <v>885.6</v>
@@ -7929,28 +7929,28 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M81">
-        <v>429.73551</v>
+        <v>435.1752</v>
       </c>
       <c r="N81">
-        <v>224.5644900000001</v>
+        <v>219.1248000000002</v>
       </c>
       <c r="O81">
-        <v>67.36934700000005</v>
+        <v>65.73744000000005</v>
       </c>
       <c r="P81">
-        <v>157.1951430000001</v>
+        <v>153.3873600000001</v>
       </c>
       <c r="Q81">
-        <v>714.8951430000002</v>
+        <v>711.0873600000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1251569323591659</v>
+        <v>0.1287971586141735</v>
       </c>
       <c r="T81">
-        <v>1.832723611066188</v>
+        <v>1.916793501482068</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.52256442573247</v>
+        <v>1.503532370410814</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07615943172283471</v>
+        <v>0.1121431342004322</v>
       </c>
       <c r="C82">
-        <v>-1560.711330495408</v>
+        <v>-2916.899642825358</v>
       </c>
       <c r="D82">
-        <v>2388.968669504593</v>
+        <v>1093.221357174642</v>
       </c>
       <c r="E82">
-        <v>352.7800000000007</v>
+        <v>413.2210000000005</v>
       </c>
       <c r="F82">
-        <v>4835.280000000001</v>
+        <v>4895.721</v>
       </c>
       <c r="G82">
         <v>885.6</v>
@@ -8011,45 +8011,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M82">
-        <v>435.1752</v>
+        <v>718.6918428000001</v>
       </c>
       <c r="N82">
-        <v>219.1248000000002</v>
+        <v>-64.39184279999995</v>
       </c>
       <c r="O82">
-        <v>65.73744000000005</v>
+        <v>-19.31755283999998</v>
       </c>
       <c r="P82">
-        <v>153.3873600000001</v>
+        <v>-45.07428995999997</v>
       </c>
       <c r="Q82">
-        <v>711.0873600000002</v>
+        <v>512.6257100400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1287971586141735</v>
+        <v>0.1353233336910831</v>
       </c>
       <c r="T82">
-        <v>1.916793501482068</v>
+        <v>2.067513480163581</v>
       </c>
       <c r="U82">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.3</v>
+        <v>0.2731212298657246</v>
       </c>
       <c r="W82">
-        <v>0.063</v>
+        <v>0.1067058034557116</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.503532370410814</v>
+        <v>0.9104040995524154</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1121431342004322</v>
+        <v>0.1131531342004322</v>
       </c>
       <c r="C83">
-        <v>-2916.899642825358</v>
+        <v>-2993.734142309147</v>
       </c>
       <c r="D83">
-        <v>1093.221357174642</v>
+        <v>1076.827857690854</v>
       </c>
       <c r="E83">
-        <v>413.2210000000005</v>
+        <v>473.6620000000003</v>
       </c>
       <c r="F83">
-        <v>4895.721</v>
+        <v>4956.162</v>
       </c>
       <c r="G83">
         <v>885.6</v>
@@ -8093,37 +8093,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M83">
-        <v>718.6918428000001</v>
+        <v>727.5645816000001</v>
       </c>
       <c r="N83">
-        <v>-64.39184279999995</v>
+        <v>-73.26458159999993</v>
       </c>
       <c r="O83">
-        <v>-19.31755283999998</v>
+        <v>-21.97937447999998</v>
       </c>
       <c r="P83">
-        <v>-45.07428995999997</v>
+        <v>-51.28520711999995</v>
       </c>
       <c r="Q83">
-        <v>512.6257100400001</v>
+        <v>506.4147928800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1353233336910831</v>
+        <v>0.1402968522294766</v>
       </c>
       <c r="T83">
-        <v>2.067513480163581</v>
+        <v>2.182375340172669</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2731212298657246</v>
+        <v>0.2697904831600451</v>
       </c>
       <c r="W83">
-        <v>0.1067058034557116</v>
+        <v>0.1071947570721054</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9104040995524154</v>
+        <v>0.8993016105334835</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1131531342004322</v>
+        <v>0.1141631342004322</v>
       </c>
       <c r="C84">
-        <v>-2993.734142309147</v>
+        <v>-3070.084245204856</v>
       </c>
       <c r="D84">
-        <v>1076.827857690854</v>
+        <v>1060.918754795145</v>
       </c>
       <c r="E84">
-        <v>473.6620000000003</v>
+        <v>534.103000000001</v>
       </c>
       <c r="F84">
-        <v>4956.162</v>
+        <v>5016.603000000001</v>
       </c>
       <c r="G84">
         <v>885.6</v>
@@ -8175,37 +8175,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M84">
-        <v>727.5645816000001</v>
+        <v>736.4373204000002</v>
       </c>
       <c r="N84">
-        <v>-73.26458159999993</v>
+        <v>-82.13732040000002</v>
       </c>
       <c r="O84">
-        <v>-21.97937447999998</v>
+        <v>-24.64119612000001</v>
       </c>
       <c r="P84">
-        <v>-51.28520711999995</v>
+        <v>-57.49612428000002</v>
       </c>
       <c r="Q84">
-        <v>506.4147928800001</v>
+        <v>500.20387572</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1402968522294766</v>
+        <v>0.1458554905959164</v>
       </c>
       <c r="T84">
-        <v>2.182375340172669</v>
+        <v>2.310750360182826</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2697904831600451</v>
+        <v>0.2665399954111288</v>
       </c>
       <c r="W84">
-        <v>0.1071947570721054</v>
+        <v>0.1076719286736463</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8993016105334835</v>
+        <v>0.8884666513704294</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1141631342004322</v>
+        <v>0.1151731342004322</v>
       </c>
       <c r="C85">
-        <v>-3070.084245204856</v>
+        <v>-3145.971108429765</v>
       </c>
       <c r="D85">
-        <v>1060.918754795145</v>
+        <v>1045.472891570236</v>
       </c>
       <c r="E85">
-        <v>534.103000000001</v>
+        <v>594.5440000000008</v>
       </c>
       <c r="F85">
-        <v>5016.603000000001</v>
+        <v>5077.044000000001</v>
       </c>
       <c r="G85">
         <v>885.6</v>
@@ -8257,37 +8257,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M85">
-        <v>736.4373204000002</v>
+        <v>745.3100592000002</v>
       </c>
       <c r="N85">
-        <v>-82.13732040000002</v>
+        <v>-91.0100592</v>
       </c>
       <c r="O85">
-        <v>-24.64119612000001</v>
+        <v>-27.30301776</v>
       </c>
       <c r="P85">
-        <v>-57.49612428000002</v>
+        <v>-63.70704144</v>
       </c>
       <c r="Q85">
-        <v>500.20387572</v>
+        <v>493.99295856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1458554905959164</v>
+        <v>0.1521089587581612</v>
       </c>
       <c r="T85">
-        <v>2.310750360182826</v>
+        <v>2.455172257694253</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2665399954111288</v>
+        <v>0.263366900227663</v>
       </c>
       <c r="W85">
-        <v>0.1076719286736463</v>
+        <v>0.1081377390465791</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8884666513704294</v>
+        <v>0.8778896674255433</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1151731342004322</v>
+        <v>0.1161831342004322</v>
       </c>
       <c r="C86">
-        <v>-3145.971108429763</v>
+        <v>-3221.414674491669</v>
       </c>
       <c r="D86">
-        <v>1045.472891570237</v>
+        <v>1030.470325508331</v>
       </c>
       <c r="E86">
-        <v>594.5439999999999</v>
+        <v>654.9850000000006</v>
       </c>
       <c r="F86">
-        <v>5077.044</v>
+        <v>5137.485000000001</v>
       </c>
       <c r="G86">
         <v>885.6</v>
@@ -8339,37 +8339,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M86">
-        <v>745.3100592000001</v>
+        <v>754.1827980000002</v>
       </c>
       <c r="N86">
-        <v>-91.01005919999989</v>
+        <v>-99.88279799999998</v>
       </c>
       <c r="O86">
-        <v>-27.30301775999996</v>
+        <v>-29.96483939999999</v>
       </c>
       <c r="P86">
-        <v>-63.70704143999993</v>
+        <v>-69.91795859999999</v>
       </c>
       <c r="Q86">
-        <v>493.9929585600001</v>
+        <v>487.7820414</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1521089587581611</v>
+        <v>0.1591962226753718</v>
       </c>
       <c r="T86">
-        <v>2.455172257694251</v>
+        <v>2.618850408207202</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2633669002276631</v>
+        <v>0.2602684661073376</v>
       </c>
       <c r="W86">
-        <v>0.1081377390465791</v>
+        <v>0.1085925891754429</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8778896674255434</v>
+        <v>0.8675615536911252</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1161831342004322</v>
+        <v>0.1171931342004322</v>
       </c>
       <c r="C87">
-        <v>-3221.414674491669</v>
+        <v>-3296.43375739025</v>
       </c>
       <c r="D87">
-        <v>1030.470325508331</v>
+        <v>1015.89224260975</v>
       </c>
       <c r="E87">
-        <v>654.9850000000006</v>
+        <v>715.4260000000004</v>
       </c>
       <c r="F87">
-        <v>5137.485000000001</v>
+        <v>5197.926</v>
       </c>
       <c r="G87">
         <v>885.6</v>
@@ -8421,37 +8421,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M87">
-        <v>754.1827980000002</v>
+        <v>763.0555368000001</v>
       </c>
       <c r="N87">
-        <v>-99.88279799999998</v>
+        <v>-108.7555368</v>
       </c>
       <c r="O87">
-        <v>-29.96483939999999</v>
+        <v>-32.62666103999999</v>
       </c>
       <c r="P87">
-        <v>-69.91795859999999</v>
+        <v>-76.12887575999997</v>
       </c>
       <c r="Q87">
-        <v>487.7820414</v>
+        <v>481.5711242400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1591962226753718</v>
+        <v>0.1672959528664698</v>
       </c>
       <c r="T87">
-        <v>2.618850408207202</v>
+        <v>2.805911151650573</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2602684661073376</v>
+        <v>0.2572420885944616</v>
       </c>
       <c r="W87">
-        <v>0.1085925891754429</v>
+        <v>0.1090368613943331</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8675615536911252</v>
+        <v>0.8574736286482052</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1171931342004322</v>
+        <v>0.1182031342004322</v>
       </c>
       <c r="C88">
-        <v>-3296.43375739025</v>
+        <v>-3371.046121328659</v>
       </c>
       <c r="D88">
-        <v>1015.89224260975</v>
+        <v>1001.720878671341</v>
       </c>
       <c r="E88">
-        <v>715.4260000000004</v>
+        <v>775.8670000000002</v>
       </c>
       <c r="F88">
-        <v>5197.926</v>
+        <v>5258.367</v>
       </c>
       <c r="G88">
         <v>885.6</v>
@@ -8503,37 +8503,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M88">
-        <v>763.0555368000001</v>
+        <v>771.9282756000001</v>
       </c>
       <c r="N88">
-        <v>-108.7555368</v>
+        <v>-117.6282755999999</v>
       </c>
       <c r="O88">
-        <v>-32.62666103999999</v>
+        <v>-35.28848267999998</v>
       </c>
       <c r="P88">
-        <v>-76.12887575999997</v>
+        <v>-82.33979291999995</v>
       </c>
       <c r="Q88">
-        <v>481.5711242400001</v>
+        <v>475.3602070800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1672959528664698</v>
+        <v>0.1766417953946598</v>
       </c>
       <c r="T88">
-        <v>2.805911151650573</v>
+        <v>3.02175047100831</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2572420885944616</v>
+        <v>0.2542852829784332</v>
       </c>
       <c r="W88">
-        <v>0.1090368613943331</v>
+        <v>0.109470920458766</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8574736286482052</v>
+        <v>0.8476176099281109</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1182031342004322</v>
+        <v>0.1192131342004322</v>
       </c>
       <c r="C89">
-        <v>-3371.046121328659</v>
+        <v>-3445.268552927749</v>
       </c>
       <c r="D89">
-        <v>1001.720878671341</v>
+        <v>987.9394470722508</v>
       </c>
       <c r="E89">
-        <v>775.8670000000002</v>
+        <v>836.308</v>
       </c>
       <c r="F89">
-        <v>5258.367</v>
+        <v>5318.808</v>
       </c>
       <c r="G89">
         <v>885.6</v>
@@ -8585,37 +8585,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M89">
-        <v>771.9282756000001</v>
+        <v>780.8010144000001</v>
       </c>
       <c r="N89">
-        <v>-117.6282755999999</v>
+        <v>-126.5010143999999</v>
       </c>
       <c r="O89">
-        <v>-35.28848267999998</v>
+        <v>-37.95030431999997</v>
       </c>
       <c r="P89">
-        <v>-82.33979291999995</v>
+        <v>-88.55071007999994</v>
       </c>
       <c r="Q89">
-        <v>475.3602070800001</v>
+        <v>469.1492899200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1766417953946598</v>
+        <v>0.1875452783442148</v>
       </c>
       <c r="T89">
-        <v>3.02175047100831</v>
+        <v>3.273563010259003</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2542852829784332</v>
+        <v>0.251395677490042</v>
       </c>
       <c r="W89">
-        <v>0.109470920458766</v>
+        <v>0.1098951145444619</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8476176099281109</v>
+        <v>0.8379855916334733</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1192131342004322</v>
+        <v>0.1202231342004322</v>
       </c>
       <c r="C90">
-        <v>-3445.268552927749</v>
+        <v>-3519.116927560155</v>
       </c>
       <c r="D90">
-        <v>987.9394470722508</v>
+        <v>974.5320724398454</v>
       </c>
       <c r="E90">
-        <v>836.308</v>
+        <v>896.7490000000007</v>
       </c>
       <c r="F90">
-        <v>5318.808</v>
+        <v>5379.249000000001</v>
       </c>
       <c r="G90">
         <v>885.6</v>
@@ -8667,37 +8667,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M90">
-        <v>780.8010144000001</v>
+        <v>789.6737532000002</v>
       </c>
       <c r="N90">
-        <v>-126.5010143999999</v>
+        <v>-135.3737532</v>
       </c>
       <c r="O90">
-        <v>-37.95030431999997</v>
+        <v>-40.61212596</v>
       </c>
       <c r="P90">
-        <v>-88.55071007999994</v>
+        <v>-94.76162724000001</v>
       </c>
       <c r="Q90">
-        <v>469.1492899200001</v>
+        <v>462.93837276</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1875452783442148</v>
+        <v>0.2004312127391434</v>
       </c>
       <c r="T90">
-        <v>3.273563010259003</v>
+        <v>3.571159647555276</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.251395677490042</v>
+        <v>0.248571006956446</v>
       </c>
       <c r="W90">
-        <v>0.1098951145444619</v>
+        <v>0.1103097761787937</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8379855916334733</v>
+        <v>0.8285700231881532</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1202231342004322</v>
+        <v>0.1212331342004322</v>
       </c>
       <c r="C91">
-        <v>-3519.116927560155</v>
+        <v>-3592.606270355365</v>
       </c>
       <c r="D91">
-        <v>974.5320724398454</v>
+        <v>961.4837296446357</v>
       </c>
       <c r="E91">
-        <v>896.7490000000007</v>
+        <v>957.1900000000005</v>
       </c>
       <c r="F91">
-        <v>5379.249000000001</v>
+        <v>5439.690000000001</v>
       </c>
       <c r="G91">
         <v>885.6</v>
@@ -8749,37 +8749,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M91">
-        <v>789.6737532000002</v>
+        <v>798.5464920000002</v>
       </c>
       <c r="N91">
-        <v>-135.3737532</v>
+        <v>-144.246492</v>
       </c>
       <c r="O91">
-        <v>-40.61212596</v>
+        <v>-43.27394759999999</v>
       </c>
       <c r="P91">
-        <v>-94.76162724000001</v>
+        <v>-100.9725444</v>
       </c>
       <c r="Q91">
-        <v>462.93837276</v>
+        <v>456.7274556</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2004312127391434</v>
+        <v>0.2158943340130578</v>
       </c>
       <c r="T91">
-        <v>3.571159647555276</v>
+        <v>3.928275612310804</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.248571006956446</v>
+        <v>0.2458091068791521</v>
       </c>
       <c r="W91">
-        <v>0.1103097761787937</v>
+        <v>0.1107152231101405</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8285700231881532</v>
+        <v>0.8193636895971739</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1212331342004322</v>
+        <v>0.1222431342004322</v>
       </c>
       <c r="C92">
-        <v>-3592.606270355365</v>
+        <v>-3665.750812368632</v>
       </c>
       <c r="D92">
-        <v>961.4837296446357</v>
+        <v>948.7801876313683</v>
       </c>
       <c r="E92">
-        <v>957.1900000000005</v>
+        <v>1017.631</v>
       </c>
       <c r="F92">
-        <v>5439.690000000001</v>
+        <v>5500.131</v>
       </c>
       <c r="G92">
         <v>885.6</v>
@@ -8831,37 +8831,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M92">
-        <v>798.5464920000002</v>
+        <v>807.4192308000002</v>
       </c>
       <c r="N92">
-        <v>-144.246492</v>
+        <v>-153.1192308</v>
       </c>
       <c r="O92">
-        <v>-43.27394759999999</v>
+        <v>-45.93576923999999</v>
       </c>
       <c r="P92">
-        <v>-100.9725444</v>
+        <v>-107.18346156</v>
       </c>
       <c r="Q92">
-        <v>456.7274556</v>
+        <v>450.5165384400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2158943340130578</v>
+        <v>0.2347937044589531</v>
       </c>
       <c r="T92">
-        <v>3.928275612310804</v>
+        <v>4.364750680345338</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2458091068791521</v>
+        <v>0.2431079079024581</v>
       </c>
       <c r="W92">
-        <v>0.1107152231101405</v>
+        <v>0.1111117591199191</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8193636895971739</v>
+        <v>0.8103596930081939</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1222431342004322</v>
+        <v>0.1232531342004322</v>
       </c>
       <c r="C93">
-        <v>-3665.750812368632</v>
+        <v>-3738.564042355193</v>
       </c>
       <c r="D93">
-        <v>948.7801876313683</v>
+        <v>936.4079576448078</v>
       </c>
       <c r="E93">
-        <v>1017.631</v>
+        <v>1078.072000000001</v>
       </c>
       <c r="F93">
-        <v>5500.131</v>
+        <v>5560.572000000001</v>
       </c>
       <c r="G93">
         <v>885.6</v>
@@ -8913,37 +8913,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M93">
-        <v>807.4192308000002</v>
+        <v>816.2919696000002</v>
       </c>
       <c r="N93">
-        <v>-153.1192308</v>
+        <v>-161.9919696000001</v>
       </c>
       <c r="O93">
-        <v>-45.93576923999999</v>
+        <v>-48.59759088000002</v>
       </c>
       <c r="P93">
-        <v>-107.18346156</v>
+        <v>-113.39437872</v>
       </c>
       <c r="Q93">
-        <v>450.5165384400001</v>
+        <v>444.30562128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2347937044589531</v>
+        <v>0.2584179175163223</v>
       </c>
       <c r="T93">
-        <v>4.364750680345338</v>
+        <v>4.910344515388506</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2431079079024581</v>
+        <v>0.2404654306426488</v>
       </c>
       <c r="W93">
-        <v>0.1111117591199191</v>
+        <v>0.1114996747816592</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8103596930081939</v>
+        <v>0.801551435475496</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1232531342004322</v>
+        <v>0.1757825560278822</v>
       </c>
       <c r="C94">
-        <v>-3738.564042355193</v>
+        <v>-4177.432503030406</v>
       </c>
       <c r="D94">
-        <v>936.4079576448078</v>
+        <v>557.980496969595</v>
       </c>
       <c r="E94">
-        <v>1078.072000000001</v>
+        <v>1138.513000000001</v>
       </c>
       <c r="F94">
-        <v>5560.572000000001</v>
+        <v>5621.013000000001</v>
       </c>
       <c r="G94">
         <v>885.6</v>
@@ -8995,45 +8995,45 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M94">
-        <v>816.2919696000002</v>
+        <v>1128.6994104</v>
       </c>
       <c r="N94">
-        <v>-161.9919696000001</v>
+        <v>-474.3994104000001</v>
       </c>
       <c r="O94">
-        <v>-48.59759088000002</v>
+        <v>-142.31982312</v>
       </c>
       <c r="P94">
-        <v>-113.39437872</v>
+        <v>-332.0795872800001</v>
       </c>
       <c r="Q94">
-        <v>444.30562128</v>
+        <v>225.62041272</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2584179175163223</v>
+        <v>0.3073550746965109</v>
       </c>
       <c r="T94">
-        <v>4.910344515388506</v>
+        <v>6.040532902921729</v>
       </c>
       <c r="U94">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.2404654306426488</v>
+        <v>0.1739081266379299</v>
       </c>
       <c r="W94">
-        <v>0.1114996747816592</v>
+        <v>0.1658792481711037</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.801551435475496</v>
+        <v>0.5796937554597663</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1757825560278822</v>
+        <v>0.1773325560278822</v>
       </c>
       <c r="C95">
-        <v>-4177.432503030406</v>
+        <v>-4244.448831575831</v>
       </c>
       <c r="D95">
-        <v>557.980496969595</v>
+        <v>551.4051684241697</v>
       </c>
       <c r="E95">
-        <v>1138.513000000001</v>
+        <v>1198.954000000001</v>
       </c>
       <c r="F95">
-        <v>5621.013000000001</v>
+        <v>5681.454000000001</v>
       </c>
       <c r="G95">
         <v>885.6</v>
@@ -9077,37 +9077,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M95">
-        <v>1128.6994104</v>
+        <v>1140.8359632</v>
       </c>
       <c r="N95">
-        <v>-474.3994104000001</v>
+        <v>-486.5359632</v>
       </c>
       <c r="O95">
-        <v>-142.31982312</v>
+        <v>-145.96078896</v>
       </c>
       <c r="P95">
-        <v>-332.0795872800001</v>
+        <v>-340.57517424</v>
       </c>
       <c r="Q95">
-        <v>225.62041272</v>
+        <v>217.12482576</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3073550746965109</v>
+        <v>0.3509475871459294</v>
       </c>
       <c r="T95">
-        <v>6.040532902921729</v>
+        <v>7.047288386742019</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1739081266379299</v>
+        <v>0.1720580401843349</v>
       </c>
       <c r="W95">
-        <v>0.1658792481711037</v>
+        <v>0.1662507455309856</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5796937554597663</v>
+        <v>0.5735268006144497</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1773325560278822</v>
+        <v>0.1788825560278822</v>
       </c>
       <c r="C96">
-        <v>-4244.448831575831</v>
+        <v>-4311.311995656286</v>
       </c>
       <c r="D96">
-        <v>551.4051684241697</v>
+        <v>544.9830043437144</v>
       </c>
       <c r="E96">
-        <v>1198.954000000001</v>
+        <v>1259.395</v>
       </c>
       <c r="F96">
-        <v>5681.454000000001</v>
+        <v>5741.895</v>
       </c>
       <c r="G96">
         <v>885.6</v>
@@ -9159,37 +9159,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M96">
-        <v>1140.8359632</v>
+        <v>1152.972516</v>
       </c>
       <c r="N96">
-        <v>-486.5359632</v>
+        <v>-498.6725159999999</v>
       </c>
       <c r="O96">
-        <v>-145.96078896</v>
+        <v>-149.6017548</v>
       </c>
       <c r="P96">
-        <v>-340.57517424</v>
+        <v>-349.0707611999999</v>
       </c>
       <c r="Q96">
-        <v>217.12482576</v>
+        <v>208.6292388000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3509475871459294</v>
+        <v>0.4119771045751155</v>
       </c>
       <c r="T96">
-        <v>7.047288386742019</v>
+        <v>8.456746064090428</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1720580401843349</v>
+        <v>0.1702469029192366</v>
       </c>
       <c r="W96">
-        <v>0.1662507455309856</v>
+        <v>0.1666144218938173</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5735268006144497</v>
+        <v>0.5674896763974555</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1788825560278822</v>
+        <v>0.1804325560278822</v>
       </c>
       <c r="C97">
-        <v>-4311.311995656286</v>
+        <v>-4378.027285335209</v>
       </c>
       <c r="D97">
-        <v>544.9830043437144</v>
+        <v>538.7087146647916</v>
       </c>
       <c r="E97">
-        <v>1259.395</v>
+        <v>1319.836000000001</v>
       </c>
       <c r="F97">
-        <v>5741.895</v>
+        <v>5802.336000000001</v>
       </c>
       <c r="G97">
         <v>885.6</v>
@@ -9241,37 +9241,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M97">
-        <v>1152.972516</v>
+        <v>1165.1090688</v>
       </c>
       <c r="N97">
-        <v>-498.6725159999999</v>
+        <v>-510.8090688</v>
       </c>
       <c r="O97">
-        <v>-149.6017548</v>
+        <v>-153.24272064</v>
       </c>
       <c r="P97">
-        <v>-349.0707611999999</v>
+        <v>-357.56634816</v>
       </c>
       <c r="Q97">
-        <v>208.6292388000002</v>
+        <v>200.1336518400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4119771045751155</v>
+        <v>0.5035213807188945</v>
       </c>
       <c r="T97">
-        <v>8.456746064090428</v>
+        <v>10.57093258011304</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1702469029192366</v>
+        <v>0.1684734976804946</v>
       </c>
       <c r="W97">
-        <v>0.1666144218938173</v>
+        <v>0.1669705216657567</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5674896763974555</v>
+        <v>0.5615783256016487</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1804325560278822</v>
+        <v>0.1819825560278822</v>
       </c>
       <c r="C98">
-        <v>-4378.027285335209</v>
+        <v>-4444.599749834667</v>
       </c>
       <c r="D98">
-        <v>538.7087146647916</v>
+        <v>532.5772501653333</v>
       </c>
       <c r="E98">
-        <v>1319.836</v>
+        <v>1380.277</v>
       </c>
       <c r="F98">
-        <v>5802.336</v>
+        <v>5862.777</v>
       </c>
       <c r="G98">
         <v>885.6</v>
@@ -9323,37 +9323,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M98">
-        <v>1165.1090688</v>
+        <v>1177.2456216</v>
       </c>
       <c r="N98">
-        <v>-510.8090688</v>
+        <v>-522.9456215999999</v>
       </c>
       <c r="O98">
-        <v>-153.24272064</v>
+        <v>-156.88368648</v>
       </c>
       <c r="P98">
-        <v>-357.56634816</v>
+        <v>-366.0619351199999</v>
       </c>
       <c r="Q98">
-        <v>200.1336518400001</v>
+        <v>191.6380648800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5035213807188933</v>
+        <v>0.6560951742918577</v>
       </c>
       <c r="T98">
-        <v>10.57093258011301</v>
+        <v>14.09457677348401</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1684734976804946</v>
+        <v>0.1667366574982214</v>
       </c>
       <c r="W98">
-        <v>0.1669705216657567</v>
+        <v>0.1673192791743572</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5615783256016487</v>
+        <v>0.5557888583274049</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1819825560278822</v>
+        <v>0.1835325560278822</v>
       </c>
       <c r="C99">
-        <v>-4444.599749834667</v>
+        <v>-4511.034211087133</v>
       </c>
       <c r="D99">
-        <v>532.5772501653333</v>
+        <v>526.583788912867</v>
       </c>
       <c r="E99">
-        <v>1380.277</v>
+        <v>1440.718</v>
       </c>
       <c r="F99">
-        <v>5862.777</v>
+        <v>5923.218</v>
       </c>
       <c r="G99">
         <v>885.6</v>
@@ -9405,37 +9405,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M99">
-        <v>1177.2456216</v>
+        <v>1189.3821744</v>
       </c>
       <c r="N99">
-        <v>-522.9456215999999</v>
+        <v>-535.0821743999998</v>
       </c>
       <c r="O99">
-        <v>-156.88368648</v>
+        <v>-160.5246523199999</v>
       </c>
       <c r="P99">
-        <v>-366.0619351199999</v>
+        <v>-374.5575220799998</v>
       </c>
       <c r="Q99">
-        <v>191.6380648800001</v>
+        <v>183.1424779200002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6560951742918577</v>
+        <v>0.9612427614377866</v>
       </c>
       <c r="T99">
-        <v>14.09457677348401</v>
+        <v>21.14186516022602</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1667366574982214</v>
+        <v>0.1650352630339539</v>
       </c>
       <c r="W99">
-        <v>0.1673192791743572</v>
+        <v>0.1676609191827821</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5557888583274049</v>
+        <v>0.5501175434465131</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1835325560278822</v>
+        <v>0.1850825560278822</v>
       </c>
       <c r="C100">
-        <v>-4511.034211087133</v>
+        <v>-4577.3352763824</v>
       </c>
       <c r="D100">
-        <v>526.583788912867</v>
+        <v>520.723723617601</v>
       </c>
       <c r="E100">
-        <v>1440.718</v>
+        <v>1501.159000000001</v>
       </c>
       <c r="F100">
-        <v>5923.218</v>
+        <v>5983.659000000001</v>
       </c>
       <c r="G100">
         <v>885.6</v>
@@ -9487,37 +9487,37 @@
         <v>654.3000000000002</v>
       </c>
       <c r="M100">
-        <v>1189.3821744</v>
+        <v>1201.5187272</v>
       </c>
       <c r="N100">
-        <v>-535.0821743999998</v>
+        <v>-547.2187271999999</v>
       </c>
       <c r="O100">
-        <v>-160.5246523199999</v>
+        <v>-164.16561816</v>
       </c>
       <c r="P100">
-        <v>-374.5575220799998</v>
+        <v>-383.0531090399999</v>
       </c>
       <c r="Q100">
-        <v>183.1424779200002</v>
+        <v>174.6468909600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9612427614377866</v>
+        <v>1.876685522875573</v>
       </c>
       <c r="T100">
-        <v>21.14186516022602</v>
+        <v>42.28373032045204</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1650352630339539</v>
+        <v>0.1633682401750251</v>
       </c>
       <c r="W100">
-        <v>0.1676609191827821</v>
+        <v>0.167995657372855</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5501175434465131</v>
+        <v>0.5445608005834169</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1850825560278822</v>
-      </c>
-      <c r="C101">
-        <v>-4577.3352763824</v>
-      </c>
-      <c r="D101">
-        <v>520.723723617601</v>
-      </c>
-      <c r="E101">
-        <v>1501.159000000001</v>
-      </c>
-      <c r="F101">
-        <v>5983.659000000001</v>
-      </c>
-      <c r="G101">
-        <v>885.6</v>
-      </c>
-      <c r="H101">
-        <v>1561.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1212</v>
-      </c>
-      <c r="K101">
-        <v>557.7</v>
-      </c>
-      <c r="L101">
-        <v>654.3000000000002</v>
-      </c>
-      <c r="M101">
-        <v>1201.5187272</v>
-      </c>
-      <c r="N101">
-        <v>-547.2187271999999</v>
-      </c>
-      <c r="O101">
-        <v>-164.16561816</v>
-      </c>
-      <c r="P101">
-        <v>-383.0531090399999</v>
-      </c>
-      <c r="Q101">
-        <v>174.6468909600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.876685522875573</v>
-      </c>
-      <c r="T101">
-        <v>42.28373032045204</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1633682401750251</v>
-      </c>
-      <c r="W101">
-        <v>0.167995657372855</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5445608005834169</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
